--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -528,25 +528,25 @@
         <v>1400000</v>
       </c>
       <c r="D2" t="n">
-        <v>164048</v>
+        <v>242888</v>
       </c>
       <c r="E2" t="n">
-        <v>43905</v>
+        <v>49678</v>
       </c>
       <c r="F2" t="n">
-        <v>120143</v>
+        <v>193210</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,11 +554,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-76291</v>
+        <v>-96249</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-257.5%</t>
+          <t>-300.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -581,25 +581,25 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>80448</v>
+        <v>91391</v>
       </c>
       <c r="E3" t="n">
-        <v>102330</v>
+        <v>121124</v>
       </c>
       <c r="F3" t="n">
-        <v>-21882</v>
+        <v>-29733</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -607,11 +607,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-70360</v>
+        <v>-106834</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-68.9%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -634,25 +634,25 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>187339</v>
+        <v>242602</v>
       </c>
       <c r="E4" t="n">
-        <v>35582</v>
+        <v>36361</v>
       </c>
       <c r="F4" t="n">
-        <v>151757</v>
+        <v>206241</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -660,11 +660,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-87466</v>
+        <v>-96137</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-273.5%</t>
+          <t>-314.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -687,25 +687,25 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>255954</v>
+        <v>316457</v>
       </c>
       <c r="E5" t="n">
-        <v>18037</v>
+        <v>84030</v>
       </c>
       <c r="F5" t="n">
-        <v>237917</v>
+        <v>232427</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-237442</v>
+        <v>-293447</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-200.2%</t>
+          <t>-179.2%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -740,50 +740,50 @@
         <v>2000000</v>
       </c>
       <c r="D6" t="n">
-        <v>290097</v>
+        <v>590420</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>290097</v>
+        <v>590420</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>492709</v>
+        <v>608284</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>492709</v>
+        <v>608284</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>130403</v>
+        <v>30417</v>
       </c>
       <c r="P6" t="n">
-        <v>159694</v>
+        <v>560003</v>
       </c>
       <c r="Q6" t="n">
-        <v>279699</v>
+        <v>549624</v>
       </c>
     </row>
     <row r="7">
@@ -801,23 +801,23 @@
         <v>380000</v>
       </c>
       <c r="D7" t="n">
-        <v>56438</v>
+        <v>57135</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>3419</v>
       </c>
       <c r="F7" t="n">
-        <v>56419</v>
+        <v>53716</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -825,26 +825,26 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+26775.2%</t>
+          <t>+27107.1%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-19190</v>
+        <v>-26190</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-394.0%</t>
+          <t>-305.1%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>45604</v>
+        <v>45903</v>
       </c>
       <c r="P7" t="n">
-        <v>10815</v>
+        <v>7813</v>
       </c>
       <c r="Q7" t="n">
-        <v>18037</v>
+        <v>18336</v>
       </c>
     </row>
     <row r="8">
@@ -862,23 +862,23 @@
         <v>400000</v>
       </c>
       <c r="D8" t="n">
-        <v>178784</v>
+        <v>236801</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>178784</v>
+        <v>236801</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -886,22 +886,22 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-10028</v>
+        <v>-23028</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-1882.8%</t>
+          <t>-1128.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>22388</v>
+        <v>29007</v>
       </c>
       <c r="P8" t="n">
-        <v>156396</v>
+        <v>207794</v>
       </c>
       <c r="Q8" t="n">
-        <v>45600</v>
+        <v>52219</v>
       </c>
     </row>
     <row r="9">
@@ -919,23 +919,23 @@
         <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>131088</v>
+        <v>193702</v>
       </c>
       <c r="E9" t="n">
-        <v>25500</v>
+        <v>33000</v>
       </c>
       <c r="F9" t="n">
-        <v>105588</v>
+        <v>160702</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -943,7 +943,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+1549.7%</t>
+          <t>+2337.7%</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -951,20 +951,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-687.2%</t>
+          <t>-993.7%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6023</v>
+        <v>6844</v>
       </c>
       <c r="O9" t="n">
-        <v>15629</v>
+        <v>31425</v>
       </c>
       <c r="P9" t="n">
-        <v>83935</v>
+        <v>122433</v>
       </c>
       <c r="Q9" t="n">
-        <v>14796</v>
+        <v>15616</v>
       </c>
     </row>
     <row r="10">
@@ -982,52 +982,52 @@
         <v>800000</v>
       </c>
       <c r="D10" t="n">
-        <v>45155</v>
+        <v>51229</v>
       </c>
       <c r="E10" t="n">
-        <v>42780</v>
+        <v>73809</v>
       </c>
       <c r="F10" t="n">
-        <v>2375</v>
+        <v>-22580</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7276</v>
+        <v>7715</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+520.6%</t>
+          <t>+564.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-7590</v>
+        <v>-7151</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-131.3%</t>
+          <t>+215.8%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1494</v>
+        <v>6355</v>
       </c>
       <c r="O10" t="n">
-        <v>-34915</v>
+        <v>-35527</v>
       </c>
       <c r="P10" t="n">
-        <v>35796</v>
+        <v>6592</v>
       </c>
       <c r="Q10" t="n">
-        <v>-34019</v>
+        <v>-30168</v>
       </c>
     </row>
     <row r="11">
@@ -1045,23 +1045,23 @@
         <v>260000</v>
       </c>
       <c r="D11" t="n">
-        <v>15733</v>
+        <v>16952</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>7102</v>
       </c>
       <c r="F11" t="n">
-        <v>15714</v>
+        <v>9850</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>-6838</v>
+        <v>-15857</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-329.8%</t>
+          <t>-162.1%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>38</v>
+        <v>-7026</v>
       </c>
       <c r="P11" t="n">
-        <v>15676</v>
+        <v>16876</v>
       </c>
       <c r="Q11" t="n">
-        <v>1718</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="12">
@@ -1102,23 +1102,23 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>54407</v>
+        <v>150397</v>
       </c>
       <c r="E12" t="n">
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>45207</v>
+        <v>141197</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1130,18 +1130,18 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-10941.0%</t>
+          <t>-33960.2%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>6613</v>
+        <v>7807</v>
       </c>
       <c r="P12" t="n">
-        <v>38594</v>
+        <v>133390</v>
       </c>
       <c r="Q12" t="n">
-        <v>6619</v>
+        <v>26619</v>
       </c>
     </row>
     <row r="13">
@@ -1159,23 +1159,23 @@
         <v>700000</v>
       </c>
       <c r="D13" t="n">
-        <v>64413</v>
+        <v>87201</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>10796</v>
       </c>
       <c r="F13" t="n">
-        <v>64413</v>
+        <v>76405</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1183,28 +1183,28 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+243.9%</t>
+          <t>+365.5%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-21268</v>
+        <v>-27868</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-402.9%</t>
+          <t>-374.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>12318</v>
       </c>
       <c r="O13" t="n">
-        <v>2607</v>
+        <v>14201</v>
       </c>
       <c r="P13" t="n">
-        <v>49488</v>
+        <v>49886</v>
       </c>
       <c r="Q13" t="n">
-        <v>18937</v>
+        <v>18141</v>
       </c>
     </row>
     <row r="14">
@@ -1222,23 +1222,23 @@
         <v>900000</v>
       </c>
       <c r="D14" t="n">
-        <v>120748</v>
+        <v>478418</v>
       </c>
       <c r="E14" t="n">
-        <v>58847</v>
+        <v>60447</v>
       </c>
       <c r="F14" t="n">
-        <v>61901</v>
+        <v>417971</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1250,18 +1250,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-414.9%</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>-2226.3%</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>21200</v>
+      </c>
       <c r="O14" t="n">
-        <v>-30511</v>
+        <v>57129</v>
       </c>
       <c r="P14" t="n">
-        <v>92412</v>
+        <v>339642</v>
       </c>
       <c r="Q14" t="n">
-        <v>11903</v>
+        <v>105195</v>
       </c>
     </row>
     <row r="15">
@@ -1279,52 +1281,52 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>107777</v>
+        <v>166831</v>
       </c>
       <c r="E15" t="n">
-        <v>8009</v>
+        <v>30609</v>
       </c>
       <c r="F15" t="n">
-        <v>99768</v>
+        <v>136222</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3608</v>
+        <v>4953</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+2887.2%</t>
+          <t>+3268.3%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3399</v>
+        <v>4744</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+2835.2%</t>
+          <t>+2771.5%</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>16580</v>
+        <v>38240</v>
       </c>
       <c r="O15" t="n">
-        <v>28792</v>
+        <v>31586</v>
       </c>
       <c r="P15" t="n">
-        <v>54396</v>
+        <v>66396</v>
       </c>
       <c r="Q15" t="n">
-        <v>16580</v>
+        <v>38240</v>
       </c>
     </row>
     <row r="16">
@@ -1342,23 +1344,23 @@
         <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>39388</v>
+        <v>41715</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>39388</v>
+        <v>41715</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1366,22 +1368,22 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-38689</v>
+        <v>-40765</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-201.8%</t>
+          <t>-202.3%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>11694</v>
+        <v>12429</v>
       </c>
       <c r="P16" t="n">
-        <v>27694</v>
+        <v>29286</v>
       </c>
       <c r="Q16" t="n">
-        <v>102</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17">
@@ -1415,11 +1417,11 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-6819</v>
+        <v>-22514</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1448,54 +1450,54 @@
         <v>14090000</v>
       </c>
       <c r="D18" t="n">
-        <v>1791817</v>
+        <v>2964140</v>
       </c>
       <c r="E18" t="n">
-        <v>350727</v>
+        <v>526074</v>
       </c>
       <c r="F18" t="n">
-        <v>1441090</v>
+        <v>2438066</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>530482</v>
+        <v>647841</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+237.8%</t>
+          <t>+357.5%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-123928</v>
+        <v>-181067</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-1262.8%</t>
+          <t>-1446.5%</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>36415</v>
+        <v>84957</v>
       </c>
       <c r="O18" t="n">
-        <v>647413</v>
+        <v>747432</v>
       </c>
       <c r="P18" t="n">
-        <v>757260</v>
+        <v>1605675</v>
       </c>
       <c r="Q18" t="n">
-        <v>668711</v>
+        <v>1192675</v>
       </c>
     </row>
   </sheetData>
@@ -1630,13 +1632,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>455572</v>
+        <v>536582</v>
       </c>
       <c r="D2" t="n">
-        <v>32363</v>
+        <v>65563</v>
       </c>
       <c r="E2" t="n">
-        <v>288740</v>
+        <v>396678</v>
       </c>
     </row>
     <row r="3">
@@ -1651,13 +1653,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>198342</v>
+        <v>217350</v>
       </c>
       <c r="D3" t="n">
-        <v>724896</v>
+        <v>1540111</v>
       </c>
       <c r="E3" t="n">
-        <v>379972</v>
+        <v>795998</v>
       </c>
     </row>
     <row r="4">
@@ -1672,13 +1674,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>123316</v>
+        <v>176383</v>
       </c>
       <c r="D4" t="n">
-        <v>-3173</v>
+        <v>16827</v>
       </c>
       <c r="E4" t="n">
-        <v>77951</v>
+        <v>140222</v>
       </c>
     </row>
     <row r="5">
@@ -1693,13 +1695,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-22200</v>
+        <v>-30051</v>
       </c>
       <c r="D5" t="n">
         <v>318</v>
       </c>
       <c r="E5" t="n">
-        <v>-23276</v>
+        <v>-12627</v>
       </c>
     </row>
     <row r="6">
@@ -1714,13 +1716,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>141738</v>
+        <v>196222</v>
       </c>
       <c r="D6" t="n">
         <v>10019</v>
       </c>
       <c r="E6" t="n">
-        <v>112365</v>
+        <v>146451</v>
       </c>
     </row>
     <row r="7">
@@ -1735,13 +1737,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>212717</v>
+        <v>194027</v>
       </c>
       <c r="D7" t="n">
-        <v>25200</v>
+        <v>38400</v>
       </c>
       <c r="E7" t="n">
-        <v>121699</v>
+        <v>122631</v>
       </c>
     </row>
     <row r="8">
@@ -1756,13 +1758,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>130403</v>
+        <v>30417</v>
       </c>
       <c r="D8" t="n">
-        <v>159694</v>
+        <v>560003</v>
       </c>
       <c r="E8" t="n">
-        <v>279699</v>
+        <v>549624</v>
       </c>
     </row>
     <row r="9">
@@ -1777,13 +1779,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45604</v>
+        <v>45903</v>
       </c>
       <c r="D9" t="n">
-        <v>10815</v>
+        <v>7813</v>
       </c>
       <c r="E9" t="n">
-        <v>18037</v>
+        <v>18336</v>
       </c>
     </row>
     <row r="10">
@@ -1798,13 +1800,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22388</v>
+        <v>29007</v>
       </c>
       <c r="D10" t="n">
-        <v>156396</v>
+        <v>207794</v>
       </c>
       <c r="E10" t="n">
-        <v>45600</v>
+        <v>52219</v>
       </c>
     </row>
     <row r="11">
@@ -1819,13 +1821,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15629</v>
+        <v>31425</v>
       </c>
       <c r="D11" t="n">
-        <v>83935</v>
+        <v>122433</v>
       </c>
       <c r="E11" t="n">
-        <v>14796</v>
+        <v>15616</v>
       </c>
     </row>
     <row r="12">
@@ -1840,13 +1842,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-34915</v>
+        <v>-35527</v>
       </c>
       <c r="D12" t="n">
-        <v>35796</v>
+        <v>6592</v>
       </c>
       <c r="E12" t="n">
-        <v>-34019</v>
+        <v>-30168</v>
       </c>
     </row>
     <row r="13">
@@ -1861,13 +1863,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>-7026</v>
       </c>
       <c r="D13" t="n">
-        <v>15676</v>
+        <v>16876</v>
       </c>
       <c r="E13" t="n">
-        <v>1718</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="14">
@@ -1882,13 +1884,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6613</v>
+        <v>7807</v>
       </c>
       <c r="D14" t="n">
-        <v>38594</v>
+        <v>133390</v>
       </c>
       <c r="E14" t="n">
-        <v>6619</v>
+        <v>26619</v>
       </c>
     </row>
     <row r="15">
@@ -1903,13 +1905,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2607</v>
+        <v>14201</v>
       </c>
       <c r="D15" t="n">
-        <v>49488</v>
+        <v>49886</v>
       </c>
       <c r="E15" t="n">
-        <v>18937</v>
+        <v>18141</v>
       </c>
     </row>
     <row r="16">
@@ -1924,13 +1926,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-30511</v>
+        <v>57129</v>
       </c>
       <c r="D16" t="n">
-        <v>92412</v>
+        <v>339642</v>
       </c>
       <c r="E16" t="n">
-        <v>11903</v>
+        <v>105195</v>
       </c>
     </row>
     <row r="17">
@@ -1945,13 +1947,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28792</v>
+        <v>31586</v>
       </c>
       <c r="D17" t="n">
-        <v>54396</v>
+        <v>66396</v>
       </c>
       <c r="E17" t="n">
-        <v>16580</v>
+        <v>38240</v>
       </c>
     </row>
     <row r="18">
@@ -1966,13 +1968,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11694</v>
+        <v>12429</v>
       </c>
       <c r="D18" t="n">
-        <v>27694</v>
+        <v>29286</v>
       </c>
       <c r="E18" t="n">
-        <v>102</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19">
@@ -2008,13 +2010,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>647413</v>
+        <v>747432</v>
       </c>
       <c r="D20" t="n">
-        <v>757260</v>
+        <v>1605675</v>
       </c>
       <c r="E20" t="n">
-        <v>668711</v>
+        <v>1192675</v>
       </c>
     </row>
   </sheetData>
@@ -2098,31 +2100,31 @@
         <v>191500</v>
       </c>
       <c r="D2" t="n">
-        <v>28734</v>
+        <v>74994</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8096.7</v>
+        <v>9776.700000000001</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>20637.3</v>
+        <v>65217.3</v>
       </c>
     </row>
     <row r="3">
@@ -2140,19 +2142,19 @@
         <v>185200</v>
       </c>
       <c r="D3" t="n">
-        <v>1280</v>
+        <v>6260</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2160,11 +2162,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>389.0%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-3699</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="4">
@@ -2266,31 +2268,31 @@
         <v>98625</v>
       </c>
       <c r="D6" t="n">
-        <v>4980</v>
+        <v>14940</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4000</v>
+        <v>5680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>980</v>
+        <v>9260</v>
       </c>
     </row>
     <row r="7">
@@ -2492,15 +2494,15 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>200.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4980</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="12">
@@ -2518,19 +2520,19 @@
         <v>148625</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2542,7 +2544,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="13">
@@ -2686,19 +2688,19 @@
         <v>171500</v>
       </c>
       <c r="D16" t="n">
-        <v>19960</v>
+        <v>24940</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2710,7 +2712,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19960</v>
+        <v>24940</v>
       </c>
     </row>
     <row r="17">
@@ -2728,19 +2730,19 @@
         <v>175475</v>
       </c>
       <c r="D17" t="n">
-        <v>58696</v>
+        <v>84074</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2748,11 +2750,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>54131</v>
+        <v>79509</v>
       </c>
     </row>
     <row r="18">
@@ -2770,19 +2772,19 @@
         <v>178625</v>
       </c>
       <c r="D18" t="n">
-        <v>24416</v>
+        <v>25696</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2794,7 +2796,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>24416</v>
+        <v>25696</v>
       </c>
     </row>
     <row r="19">
@@ -2812,19 +2814,19 @@
         <v>178900</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2832,11 +2834,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>200.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-10000</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="20">
@@ -2854,19 +2856,19 @@
         <v>108625</v>
       </c>
       <c r="D20" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2874,11 +2876,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5533.33</v>
+        <v>10513.33</v>
       </c>
     </row>
     <row r="21">
@@ -2896,19 +2898,19 @@
         <v>95750</v>
       </c>
       <c r="D21" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2916,11 +2918,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="22">
@@ -3038,15 +3040,15 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>26820</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>33420</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="25">
@@ -3064,31 +3066,31 @@
         <v>100737</v>
       </c>
       <c r="D25" t="n">
-        <v>24800</v>
+        <v>38000</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>24800</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="26">
@@ -3232,19 +3234,19 @@
         <v>80000</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3256,7 +3258,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="30">
@@ -3316,19 +3318,19 @@
         <v>80000</v>
       </c>
       <c r="D31" t="n">
-        <v>13690</v>
+        <v>24088</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3336,11 +3338,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>9690</v>
+        <v>20088</v>
       </c>
     </row>
     <row r="32">
@@ -3400,19 +3402,19 @@
         <v>80000</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3424,7 +3426,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="34">
@@ -3624,11 +3626,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>3774</v>
+        <v>41370</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3640,7 +3642,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3774</v>
+        <v>41370</v>
       </c>
     </row>
     <row r="3">
@@ -3658,11 +3660,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>93776</v>
+        <v>271308</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3670,11 +3672,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>34976</v>
+        <v>212508</v>
       </c>
     </row>
     <row r="4">
@@ -3692,11 +3694,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>2694</v>
+        <v>73668</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3708,7 +3710,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2694</v>
+        <v>73668</v>
       </c>
     </row>
     <row r="5">
@@ -3726,11 +3728,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>698</v>
+        <v>60698</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3742,7 +3744,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>698</v>
+        <v>60698</v>
       </c>
     </row>
     <row r="6">
@@ -3760,23 +3762,23 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>17596</v>
+        <v>28392</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>17596</v>
+        <v>26792</v>
       </c>
     </row>
     <row r="7">
@@ -3828,11 +3830,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>32694</v>
+        <v>33490</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3844,7 +3846,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>32694</v>
+        <v>33490</v>
       </c>
     </row>
     <row r="9">
@@ -3896,11 +3898,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>398</v>
+        <v>1194</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3912,7 +3914,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>398</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="11">
@@ -3964,11 +3966,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>6194</v>
+        <v>6592</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3980,7 +3982,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6194</v>
+        <v>6592</v>
       </c>
     </row>
     <row r="13">
@@ -3998,11 +4000,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>-48594.33000000002</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4010,11 +4012,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-48594.33000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4066,11 +4068,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>49866</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4082,7 +4084,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>49866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4100,11 +4102,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>29394</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4116,7 +4118,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>29394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4134,11 +4136,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>64963.61</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4150,7 +4152,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>64963.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4168,11 +4170,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>2090</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4184,7 +4186,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2090</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4236,11 +4238,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>85298.64</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4252,7 +4254,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>85298.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4270,11 +4272,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>50606</v>
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4286,7 +4288,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>50606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -4304,11 +4306,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>36056</v>
+        <v>20398</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4320,7 +4322,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>36056</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="23">
@@ -4338,11 +4340,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>32782.32</v>
+        <v>33180.32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4354,7 +4356,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>32782.32</v>
+        <v>33180.32</v>
       </c>
     </row>
     <row r="24">
@@ -4372,23 +4374,23 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>25021.88</v>
+        <v>45419.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>25021.88</v>
+        <v>44623.88</v>
       </c>
     </row>
     <row r="25">
@@ -4406,23 +4408,23 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>2794</v>
+        <v>3790</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>263.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2794</v>
+        <v>-6210</v>
       </c>
     </row>
     <row r="26">
@@ -4440,11 +4442,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4456,7 +4458,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27">
@@ -4508,11 +4510,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4524,7 +4526,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
     </row>
     <row r="29">
@@ -4542,11 +4544,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>53977.6</v>
+        <v>64756.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4558,7 +4560,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>53977.6</v>
+        <v>64756.2</v>
       </c>
     </row>
     <row r="30">
@@ -4580,19 +4582,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7000</v>
+        <v>14500</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>188.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>700</v>
+        <v>-6800</v>
       </c>
     </row>
     <row r="31">
@@ -4610,11 +4612,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>18698</v>
+        <v>49696</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4622,11 +4624,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9198</v>
+        <v>40196</v>
       </c>
     </row>
     <row r="32">
@@ -4644,11 +4646,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>20498</v>
+        <v>30498</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4660,7 +4662,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>20498</v>
+        <v>30498</v>
       </c>
     </row>
     <row r="33">
@@ -4712,11 +4714,11 @@
         <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -4728,7 +4730,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="35">
@@ -4746,11 +4748,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>24592.8</v>
+        <v>28864</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4758,11 +4760,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-9007.200000000001</v>
+        <v>-4736</v>
       </c>
     </row>
     <row r="36">
@@ -4780,11 +4782,11 @@
         <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>495.3</v>
+        <v>2278.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4796,7 +4798,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>495.3</v>
+        <v>2278.9</v>
       </c>
     </row>
     <row r="37">
@@ -4984,23 +4986,23 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7083.33</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>590.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-5883.33</v>
       </c>
     </row>
     <row r="43">
@@ -5120,11 +5122,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>33394</v>
+        <v>43792</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5136,7 +5138,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>33394</v>
+        <v>43792</v>
       </c>
     </row>
     <row r="47">
@@ -5154,11 +5156,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>12596</v>
+        <v>53790</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5166,11 +5168,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3396</v>
+        <v>44590</v>
       </c>
     </row>
     <row r="48">
@@ -5188,11 +5190,11 @@
         <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>8398</v>
+        <v>52398</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5204,7 +5206,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8398</v>
+        <v>52398</v>
       </c>
     </row>
     <row r="49">
@@ -5222,11 +5224,11 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5238,7 +5240,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50">
@@ -5256,11 +5258,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>15668.15</v>
+        <v>23668.15</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5272,7 +5274,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>15668.15</v>
+        <v>23668.15</v>
       </c>
     </row>
     <row r="51">
@@ -5290,23 +5292,23 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>32211.24</v>
+        <v>33364.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>8000</v>
+        <v>11600</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>24211.24</v>
+        <v>21764.8</v>
       </c>
     </row>
     <row r="52">
@@ -5324,11 +5326,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>533.8199999999999</v>
+        <v>46836.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5340,7 +5342,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>533.8199999999999</v>
+        <v>46836.3</v>
       </c>
     </row>
     <row r="53">
@@ -5358,11 +5360,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>28800</v>
+        <v>29198</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5374,7 +5376,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28800</v>
+        <v>29198</v>
       </c>
     </row>
     <row r="54">
@@ -5392,11 +5394,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>8572.700000000001</v>
+        <v>10972.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5408,7 +5410,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8572.700000000001</v>
+        <v>10972.7</v>
       </c>
     </row>
     <row r="55">
@@ -5426,11 +5428,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>20700</v>
+        <v>21500</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5442,7 +5444,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>20700</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="56">
@@ -5494,11 +5496,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>1194</v>
+        <v>11194</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5510,7 +5512,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1194</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="58">
@@ -5528,11 +5530,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>20398</v>
+        <v>30398</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5544,7 +5546,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>20398</v>
+        <v>30398</v>
       </c>
     </row>
     <row r="59">
@@ -5562,11 +5564,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>65600</v>
+        <v>65998</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5578,7 +5580,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>65600</v>
+        <v>65998</v>
       </c>
     </row>
     <row r="60">
@@ -5596,11 +5598,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>796</v>
+        <v>38396</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -5612,7 +5614,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>796</v>
+        <v>38396</v>
       </c>
     </row>
     <row r="61">
@@ -5698,23 +5700,23 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>42792</v>
+        <v>43190</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>42792</v>
+        <v>39790</v>
       </c>
     </row>
     <row r="64">
@@ -5877,16 +5879,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>390289</v>
+        <v>488348.57</v>
       </c>
       <c r="D2" t="n">
-        <v>1550</v>
+        <v>1955</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>390289</v>
+        <v>488348.57</v>
       </c>
     </row>
     <row r="3">
@@ -5901,16 +5903,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>334891</v>
+        <v>421051</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>334891</v>
+        <v>421051</v>
       </c>
     </row>
     <row r="4">
@@ -5925,16 +5927,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55398</v>
+        <v>67297.57000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1484</v>
+        <v>1873</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>55398</v>
+        <v>67297.57000000001</v>
       </c>
     </row>
     <row r="5">
@@ -5949,16 +5951,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>881376</v>
+        <v>1503890</v>
       </c>
       <c r="D5" t="n">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>881376</v>
+        <v>1503890</v>
       </c>
     </row>
     <row r="6">
@@ -5973,16 +5975,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>538164</v>
+        <v>974626</v>
       </c>
       <c r="D6" t="n">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>538164</v>
+        <v>974626</v>
       </c>
     </row>
     <row r="7">
@@ -5997,16 +5999,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>332814</v>
+        <v>498866</v>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>332814</v>
+        <v>498866</v>
       </c>
     </row>
     <row r="8">
@@ -6021,16 +6023,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>378795.56</v>
+        <v>675688.11</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>775</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>378795.56</v>
+        <v>675688.11</v>
       </c>
     </row>
     <row r="9">
@@ -6041,20 +6043,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>198804.33</v>
+        <v>71337.03</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>86</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>198804.33</v>
+        <v>71337.03</v>
       </c>
     </row>
     <row r="10">
@@ -6065,20 +6067,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>179991.23</v>
+        <v>55105.91</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>179991.23</v>
+        <v>55105.91</v>
       </c>
     </row>
     <row r="11">
@@ -6093,16 +6095,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>120000</v>
+        <v>144800</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>120000</v>
+        <v>144800</v>
       </c>
     </row>
     <row r="12">
@@ -6117,16 +6119,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="13">
@@ -6165,16 +6167,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1980</v>
+        <v>9900</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1980</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="15">
@@ -6189,16 +6191,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8771.360000000001</v>
+        <v>110467.86</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>8771.360000000001</v>
+        <v>110467.86</v>
       </c>
     </row>
   </sheetData>
@@ -6259,22 +6261,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>390289</v>
+        <v>488348.57</v>
       </c>
       <c r="C2" t="n">
-        <v>67667.03999999999</v>
+        <v>74561.03999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>3611</v>
+        <v>6666</v>
       </c>
       <c r="E2" t="n">
-        <v>0.93</v>
+        <v>1.37</v>
       </c>
       <c r="F2" t="n">
-        <v>64056.04</v>
+        <v>67895.03999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>16.41</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="3">
@@ -6284,10 +6286,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>881376</v>
+        <v>1503890</v>
       </c>
       <c r="C3" t="n">
-        <v>98600</v>
+        <v>228103.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6296,10 +6298,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>98600</v>
+        <v>228103.33</v>
       </c>
       <c r="G3" t="n">
-        <v>11.19</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="4">
@@ -6309,7 +6311,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>378795.56</v>
+        <v>675688.11</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -6334,10 +6336,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120000</v>
+        <v>144800</v>
       </c>
       <c r="C5" t="n">
-        <v>91200</v>
+        <v>92200</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6346,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>91200</v>
+        <v>92200</v>
       </c>
       <c r="G5" t="n">
-        <v>76</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="6">
@@ -6359,10 +6361,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>27354</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -6371,10 +6373,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>27354</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -6387,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>87380</v>
+        <v>97180</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6396,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>87380</v>
+        <v>97180</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -6409,7 +6411,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1980</v>
+        <v>9900</v>
       </c>
       <c r="C8" t="n">
         <v>1980</v>
@@ -6424,7 +6426,7 @@
         <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -6434,10 +6436,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8771.360000000001</v>
+        <v>110467.86</v>
       </c>
       <c r="C9" t="n">
-        <v>3900</v>
+        <v>4696</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6446,10 +6448,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3900</v>
+        <v>4696</v>
       </c>
       <c r="G9" t="n">
-        <v>44.46</v>
+        <v>4.25</v>
       </c>
     </row>
   </sheetData>
@@ -6495,13 +6497,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>171210.37</v>
+        <v>286801.7</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -6511,10 +6513,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>107379</v>
+        <v>107777</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
@@ -6523,14 +6525,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>24491.67</v>
+        <v>46280</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -6543,29 +6545,29 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>21200</v>
+        <v>42200</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="C6" t="n">
-        <v>16808</v>
+        <v>26480.67</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -6591,42 +6593,42 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>412</v>
+        <v>3709</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>3619</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6659,7 +6661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6710,14 +6712,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>3983</v>
+        <v>22116.67</v>
       </c>
     </row>
     <row r="4">
@@ -6728,14 +6730,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3484.67</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="5">
@@ -6768,10 +6770,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>669</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -6804,10 +6806,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -6831,7 +6833,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6843,180 +6845,180 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>58809</v>
+        <v>50600</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>27354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>16337.7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11713</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>7319</v>
+        <v>63600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4979</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3490</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>58809</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -7029,7 +7031,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7038,136 +7040,136 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>33600</v>
+        <v>18054.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="D22" t="n">
-        <v>7200</v>
+        <v>12135</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>1980</v>
+        <v>7319</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13971</v>
+        <v>4979</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>10053.67</v>
+        <v>3865</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>10000</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1116</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>365</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
@@ -7178,56 +7180,56 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="D29" t="n">
-        <v>76</v>
+        <v>14212</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D30" t="n">
-        <v>10000</v>
+        <v>10477.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>8500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7236,118 +7238,118 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D32" t="n">
-        <v>7000</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>13980</v>
+        <v>384</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>4000</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>38</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1200</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="39">
@@ -7371,25 +7373,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>6500</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7398,28 +7400,136 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>19</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>7083.33</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3419</v>
       </c>
     </row>
   </sheetData>
@@ -7456,27 +7566,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>分享咨询</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>91200</v>
+        <v>179183.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>分享咨询</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>86500</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="4">
@@ -7495,92 +7605,92 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46800</v>
+        <v>48400</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>38600</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>12100</v>
+        <v>27354</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>认知9周+年卡</t>
+          <t>家庭守护计划</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3900</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>202</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>3528</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>观心少年（线下体验课）</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="C10" t="n">
-        <v>1980</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>认知9周+年卡</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1980</v>
+        <v>3900</v>
       </c>
     </row>
   </sheetData>
@@ -7617,27 +7727,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="C2" t="n">
-        <v>92590</v>
+        <v>146606.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>80056</v>
+        <v>92946</v>
       </c>
     </row>
     <row r="4">
@@ -7647,166 +7757,166 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>59189</v>
+        <v>62202</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>14695.7</v>
+        <v>54489</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>13418</v>
+        <v>35693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>13074</v>
+        <v>22359.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>10152</v>
+        <v>13465</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>9225.67</v>
+        <v>13135.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>9190.67</v>
+        <v>10880</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>9047</v>
+        <v>10256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>7983</v>
+        <v>9913</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>7036</v>
+        <v>9263.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>6548</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>5019</v>
+        <v>7074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>4202</v>
+        <v>6567</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1400000</v>
+        <v>1450000</v>
       </c>
       <c r="D2" t="n">
         <v>242888</v>
@@ -541,12 +541,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>800000</v>
+        <v>1030000</v>
       </c>
       <c r="D10" t="n">
         <v>51229</v>
@@ -993,12 +993,12 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>700000</v>
+        <v>1600000</v>
       </c>
       <c r="D13" t="n">
         <v>87201</v>
@@ -1170,12 +1170,12 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14090000</v>
+        <v>15270000</v>
       </c>
       <c r="D18" t="n">
         <v>2964140</v>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>191500</v>
+        <v>312912</v>
       </c>
       <c r="D2" t="n">
         <v>74994</v>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>185200</v>
+        <v>302618</v>
       </c>
       <c r="D3" t="n">
         <v>6260</v>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>165200</v>
+        <v>269938</v>
       </c>
       <c r="D4" t="n">
         <v>34860</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>98625</v>
+        <v>161154</v>
       </c>
       <c r="D5" t="n">
         <v>22000</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>98625</v>
+        <v>161154</v>
       </c>
       <c r="D6" t="n">
         <v>14940</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>148350</v>
+        <v>242405</v>
       </c>
       <c r="D7" t="n">
         <v>4681</v>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>115750</v>
+        <v>189136</v>
       </c>
       <c r="D8" t="n">
         <v>4980</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>207250</v>
+        <v>333616</v>
       </c>
       <c r="D9" t="n">
         <v>32976</v>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>168625</v>
+        <v>271440</v>
       </c>
       <c r="D10" t="n">
         <v>4980</v>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>168625</v>
+        <v>271440</v>
       </c>
       <c r="D11" t="n">
         <v>4980</v>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>148625</v>
+        <v>239246</v>
       </c>
       <c r="D12" t="n">
         <v>9960</v>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>141500</v>
+        <v>227777</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>128625</v>
+        <v>207051</v>
       </c>
       <c r="D14" t="n">
         <v>9960</v>
@@ -2611,12 +2611,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>91500</v>
+        <v>147291</v>
       </c>
       <c r="D15" t="n">
         <v>6600</v>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>171500</v>
+        <v>279050</v>
       </c>
       <c r="D16" t="n">
         <v>24940</v>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>175475</v>
+        <v>285517</v>
       </c>
       <c r="D17" t="n">
         <v>84074</v>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>178625</v>
+        <v>290643</v>
       </c>
       <c r="D18" t="n">
         <v>25696</v>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>178900</v>
+        <v>291091</v>
       </c>
       <c r="D19" t="n">
         <v>4980</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>108625</v>
+        <v>176745</v>
       </c>
       <c r="D20" t="n">
         <v>14940</v>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>95750</v>
+        <v>155796</v>
       </c>
       <c r="D21" t="n">
         <v>9960</v>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>98625</v>
+        <v>160474</v>
       </c>
       <c r="D22" t="n">
         <v>14940</v>
@@ -2947,12 +2947,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>207895</v>
+        <v>265322</v>
       </c>
       <c r="D23" t="n">
         <v>36178</v>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>104842</v>
+        <v>133802</v>
       </c>
       <c r="D24" t="n">
         <v>33420</v>
@@ -3031,12 +3031,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>100737</v>
+        <v>128563</v>
       </c>
       <c r="D25" t="n">
         <v>38000</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>154842</v>
+        <v>197614</v>
       </c>
       <c r="D26" t="n">
         <v>24000</v>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>150737</v>
+        <v>192375</v>
       </c>
       <c r="D27" t="n">
         <v>66400</v>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D29" t="n">
         <v>12000</v>
@@ -3241,12 +3241,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>108947</v>
+        <v>139041</v>
       </c>
       <c r="D30" t="n">
         <v>6600</v>
@@ -3283,12 +3283,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D31" t="n">
         <v>24088</v>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D32" t="n">
         <v>43800</v>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D33" t="n">
         <v>24800</v>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>80000</v>
+        <v>102098</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>80000</v>
+        <v>102103</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2000000</v>
+        <v>2500000</v>
       </c>
       <c r="D6" t="n">
         <v>590420</v>
@@ -751,12 +751,12 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>380000</v>
+        <v>500000</v>
       </c>
       <c r="D7" t="n">
         <v>57135</v>
@@ -812,12 +812,12 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="D8" t="n">
         <v>236801</v>
@@ -873,12 +873,12 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="D9" t="n">
         <v>193702</v>
@@ -930,12 +930,12 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1030000</v>
+        <v>1100000</v>
       </c>
       <c r="D10" t="n">
         <v>51229</v>
@@ -993,12 +993,12 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>260000</v>
+        <v>400000</v>
       </c>
       <c r="D11" t="n">
         <v>16952</v>
@@ -1056,12 +1056,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="D12" t="n">
         <v>150397</v>
@@ -1113,12 +1113,12 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1600000</v>
+        <v>1900000</v>
       </c>
       <c r="D13" t="n">
         <v>87201</v>
@@ -1170,12 +1170,12 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="D14" t="n">
         <v>478418</v>
@@ -1233,12 +1233,12 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1292,12 +1292,12 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>700000</v>
+        <v>900000</v>
       </c>
       <c r="D16" t="n">
         <v>41715</v>
@@ -1355,12 +1355,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15270000</v>
+        <v>17200000</v>
       </c>
       <c r="D18" t="n">
         <v>2964140</v>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>312912</v>
+        <v>3129120000</v>
       </c>
       <c r="D2" t="n">
         <v>74994</v>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>302618</v>
+        <v>3026180000</v>
       </c>
       <c r="D3" t="n">
         <v>6260</v>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>269938</v>
+        <v>2699380000</v>
       </c>
       <c r="D4" t="n">
         <v>34860</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>161154</v>
+        <v>1611540000</v>
       </c>
       <c r="D5" t="n">
         <v>22000</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>161154</v>
+        <v>1611540000</v>
       </c>
       <c r="D6" t="n">
         <v>14940</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>242405</v>
+        <v>2424050000</v>
       </c>
       <c r="D7" t="n">
         <v>4681</v>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>189136</v>
+        <v>1891360000</v>
       </c>
       <c r="D8" t="n">
         <v>4980</v>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>333616</v>
+        <v>3336160000</v>
       </c>
       <c r="D9" t="n">
         <v>32976</v>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>271440</v>
+        <v>2714400000</v>
       </c>
       <c r="D10" t="n">
         <v>4980</v>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>271440</v>
+        <v>2714400000</v>
       </c>
       <c r="D11" t="n">
         <v>4980</v>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>239246</v>
+        <v>2392460000</v>
       </c>
       <c r="D12" t="n">
         <v>9960</v>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>227777</v>
+        <v>2277770000</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>207051</v>
+        <v>2070510000</v>
       </c>
       <c r="D14" t="n">
         <v>9960</v>
@@ -2611,12 +2611,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>147291</v>
+        <v>1472910000</v>
       </c>
       <c r="D15" t="n">
         <v>6600</v>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>279050</v>
+        <v>2790500000</v>
       </c>
       <c r="D16" t="n">
         <v>24940</v>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>285517</v>
+        <v>2855170000</v>
       </c>
       <c r="D17" t="n">
         <v>84074</v>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>290643</v>
+        <v>2906430000</v>
       </c>
       <c r="D18" t="n">
         <v>25696</v>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>291091</v>
+        <v>2910910000</v>
       </c>
       <c r="D19" t="n">
         <v>4980</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>176745</v>
+        <v>1767450000</v>
       </c>
       <c r="D20" t="n">
         <v>14940</v>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>155796</v>
+        <v>1557960000</v>
       </c>
       <c r="D21" t="n">
         <v>9960</v>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>160474</v>
+        <v>1604740000</v>
       </c>
       <c r="D22" t="n">
         <v>14940</v>
@@ -2947,12 +2947,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>265322</v>
+        <v>2653220000</v>
       </c>
       <c r="D23" t="n">
         <v>36178</v>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>133802</v>
+        <v>1338020000</v>
       </c>
       <c r="D24" t="n">
         <v>33420</v>
@@ -3031,12 +3031,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>128563</v>
+        <v>1285630000</v>
       </c>
       <c r="D25" t="n">
         <v>38000</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>197614</v>
+        <v>1976140000</v>
       </c>
       <c r="D26" t="n">
         <v>24000</v>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>192375</v>
+        <v>1923750000</v>
       </c>
       <c r="D27" t="n">
         <v>66400</v>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D29" t="n">
         <v>12000</v>
@@ -3241,12 +3241,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>139041</v>
+        <v>1390410000</v>
       </c>
       <c r="D30" t="n">
         <v>6600</v>
@@ -3283,12 +3283,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D31" t="n">
         <v>24088</v>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D32" t="n">
         <v>43800</v>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D33" t="n">
         <v>24800</v>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>102098</v>
+        <v>1020980000</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>102103</v>
+        <v>1021030000</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F63" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1389,12 +1389,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>望京</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1404,29 +1404,33 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-22514</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>-71.1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1438,65 +1442,114 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-6500</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>-22514</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-71.1%</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>-6500</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>南区合计</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>17200000</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="C19" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="D19" t="n">
         <v>2964140</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>526074</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>2438066</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>647841</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>+357.5%</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>-181067</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>-1446.5%</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>84957</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>747432</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>1605675</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>1192675</v>
       </c>
     </row>
@@ -1590,7 +1643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1985,11 +2038,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>望京</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2001,21 +2054,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-6500</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>南区合计</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>747432</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>1605675</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>1192675</v>
       </c>
     </row>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -528,25 +528,25 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>242888</v>
+        <v>283217</v>
       </c>
       <c r="E2" t="n">
-        <v>49678</v>
+        <v>50850</v>
       </c>
       <c r="F2" t="n">
-        <v>193210</v>
+        <v>232366</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,11 +554,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-96249</v>
+        <v>-97838</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-300.7%</t>
+          <t>-337.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -581,25 +581,25 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>91391</v>
+        <v>112657</v>
       </c>
       <c r="E3" t="n">
-        <v>121124</v>
+        <v>131545</v>
       </c>
       <c r="F3" t="n">
-        <v>-29733</v>
+        <v>-18888</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -607,11 +607,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-106834</v>
+        <v>-107062</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-82.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -634,25 +634,25 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>242602</v>
+        <v>309517</v>
       </c>
       <c r="E4" t="n">
-        <v>36361</v>
+        <v>46895</v>
       </c>
       <c r="F4" t="n">
-        <v>206241</v>
+        <v>262622</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -660,11 +660,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-96137</v>
+        <v>-96327</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-314.5%</t>
+          <t>-372.6%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -687,25 +687,25 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>316457</v>
+        <v>358903</v>
       </c>
       <c r="E5" t="n">
-        <v>84030</v>
+        <v>152664</v>
       </c>
       <c r="F5" t="n">
-        <v>232427</v>
+        <v>206239</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-293447</v>
+        <v>-293485</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-179.2%</t>
+          <t>-170.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -740,50 +740,50 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>590420</v>
+        <v>596300</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>36800</v>
       </c>
       <c r="F6" t="n">
-        <v>590420</v>
+        <v>559500</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>608284</v>
+        <v>712622</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>608284</v>
+        <v>712622</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>30417</v>
+        <v>208473</v>
       </c>
       <c r="P6" t="n">
-        <v>560003</v>
+        <v>351027</v>
       </c>
       <c r="Q6" t="n">
-        <v>549624</v>
+        <v>518704</v>
       </c>
     </row>
     <row r="7">
@@ -862,23 +862,23 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>236801</v>
+        <v>257597</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F8" t="n">
-        <v>236801</v>
+        <v>256597</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -890,18 +890,18 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-1128.3%</t>
+          <t>-1214.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>29007</v>
+        <v>29405</v>
       </c>
       <c r="P8" t="n">
-        <v>207794</v>
+        <v>227192</v>
       </c>
       <c r="Q8" t="n">
-        <v>52219</v>
+        <v>52419</v>
       </c>
     </row>
     <row r="9">
@@ -919,23 +919,23 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>193702</v>
+        <v>205081</v>
       </c>
       <c r="E9" t="n">
         <v>33000</v>
       </c>
       <c r="F9" t="n">
-        <v>160702</v>
+        <v>172081</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -943,28 +943,28 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+2337.7%</t>
+          <t>+2480.9%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-17982</v>
+        <v>-18001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-993.7%</t>
+          <t>-1056.0%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6844</v>
+        <v>6927</v>
       </c>
       <c r="O9" t="n">
-        <v>31425</v>
+        <v>42322</v>
       </c>
       <c r="P9" t="n">
-        <v>122433</v>
+        <v>122831</v>
       </c>
       <c r="Q9" t="n">
-        <v>15616</v>
+        <v>16199</v>
       </c>
     </row>
     <row r="10">
@@ -982,39 +982,39 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>51229</v>
+        <v>62025</v>
       </c>
       <c r="E10" t="n">
-        <v>73809</v>
+        <v>75789</v>
       </c>
       <c r="F10" t="n">
-        <v>-22580</v>
+        <v>-13764</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7715</v>
+        <v>9842</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+564.0%</t>
+          <t>+530.2%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-7151</v>
+        <v>-5024</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+215.8%</t>
+          <t>+174.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1024,10 +1024,10 @@
         <v>-35527</v>
       </c>
       <c r="P10" t="n">
-        <v>6592</v>
+        <v>15408</v>
       </c>
       <c r="Q10" t="n">
-        <v>-30168</v>
+        <v>-32148</v>
       </c>
     </row>
     <row r="11">
@@ -1045,23 +1045,23 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>16952</v>
+        <v>18651</v>
       </c>
       <c r="E11" t="n">
-        <v>7102</v>
+        <v>7121</v>
       </c>
       <c r="F11" t="n">
-        <v>9850</v>
+        <v>11530</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-162.1%</t>
+          <t>-172.7%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         <v>-7026</v>
       </c>
       <c r="P11" t="n">
-        <v>16876</v>
+        <v>18556</v>
       </c>
       <c r="Q11" t="n">
-        <v>1737</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="12">
@@ -1102,23 +1102,23 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>150397</v>
+        <v>220245</v>
       </c>
       <c r="E12" t="n">
-        <v>9200</v>
+        <v>9219</v>
       </c>
       <c r="F12" t="n">
-        <v>141197</v>
+        <v>211026</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1130,18 +1130,18 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-33960.2%</t>
+          <t>-50705.8%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>7807</v>
+        <v>52636</v>
       </c>
       <c r="P12" t="n">
-        <v>133390</v>
+        <v>158390</v>
       </c>
       <c r="Q12" t="n">
-        <v>26619</v>
+        <v>91448</v>
       </c>
     </row>
     <row r="13">
@@ -1159,52 +1159,52 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>87201</v>
+        <v>105001</v>
       </c>
       <c r="E13" t="n">
         <v>10796</v>
       </c>
       <c r="F13" t="n">
-        <v>76405</v>
+        <v>94205</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18732</v>
+        <v>18982</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+365.5%</t>
+          <t>+453.2%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-27868</v>
+        <v>-27618</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-374.2%</t>
+          <t>-441.1%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>12318</v>
       </c>
       <c r="O13" t="n">
-        <v>14201</v>
+        <v>13603</v>
       </c>
       <c r="P13" t="n">
-        <v>49886</v>
+        <v>68284</v>
       </c>
       <c r="Q13" t="n">
-        <v>18141</v>
+        <v>24741</v>
       </c>
     </row>
     <row r="14">
@@ -1222,23 +1222,23 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>478418</v>
+        <v>529417</v>
       </c>
       <c r="E14" t="n">
         <v>60447</v>
       </c>
       <c r="F14" t="n">
-        <v>417971</v>
+        <v>468970</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1250,20 +1250,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-2226.3%</t>
+          <t>-2485.8%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>21200</v>
       </c>
       <c r="O14" t="n">
-        <v>57129</v>
+        <v>77728</v>
       </c>
       <c r="P14" t="n">
-        <v>339642</v>
+        <v>370042</v>
       </c>
       <c r="Q14" t="n">
-        <v>105195</v>
+        <v>166594</v>
       </c>
     </row>
     <row r="15">
@@ -1281,52 +1281,52 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>166831</v>
+        <v>174531</v>
       </c>
       <c r="E15" t="n">
-        <v>30609</v>
+        <v>33609</v>
       </c>
       <c r="F15" t="n">
-        <v>136222</v>
+        <v>140922</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4953</v>
+        <v>6368</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+3268.3%</t>
+          <t>+2640.8%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4744</v>
+        <v>6159</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+2771.5%</t>
+          <t>+2188.1%</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>38240</v>
+        <v>38440</v>
       </c>
       <c r="O15" t="n">
         <v>31586</v>
       </c>
       <c r="P15" t="n">
-        <v>66396</v>
+        <v>70896</v>
       </c>
       <c r="Q15" t="n">
-        <v>38240</v>
+        <v>38440</v>
       </c>
     </row>
     <row r="16">
@@ -1344,23 +1344,23 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>41715</v>
+        <v>48671</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="F16" t="n">
-        <v>41715</v>
+        <v>48073</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1372,18 +1372,18 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-202.3%</t>
+          <t>-217.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>12429</v>
+        <v>19366</v>
       </c>
       <c r="P16" t="n">
-        <v>29286</v>
+        <v>28707</v>
       </c>
       <c r="Q16" t="n">
-        <v>439</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="17">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>-22514</v>
+        <v>-22533</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1503,54 +1503,54 @@
         <v>18500000</v>
       </c>
       <c r="D19" t="n">
-        <v>2964140</v>
+        <v>3338948</v>
       </c>
       <c r="E19" t="n">
-        <v>526074</v>
+        <v>660252</v>
       </c>
       <c r="F19" t="n">
-        <v>2438066</v>
+        <v>2678696</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>647841</v>
+        <v>755972</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+357.5%</t>
+          <t>+341.7%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-181067</v>
+        <v>-75019</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-1446.5%</t>
+          <t>-3670.7%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>84957</v>
+        <v>85240</v>
       </c>
       <c r="O19" t="n">
-        <v>747432</v>
+        <v>1090424</v>
       </c>
       <c r="P19" t="n">
-        <v>1605675</v>
+        <v>1503030</v>
       </c>
       <c r="Q19" t="n">
-        <v>1192675</v>
+        <v>1374240</v>
       </c>
     </row>
   </sheetData>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>536582</v>
+        <v>618456</v>
       </c>
       <c r="D2" t="n">
-        <v>65563</v>
+        <v>63883</v>
       </c>
       <c r="E2" t="n">
-        <v>396678</v>
+        <v>468696</v>
       </c>
     </row>
     <row r="3">
@@ -1706,13 +1706,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>217350</v>
+        <v>478468</v>
       </c>
       <c r="D3" t="n">
-        <v>1540111</v>
+        <v>1439145</v>
       </c>
       <c r="E3" t="n">
-        <v>795998</v>
+        <v>905544</v>
       </c>
     </row>
     <row r="4">
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>176383</v>
+        <v>215539</v>
       </c>
       <c r="D4" t="n">
         <v>16827</v>
       </c>
       <c r="E4" t="n">
-        <v>140222</v>
+        <v>178382</v>
       </c>
     </row>
     <row r="5">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-30051</v>
+        <v>-19506</v>
       </c>
       <c r="D5" t="n">
-        <v>318</v>
+        <v>618</v>
       </c>
       <c r="E5" t="n">
-        <v>-12627</v>
+        <v>-1782</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>196222</v>
+        <v>252603</v>
       </c>
       <c r="D6" t="n">
         <v>10019</v>
       </c>
       <c r="E6" t="n">
-        <v>146451</v>
+        <v>202832</v>
       </c>
     </row>
     <row r="7">
@@ -1790,13 +1790,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>194027</v>
+        <v>169819</v>
       </c>
       <c r="D7" t="n">
-        <v>38400</v>
+        <v>36420</v>
       </c>
       <c r="E7" t="n">
-        <v>122631</v>
+        <v>89263</v>
       </c>
     </row>
     <row r="8">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30417</v>
+        <v>208473</v>
       </c>
       <c r="D8" t="n">
-        <v>560003</v>
+        <v>351027</v>
       </c>
       <c r="E8" t="n">
-        <v>549624</v>
+        <v>518704</v>
       </c>
     </row>
     <row r="9">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29007</v>
+        <v>29405</v>
       </c>
       <c r="D10" t="n">
-        <v>207794</v>
+        <v>227192</v>
       </c>
       <c r="E10" t="n">
-        <v>52219</v>
+        <v>52419</v>
       </c>
     </row>
     <row r="11">
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31425</v>
+        <v>42322</v>
       </c>
       <c r="D11" t="n">
-        <v>122433</v>
+        <v>122831</v>
       </c>
       <c r="E11" t="n">
-        <v>15616</v>
+        <v>16199</v>
       </c>
     </row>
     <row r="12">
@@ -1898,10 +1898,10 @@
         <v>-35527</v>
       </c>
       <c r="D12" t="n">
-        <v>6592</v>
+        <v>15408</v>
       </c>
       <c r="E12" t="n">
-        <v>-30168</v>
+        <v>-32148</v>
       </c>
     </row>
     <row r="13">
@@ -1919,10 +1919,10 @@
         <v>-7026</v>
       </c>
       <c r="D13" t="n">
-        <v>16876</v>
+        <v>18556</v>
       </c>
       <c r="E13" t="n">
-        <v>1737</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="14">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7807</v>
+        <v>52636</v>
       </c>
       <c r="D14" t="n">
-        <v>133390</v>
+        <v>158390</v>
       </c>
       <c r="E14" t="n">
-        <v>26619</v>
+        <v>91448</v>
       </c>
     </row>
     <row r="15">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14201</v>
+        <v>13603</v>
       </c>
       <c r="D15" t="n">
-        <v>49886</v>
+        <v>68284</v>
       </c>
       <c r="E15" t="n">
-        <v>18141</v>
+        <v>24741</v>
       </c>
     </row>
     <row r="16">
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>57129</v>
+        <v>77728</v>
       </c>
       <c r="D16" t="n">
-        <v>339642</v>
+        <v>370042</v>
       </c>
       <c r="E16" t="n">
-        <v>105195</v>
+        <v>166594</v>
       </c>
     </row>
     <row r="17">
@@ -2003,10 +2003,10 @@
         <v>31586</v>
       </c>
       <c r="D17" t="n">
-        <v>66396</v>
+        <v>70896</v>
       </c>
       <c r="E17" t="n">
-        <v>38240</v>
+        <v>38440</v>
       </c>
     </row>
     <row r="18">
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12429</v>
+        <v>19366</v>
       </c>
       <c r="D18" t="n">
-        <v>29286</v>
+        <v>28707</v>
       </c>
       <c r="E18" t="n">
-        <v>439</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="19">
@@ -2084,13 +2084,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>747432</v>
+        <v>1090424</v>
       </c>
       <c r="D21" t="n">
-        <v>1605675</v>
+        <v>1503030</v>
       </c>
       <c r="E21" t="n">
-        <v>1192675</v>
+        <v>1374240</v>
       </c>
     </row>
   </sheetData>
@@ -2174,7 +2174,7 @@
         <v>3129120000</v>
       </c>
       <c r="D2" t="n">
-        <v>74994</v>
+        <v>84954</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2194,11 +2194,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>65217.3</v>
+        <v>75177.3</v>
       </c>
     </row>
     <row r="3">
@@ -2342,7 +2342,7 @@
         <v>1611540000</v>
       </c>
       <c r="D6" t="n">
-        <v>14940</v>
+        <v>21200</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2362,11 +2362,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9260</v>
+        <v>15520</v>
       </c>
     </row>
     <row r="7">
@@ -2468,7 +2468,7 @@
         <v>3336160000</v>
       </c>
       <c r="D9" t="n">
-        <v>32976</v>
+        <v>42936</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2484,15 +2484,15 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>48916.67</v>
+        <v>53896.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>148.3%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-15940.67</v>
+        <v>-10960.67</v>
       </c>
     </row>
     <row r="10">
@@ -2510,7 +2510,7 @@
         <v>2714400000</v>
       </c>
       <c r="D10" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2552,7 +2552,7 @@
         <v>2714400000</v>
       </c>
       <c r="D11" t="n">
-        <v>4980</v>
+        <v>10160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2572,11 +2572,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200.8%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-5020</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -2594,7 +2594,7 @@
         <v>2392460000</v>
       </c>
       <c r="D12" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="13">
@@ -2678,7 +2678,7 @@
         <v>2070510000</v>
       </c>
       <c r="D14" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2694,11 +2694,11 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>50783</v>
+        <v>55763</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>509.9%</t>
+          <t>373.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2762,7 +2762,7 @@
         <v>2790500000</v>
       </c>
       <c r="D16" t="n">
-        <v>24940</v>
+        <v>34900</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24940</v>
+        <v>34900</v>
       </c>
     </row>
     <row r="17">
@@ -2804,7 +2804,7 @@
         <v>2855170000</v>
       </c>
       <c r="D17" t="n">
-        <v>84074</v>
+        <v>89054</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2824,11 +2824,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>79509</v>
+        <v>84489</v>
       </c>
     </row>
     <row r="18">
@@ -2904,15 +2904,15 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>10000</v>
+        <v>14980</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>200.8%</t>
+          <t>300.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-5020</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="20">
@@ -2930,7 +2930,7 @@
         <v>1767450000</v>
       </c>
       <c r="D20" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2950,11 +2950,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10513.33</v>
+        <v>15493.33</v>
       </c>
     </row>
     <row r="21">
@@ -2972,7 +2972,7 @@
         <v>1557960000</v>
       </c>
       <c r="D21" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2992,11 +2992,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="22">
@@ -3014,7 +3014,7 @@
         <v>1604740000</v>
       </c>
       <c r="D22" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -3030,11 +3030,11 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5000</v>
+        <v>9980</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -3072,15 +3072,15 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>31198</v>
+        <v>26218</v>
       </c>
     </row>
     <row r="24">
@@ -3140,7 +3140,7 @@
         <v>1285630000</v>
       </c>
       <c r="D25" t="n">
-        <v>38000</v>
+        <v>44600</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -3156,15 +3156,15 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2000</v>
+        <v>18800</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>36000</v>
+        <v>25800</v>
       </c>
     </row>
     <row r="26">
@@ -3266,7 +3266,7 @@
         <v>1020980000</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="29">
@@ -3350,7 +3350,7 @@
         <v>1390410000</v>
       </c>
       <c r="D30" t="n">
-        <v>6600</v>
+        <v>25200</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>6600</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="31">
@@ -3476,7 +3476,7 @@
         <v>1020980000</v>
       </c>
       <c r="D33" t="n">
-        <v>24800</v>
+        <v>34800</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>24800</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="34">
@@ -3700,11 +3700,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>41370</v>
+        <v>61370</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41370</v>
+        <v>61370</v>
       </c>
     </row>
     <row r="3">
@@ -3734,11 +3734,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>271308</v>
+        <v>281908</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3746,11 +3746,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>212508</v>
+        <v>223108</v>
       </c>
     </row>
     <row r="4">
@@ -3768,11 +3768,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>73668</v>
+        <v>93468</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73668</v>
+        <v>93468</v>
       </c>
     </row>
     <row r="5">
@@ -3904,11 +3904,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>33490</v>
+        <v>40090</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>33490</v>
+        <v>40090</v>
       </c>
     </row>
     <row r="9">
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-598</v>
       </c>
     </row>
     <row r="10">
@@ -4074,11 +4074,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>22279.66999999998</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>22279.66999999998</v>
       </c>
     </row>
     <row r="14">
@@ -4108,11 +4108,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>20398</v>
+        <v>42671.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20398</v>
+        <v>42671.55</v>
       </c>
     </row>
     <row r="15">
@@ -4142,11 +4142,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>75946</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>75946</v>
       </c>
     </row>
     <row r="16">
@@ -4176,11 +4176,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>63906.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>63906.2</v>
       </c>
     </row>
     <row r="17">
@@ -4210,11 +4210,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>112331.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>112331.61</v>
       </c>
     </row>
     <row r="18">
@@ -4244,11 +4244,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2090</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="19">
@@ -4278,11 +4278,11 @@
         <v>90000</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20">
@@ -4312,11 +4312,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>128100.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>128100.6</v>
       </c>
     </row>
     <row r="21">
@@ -4346,11 +4346,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>64606</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>64606</v>
       </c>
     </row>
     <row r="22">
@@ -4380,11 +4380,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>20398</v>
+        <v>74349</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20398</v>
+        <v>74349</v>
       </c>
     </row>
     <row r="23">
@@ -4414,11 +4414,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>33180.32</v>
+        <v>40980.32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>33180.32</v>
+        <v>40980.32</v>
       </c>
     </row>
     <row r="24">
@@ -4448,11 +4448,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>45419.88</v>
+        <v>55419.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4460,11 +4460,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>44623.88</v>
+        <v>54623.88</v>
       </c>
     </row>
     <row r="25">
@@ -4618,11 +4618,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>64756.2</v>
+        <v>75154.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>64756.2</v>
+        <v>75154.2</v>
       </c>
     </row>
     <row r="30">
@@ -4720,11 +4720,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>30498</v>
+        <v>30896</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>30498</v>
+        <v>30896</v>
       </c>
     </row>
     <row r="33">
@@ -4822,11 +4822,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>28864</v>
+        <v>39660</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4834,11 +4834,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-4736</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="36">
@@ -4898,15 +4898,15 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>18020</v>
+        <v>16040</v>
       </c>
     </row>
     <row r="38">
@@ -5162,11 +5162,11 @@
         <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="46">
@@ -5230,11 +5230,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>53790</v>
+        <v>118590</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5242,11 +5242,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>44590</v>
+        <v>109390</v>
       </c>
     </row>
     <row r="48">
@@ -5298,11 +5298,11 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>398</v>
+        <v>5398</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>398</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="50">
@@ -5366,11 +5366,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>33364.8</v>
+        <v>33564.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5378,11 +5378,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>21764.8</v>
+        <v>21964.8</v>
       </c>
     </row>
     <row r="52">
@@ -5434,11 +5434,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>29198</v>
+        <v>36698</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>29198</v>
+        <v>36698</v>
       </c>
     </row>
     <row r="54">
@@ -5536,11 +5536,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>70796</v>
+        <v>70996</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>70796</v>
+        <v>70996</v>
       </c>
     </row>
     <row r="57">
@@ -5570,11 +5570,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>11194</v>
+        <v>30994</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>11194</v>
+        <v>30994</v>
       </c>
     </row>
     <row r="58">
@@ -5604,11 +5604,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>30398</v>
+        <v>30796</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>30398</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="59">
@@ -5646,15 +5646,15 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>65998</v>
+        <v>64998</v>
       </c>
     </row>
     <row r="60">
@@ -5672,11 +5672,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>38396</v>
+        <v>38794</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>38396</v>
+        <v>38794</v>
       </c>
     </row>
     <row r="61">
@@ -5953,16 +5953,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>488348.57</v>
+        <v>670171.5699999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1955</v>
+        <v>2264</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>488348.57</v>
+        <v>670171.5699999999</v>
       </c>
     </row>
     <row r="3">
@@ -5977,16 +5977,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>421051</v>
+        <v>595051</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>421051</v>
+        <v>595051</v>
       </c>
     </row>
     <row r="4">
@@ -6001,16 +6001,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67297.57000000001</v>
+        <v>75120.57000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1873</v>
+        <v>2151</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>67297.57000000001</v>
+        <v>75120.57000000001</v>
       </c>
     </row>
     <row r="5">
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1503890</v>
+        <v>1582374</v>
       </c>
       <c r="D5" t="n">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1503890</v>
+        <v>1582374</v>
       </c>
     </row>
     <row r="6">
@@ -6049,16 +6049,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>974626</v>
+        <v>1019916</v>
       </c>
       <c r="D6" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>974626</v>
+        <v>1019916</v>
       </c>
     </row>
     <row r="7">
@@ -6073,16 +6073,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>498866</v>
+        <v>532060</v>
       </c>
       <c r="D7" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>498866</v>
+        <v>532060</v>
       </c>
     </row>
     <row r="8">
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>675688.11</v>
+        <v>684305.78</v>
       </c>
       <c r="D8" t="n">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>675688.11</v>
+        <v>684305.78</v>
       </c>
     </row>
     <row r="9">
@@ -6117,20 +6117,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>71337.03</v>
+        <v>433234.54</v>
       </c>
       <c r="D9" t="n">
-        <v>86</v>
+        <v>443</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>71337.03</v>
+        <v>433234.54</v>
       </c>
     </row>
     <row r="10">
@@ -6141,20 +6141,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55105.91</v>
+        <v>251071.24</v>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>352</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>55105.91</v>
+        <v>251071.24</v>
       </c>
     </row>
     <row r="11">
@@ -6169,16 +6169,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>144800</v>
+        <v>170600</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>144800</v>
+        <v>170600</v>
       </c>
     </row>
     <row r="12">
@@ -6265,16 +6265,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>110467.86</v>
+        <v>190467.86</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>110467.86</v>
+        <v>190467.86</v>
       </c>
     </row>
   </sheetData>
@@ -6335,22 +6335,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>488348.57</v>
+        <v>670171.5699999999</v>
       </c>
       <c r="C2" t="n">
-        <v>74561.03999999999</v>
+        <v>101119.04</v>
       </c>
       <c r="D2" t="n">
-        <v>6666</v>
+        <v>8248</v>
       </c>
       <c r="E2" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="F2" t="n">
-        <v>67895.03999999999</v>
+        <v>92871.03999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="3">
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1503890</v>
+        <v>1582374</v>
       </c>
       <c r="C3" t="n">
-        <v>228103.33</v>
+        <v>247521.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6372,10 +6372,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>228103.33</v>
+        <v>247521.33</v>
       </c>
       <c r="G3" t="n">
-        <v>15.17</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="4">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>675688.11</v>
+        <v>684305.78</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>144800</v>
+        <v>170600</v>
       </c>
       <c r="C5" t="n">
         <v>92200</v>
@@ -6425,7 +6425,7 @@
         <v>92200</v>
       </c>
       <c r="G5" t="n">
-        <v>63.67</v>
+        <v>54.04</v>
       </c>
     </row>
     <row r="6">
@@ -6438,7 +6438,7 @@
         <v>30000</v>
       </c>
       <c r="C6" t="n">
-        <v>27354</v>
+        <v>57080</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -6447,10 +6447,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>27354</v>
+        <v>57080</v>
       </c>
       <c r="G6" t="n">
-        <v>91.18000000000001</v>
+        <v>190.27</v>
       </c>
     </row>
     <row r="7">
@@ -6463,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>97180</v>
+        <v>150780</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>97180</v>
+        <v>150780</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>9900</v>
       </c>
       <c r="C8" t="n">
-        <v>1980</v>
+        <v>5940</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -6497,10 +6497,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1980</v>
+        <v>5940</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -6510,10 +6510,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110467.86</v>
+        <v>190467.86</v>
       </c>
       <c r="C9" t="n">
-        <v>4696</v>
+        <v>5611.75</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6522,10 +6522,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4696</v>
+        <v>5611.75</v>
       </c>
       <c r="G9" t="n">
-        <v>4.25</v>
+        <v>2.95</v>
       </c>
     </row>
   </sheetData>
@@ -6571,13 +6571,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C2" t="n">
-        <v>286801.7</v>
+        <v>354332.7</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -6587,61 +6587,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>107777</v>
+        <v>129557</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>157</v>
       </c>
       <c r="C4" t="n">
-        <v>46280</v>
+        <v>69558.67</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C5" t="n">
+        <v>47646.75</v>
+      </c>
+      <c r="D5" t="n">
         <v>6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>42200</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>26480.67</v>
+        <v>42200</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>3709</v>
+        <v>4103</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6735,7 +6735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6763,79 +6763,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>92400</v>
+        <v>102106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>22116.67</v>
+        <v>27354</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4031</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1660</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6844,16 +6844,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>97380</v>
       </c>
     </row>
     <row r="9">
@@ -6894,122 +6894,122 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>27115.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>50600</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>27354</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>6000</v>
+        <v>793</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>63600</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>7200</v>
+        <v>65580</v>
       </c>
     </row>
     <row r="17">
@@ -7038,32 +7038,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3009</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>58809</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="19">
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1619</v>
+        <v>58809</v>
       </c>
     </row>
     <row r="20">
@@ -7092,32 +7092,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>18054.7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -7128,14 +7128,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>12135</v>
+        <v>18073.7</v>
       </c>
     </row>
     <row r="23">
@@ -7146,14 +7146,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D23" t="n">
-        <v>7319</v>
+        <v>11989</v>
       </c>
     </row>
     <row r="24">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>4979</v>
+        <v>7319</v>
       </c>
     </row>
     <row r="25">
@@ -7182,14 +7182,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3865</v>
+        <v>4979</v>
       </c>
     </row>
     <row r="26">
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>3287</v>
+        <v>4837.75</v>
       </c>
     </row>
     <row r="27">
@@ -7218,14 +7218,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="28">
@@ -7240,28 +7240,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>14212</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -7272,14 +7272,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>10477.67</v>
+        <v>19239</v>
       </c>
     </row>
     <row r="31">
@@ -7290,14 +7290,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>10000</v>
+        <v>15908.67</v>
       </c>
     </row>
     <row r="32">
@@ -7308,14 +7308,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1211</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="33">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D33" t="n">
-        <v>384</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="34">
@@ -7344,68 +7344,68 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>76</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>16000</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>10000</v>
+        <v>36800</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>7000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="38">
@@ -7416,14 +7416,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>19000</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="39">
@@ -7434,74 +7434,74 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>8009</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3600</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>10398</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>398</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7513,31 +7513,31 @@
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>8000</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1200</v>
+        <v>398</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7546,64 +7546,154 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>7083.33</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>6500</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>7083.33</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>昆明</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>其他/未说明</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C51" t="n">
         <v>3</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D51" t="n">
         <v>3419</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -7644,10 +7734,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>179183.33</v>
+        <v>183781.33</v>
       </c>
     </row>
     <row r="3">
@@ -7670,36 +7760,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>60537.04</v>
+        <v>85437.03999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>48400</v>
+        <v>83600</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46800</v>
+        <v>65200</v>
       </c>
     </row>
     <row r="7">
@@ -7709,10 +7799,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>27354</v>
+        <v>57080</v>
       </c>
     </row>
     <row r="8">
@@ -7722,10 +7812,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>26820</v>
+        <v>41640</v>
       </c>
     </row>
     <row r="9">
@@ -7744,27 +7834,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>4745</v>
+        <v>6736</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>认知9周+年卡</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="C11" t="n">
-        <v>3900</v>
+        <v>5390</v>
       </c>
     </row>
   </sheetData>
@@ -7805,62 +7895,62 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>146606.33</v>
+        <v>151719.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>92946</v>
+        <v>101670</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>62202</v>
+        <v>96965</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>54489</v>
+        <v>62577</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>35693</v>
+        <v>49992.7</v>
       </c>
     </row>
     <row r="7">
@@ -7870,127 +7960,127 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>22359.67</v>
+        <v>37337.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>13465</v>
+        <v>35693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>13135.7</v>
+        <v>18830</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>10880</v>
+        <v>14877</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>10256</v>
+        <v>12211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>9913</v>
+        <v>11262.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>9263.67</v>
+        <v>10861</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>7983</v>
+        <v>10294</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>7074</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>6567</v>
+        <v>7150</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -541,12 +541,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -594,12 +594,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -647,12 +647,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -700,12 +700,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2500000</v>
+        <v>2000000</v>
       </c>
       <c r="D6" t="n">
         <v>596300</v>
@@ -751,12 +751,12 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>500000</v>
+        <v>380000</v>
       </c>
       <c r="D7" t="n">
         <v>57135</v>
@@ -812,12 +812,12 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="D8" t="n">
         <v>257597</v>
@@ -873,12 +873,12 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="D9" t="n">
         <v>205081</v>
@@ -930,12 +930,12 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1100000</v>
+        <v>1030000</v>
       </c>
       <c r="D10" t="n">
         <v>62025</v>
@@ -993,12 +993,12 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>400000</v>
+        <v>260000</v>
       </c>
       <c r="D11" t="n">
         <v>18651</v>
@@ -1056,12 +1056,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="D12" t="n">
         <v>220245</v>
@@ -1113,12 +1113,12 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1900000</v>
+        <v>1600000</v>
       </c>
       <c r="D13" t="n">
         <v>105001</v>
@@ -1170,12 +1170,12 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="D14" t="n">
         <v>529417</v>
@@ -1233,12 +1233,12 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1292,12 +1292,12 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="D16" t="n">
         <v>48671</v>
@@ -1355,12 +1355,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18500000</v>
+        <v>15000000</v>
       </c>
       <c r="D19" t="n">
         <v>3338948</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2171,22 +2171,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3129120000</v>
+        <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>84954</v>
+        <v>75177.3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2213,22 +2213,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3026180000</v>
+        <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>6260</v>
+        <v>1281</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2255,22 +2255,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2699380000</v>
+        <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>34860</v>
+        <v>27357</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2297,22 +2297,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1611540000</v>
+        <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>22000</v>
+        <v>17319</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2339,22 +2339,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1611540000</v>
+        <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>21200</v>
+        <v>15520</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2424050000</v>
+        <v>242405</v>
       </c>
       <c r="D7" t="n">
         <v>4681</v>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2423,22 +2423,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1891360000</v>
+        <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>4980</v>
+        <v>1000</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2465,22 +2465,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3336160000</v>
+        <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>42936</v>
+        <v>-10960.67</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2714400000</v>
+        <v>271440</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2714400000</v>
+        <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>10160</v>
+        <v>160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2392460000</v>
+        <v>239246</v>
       </c>
       <c r="D12" t="n">
         <v>14940</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2277770000</v>
+        <v>227777</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2675,22 +2675,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2070510000</v>
+        <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>14940</v>
+        <v>-40823</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1472910000</v>
+        <v>147291</v>
       </c>
       <c r="D15" t="n">
         <v>6600</v>
@@ -2727,12 +2727,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2790500000</v>
+        <v>279050</v>
       </c>
       <c r="D16" t="n">
         <v>34900</v>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2855170000</v>
+        <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>89054</v>
+        <v>84489</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2906430000</v>
+        <v>290643</v>
       </c>
       <c r="D18" t="n">
         <v>25696</v>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2885,22 +2885,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2910910000</v>
+        <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>4980</v>
+        <v>-10000</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2927,22 +2927,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1767450000</v>
+        <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>19920</v>
+        <v>15493.33</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2969,22 +2969,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1557960000</v>
+        <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>14940</v>
+        <v>9960</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3011,22 +3011,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1604740000</v>
+        <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>19920</v>
+        <v>9940</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3053,22 +3053,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2653220000</v>
+        <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>36178</v>
+        <v>26218</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3095,22 +3095,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1338020000</v>
+        <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>33420</v>
+        <v>6600</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3137,22 +3137,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1285630000</v>
+        <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>44600</v>
+        <v>25800</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1976140000</v>
+        <v>197614</v>
       </c>
       <c r="D26" t="n">
         <v>24000</v>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3221,22 +3221,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1923750000</v>
+        <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>66400</v>
+        <v>57400</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D28" t="n">
         <v>6600</v>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D29" t="n">
         <v>12000</v>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1390410000</v>
+        <v>139041</v>
       </c>
       <c r="D30" t="n">
         <v>25200</v>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3389,22 +3389,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>24088</v>
+        <v>20088</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D32" t="n">
         <v>43800</v>
@@ -3441,12 +3441,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D33" t="n">
         <v>34800</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1020980000</v>
+        <v>102098</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1021030000</v>
+        <v>102103</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3734,11 +3734,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>281908</v>
+        <v>223108</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3836,11 +3836,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>28392</v>
+        <v>26792</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3938,11 +3938,11 @@
         <v>140000</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-598</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4448,11 +4448,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>55419.88</v>
+        <v>54623.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4482,11 +4482,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>3790</v>
+        <v>-6210</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4652,11 +4652,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>7700</v>
+        <v>-6800</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4686,11 +4686,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>49696</v>
+        <v>40196</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4754,11 +4754,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>17796</v>
+        <v>9296</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4822,11 +4822,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>39660</v>
+        <v>6060</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4890,11 +4890,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>20000</v>
+        <v>16040</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5060,11 +5060,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>1200</v>
+        <v>-5883.33</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5230,11 +5230,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>118590</v>
+        <v>109390</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5366,11 +5366,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>33564.8</v>
+        <v>21964.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5638,11 +5638,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>65998</v>
+        <v>64998</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5774,11 +5774,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>43190</v>
+        <v>39790</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F63" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15000000</v>
+        <v>15270000</v>
       </c>
       <c r="D19" t="n">
         <v>3338948</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="J19" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2000000</v>
+        <v>2500000</v>
       </c>
       <c r="D6" t="n">
         <v>596300</v>
@@ -751,12 +751,12 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>380000</v>
+        <v>500000</v>
       </c>
       <c r="D7" t="n">
         <v>57135</v>
@@ -812,12 +812,12 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="D8" t="n">
         <v>257597</v>
@@ -873,12 +873,12 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="D9" t="n">
         <v>205081</v>
@@ -930,12 +930,12 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1030000</v>
+        <v>1100000</v>
       </c>
       <c r="D10" t="n">
         <v>62025</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>260000</v>
+        <v>400000</v>
       </c>
       <c r="D11" t="n">
         <v>18651</v>
@@ -1056,12 +1056,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="D12" t="n">
         <v>220245</v>
@@ -1113,12 +1113,12 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1600000</v>
+        <v>1900000</v>
       </c>
       <c r="D13" t="n">
         <v>105001</v>
@@ -1170,12 +1170,12 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="D14" t="n">
         <v>529417</v>
@@ -1233,12 +1233,12 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>700000</v>
+        <v>900000</v>
       </c>
       <c r="D16" t="n">
         <v>48671</v>
@@ -1355,12 +1355,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15270000</v>
+        <v>18500000</v>
       </c>
       <c r="D19" t="n">
         <v>3338948</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="J19" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18500000</v>
+        <v>17200000</v>
       </c>
       <c r="D19" t="n">
         <v>3338948</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="J19" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -541,12 +541,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -594,12 +594,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -647,12 +647,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -700,12 +700,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -751,12 +751,12 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -812,12 +812,12 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -873,12 +873,12 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -930,12 +930,12 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -993,12 +993,12 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1056,12 +1056,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1113,12 +1113,12 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1170,12 +1170,12 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1233,12 +1233,12 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1292,12 +1292,12 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1355,12 +1355,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2174,19 +2174,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>75177.3</v>
+        <v>84954</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2216,19 +2216,19 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>1281</v>
+        <v>6260</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2258,19 +2258,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>27357</v>
+        <v>34860</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2300,19 +2300,19 @@
         <v>161154</v>
       </c>
       <c r="D5" t="n">
-        <v>17319</v>
+        <v>22000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2342,19 +2342,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>15520</v>
+        <v>21200</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2426,19 +2426,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>1000</v>
+        <v>4980</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2468,19 +2468,19 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>-10960.67</v>
+        <v>42936</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2552,19 +2552,19 @@
         <v>271440</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>10160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2678,19 +2678,19 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>-40823</v>
+        <v>14940</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2804,19 +2804,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>84489</v>
+        <v>89054</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2888,19 +2888,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>-10000</v>
+        <v>4980</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2930,19 +2930,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>15493.33</v>
+        <v>19920</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2972,19 +2972,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3014,19 +3014,19 @@
         <v>160474</v>
       </c>
       <c r="D22" t="n">
-        <v>9940</v>
+        <v>19920</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3056,19 +3056,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>26218</v>
+        <v>36178</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3098,19 +3098,19 @@
         <v>133802</v>
       </c>
       <c r="D24" t="n">
-        <v>6600</v>
+        <v>33420</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3140,19 +3140,19 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>25800</v>
+        <v>44600</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3224,19 +3224,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>57400</v>
+        <v>66400</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3392,19 +3392,19 @@
         <v>102098</v>
       </c>
       <c r="D31" t="n">
-        <v>20088</v>
+        <v>24088</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3734,11 +3734,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>223108</v>
+        <v>281908</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3836,11 +3836,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>26792</v>
+        <v>28392</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3938,11 +3938,11 @@
         <v>140000</v>
       </c>
       <c r="D9" t="n">
-        <v>-598</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4448,11 +4448,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>54623.88</v>
+        <v>55419.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4482,11 +4482,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>-6210</v>
+        <v>3790</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4652,11 +4652,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>-6800</v>
+        <v>7700</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4686,11 +4686,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>40196</v>
+        <v>49696</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4754,11 +4754,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>9296</v>
+        <v>17796</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4822,11 +4822,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>6060</v>
+        <v>39660</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4890,11 +4890,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>16040</v>
+        <v>20000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5060,11 +5060,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>-5883.33</v>
+        <v>1200</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5230,11 +5230,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>109390</v>
+        <v>118590</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5366,11 +5366,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>21964.8</v>
+        <v>33564.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5638,11 +5638,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>64998</v>
+        <v>65998</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5774,11 +5774,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>39790</v>
+        <v>43190</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F63" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-97838</v>
+        <v>-174194</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-337.5%</t>
+          <t>-233.4%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -607,11 +607,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-107062</v>
+        <v>-164475</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-82.4%</t>
+          <t>-88.5%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -660,11 +660,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-96327</v>
+        <v>-117527</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-372.6%</t>
+          <t>-323.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -713,11 +713,11 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-293485</v>
+        <v>-479265</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-170.3%</t>
+          <t>-143.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1533,11 +1533,11 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-75019</v>
+        <v>-415768</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-3670.7%</t>
+          <t>-744.3%</t>
         </is>
       </c>
       <c r="N19" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -550,15 +550,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>236512</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>+19.7%</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>-174194</v>
+        <v>160156</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-233.4%</t>
+          <t>+45.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -603,15 +607,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>320820</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-64.9%</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>-164475</v>
+        <v>216257</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-108.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -656,15 +664,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>327577</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-5.5%</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>-117527</v>
+        <v>306377</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-323.5%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -709,15 +721,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>1109059</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-67.6%</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>-479265</v>
+        <v>777779</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-143.0%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -760,19 +776,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>712622</v>
+        <v>788050</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>712622</v>
+        <v>788050</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -821,19 +837,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>210</v>
+        <v>143212</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+27107.1%</t>
+          <t>-60.1%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-26190</v>
+        <v>116812</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-305.1%</t>
+          <t>-54.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -882,15 +898,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>280599</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-8.2%</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>-23028</v>
+        <v>257571</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-1214.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -939,19 +959,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7946</v>
+        <v>264021</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+2480.9%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-18001</v>
+        <v>238113</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-1056.0%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1002,19 +1022,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>9842</v>
+        <v>96892</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+530.2%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-5024</v>
+        <v>82026</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+174.0%</t>
+          <t>-116.8%</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1065,15 +1085,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>79127</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-76.4%</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>-15857</v>
+        <v>63270</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-172.7%</t>
+          <t>-81.8%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1122,15 +1146,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>120764</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>+82.4%</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>-417</v>
+        <v>120366</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-50705.8%</t>
+          <t>+75.3%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1179,19 +1207,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18982</v>
+        <v>209357</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+453.2%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-27618</v>
+        <v>162757</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-441.1%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1242,15 +1270,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>473019</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>+11.9%</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>-19657</v>
+        <v>453362</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-2485.8%</t>
+          <t>+3.4%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1301,19 +1333,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6368</v>
+        <v>145003</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+2640.8%</t>
+          <t>+20.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6159</v>
+        <v>144794</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+2188.1%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1364,15 +1396,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>240008</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-79.7%</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>-40765</v>
+        <v>199243</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-217.9%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1466,15 +1502,19 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>1404551</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-100.0%</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>-22533</v>
+        <v>900135</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-100.7%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1525,19 +1565,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>755972</v>
+        <v>6238573</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+341.7%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-415768</v>
+        <v>4987069</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-744.3%</t>
+          <t>-46.3%</t>
         </is>
       </c>
       <c r="N19" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>二阶</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1604,7 +1604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,38 +1637,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>907.8</v>
+        <v>567.2</v>
       </c>
       <c r="E2" t="n">
-        <v>2930</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>二阶</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>340.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>门店</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>660</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>111</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>1388.4</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>3311</v>
       </c>
     </row>
@@ -1683,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,17 +1740,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>618456</v>
+        <v>448637</v>
       </c>
       <c r="D2" t="n">
-        <v>63883</v>
+        <v>27463</v>
       </c>
       <c r="E2" t="n">
-        <v>468696</v>
+        <v>379432</v>
       </c>
     </row>
     <row r="3">
@@ -1742,38 +1761,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>门店</t>
+          <t>二阶</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>478468</v>
+        <v>169819</v>
       </c>
       <c r="D3" t="n">
-        <v>1439145</v>
+        <v>36420</v>
       </c>
       <c r="E3" t="n">
-        <v>905544</v>
+        <v>89263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>分组</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>215539</v>
+        <v>478468</v>
       </c>
       <c r="D4" t="n">
-        <v>16827</v>
+        <v>1439145</v>
       </c>
       <c r="E4" t="n">
-        <v>178382</v>
+        <v>905544</v>
       </c>
     </row>
     <row r="5">
@@ -1784,17 +1803,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-19506</v>
+        <v>215539</v>
       </c>
       <c r="D5" t="n">
-        <v>618</v>
+        <v>16827</v>
       </c>
       <c r="E5" t="n">
-        <v>-1782</v>
+        <v>178382</v>
       </c>
     </row>
     <row r="6">
@@ -1805,17 +1824,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>252603</v>
+        <v>-19506</v>
       </c>
       <c r="D6" t="n">
-        <v>10019</v>
+        <v>618</v>
       </c>
       <c r="E6" t="n">
-        <v>202832</v>
+        <v>-1782</v>
       </c>
     </row>
     <row r="7">
@@ -1826,17 +1845,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>169819</v>
+        <v>252603</v>
       </c>
       <c r="D7" t="n">
-        <v>36420</v>
+        <v>10019</v>
       </c>
       <c r="E7" t="n">
-        <v>89263</v>
+        <v>202832</v>
       </c>
     </row>
     <row r="8">
@@ -1847,17 +1866,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>208473</v>
+        <v>169819</v>
       </c>
       <c r="D8" t="n">
-        <v>351027</v>
+        <v>36420</v>
       </c>
       <c r="E8" t="n">
-        <v>518704</v>
+        <v>89263</v>
       </c>
     </row>
     <row r="9">
@@ -1868,17 +1887,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45903</v>
+        <v>208473</v>
       </c>
       <c r="D9" t="n">
-        <v>7813</v>
+        <v>351027</v>
       </c>
       <c r="E9" t="n">
-        <v>18336</v>
+        <v>518704</v>
       </c>
     </row>
     <row r="10">
@@ -1889,17 +1908,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29405</v>
+        <v>45903</v>
       </c>
       <c r="D10" t="n">
-        <v>227192</v>
+        <v>7813</v>
       </c>
       <c r="E10" t="n">
-        <v>52419</v>
+        <v>18336</v>
       </c>
     </row>
     <row r="11">
@@ -1910,17 +1929,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42322</v>
+        <v>29405</v>
       </c>
       <c r="D11" t="n">
-        <v>122831</v>
+        <v>227192</v>
       </c>
       <c r="E11" t="n">
-        <v>16199</v>
+        <v>52419</v>
       </c>
     </row>
     <row r="12">
@@ -1931,17 +1950,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-35527</v>
+        <v>42322</v>
       </c>
       <c r="D12" t="n">
-        <v>15408</v>
+        <v>122831</v>
       </c>
       <c r="E12" t="n">
-        <v>-32148</v>
+        <v>16199</v>
       </c>
     </row>
     <row r="13">
@@ -1952,17 +1971,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-7026</v>
+        <v>-35527</v>
       </c>
       <c r="D13" t="n">
-        <v>18556</v>
+        <v>15408</v>
       </c>
       <c r="E13" t="n">
-        <v>3417</v>
+        <v>-32148</v>
       </c>
     </row>
     <row r="14">
@@ -1973,17 +1992,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>52636</v>
+        <v>-7026</v>
       </c>
       <c r="D14" t="n">
-        <v>158390</v>
+        <v>18556</v>
       </c>
       <c r="E14" t="n">
-        <v>91448</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="15">
@@ -1994,17 +2013,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13603</v>
+        <v>52636</v>
       </c>
       <c r="D15" t="n">
-        <v>68284</v>
+        <v>158390</v>
       </c>
       <c r="E15" t="n">
-        <v>24741</v>
+        <v>91448</v>
       </c>
     </row>
     <row r="16">
@@ -2015,17 +2034,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>77728</v>
+        <v>13603</v>
       </c>
       <c r="D16" t="n">
-        <v>370042</v>
+        <v>68284</v>
       </c>
       <c r="E16" t="n">
-        <v>166594</v>
+        <v>24741</v>
       </c>
     </row>
     <row r="17">
@@ -2036,17 +2055,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31586</v>
+        <v>77728</v>
       </c>
       <c r="D17" t="n">
-        <v>70896</v>
+        <v>370042</v>
       </c>
       <c r="E17" t="n">
-        <v>38440</v>
+        <v>166594</v>
       </c>
     </row>
     <row r="18">
@@ -2057,17 +2076,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19366</v>
+        <v>31586</v>
       </c>
       <c r="D18" t="n">
-        <v>28707</v>
+        <v>70896</v>
       </c>
       <c r="E18" t="n">
-        <v>7395</v>
+        <v>38440</v>
       </c>
     </row>
     <row r="19">
@@ -2078,17 +2097,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>望京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>19366</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>28707</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="20">
@@ -2099,11 +2118,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>望京</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2115,21 +2134,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-6500</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>南区合计</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>1090424</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>1503030</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>1374240</v>
       </c>
     </row>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -6039,10 +6039,10 @@
         <v>2264</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>580961.5699999999</v>
       </c>
       <c r="F2" t="n">
-        <v>670171.5699999999</v>
+        <v>89210</v>
       </c>
     </row>
     <row r="3">
@@ -6063,10 +6063,10 @@
         <v>113</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>509131</v>
       </c>
       <c r="F3" t="n">
-        <v>595051</v>
+        <v>85920</v>
       </c>
     </row>
     <row r="4">
@@ -6087,10 +6087,10 @@
         <v>2151</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>71830.57000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>75120.57000000001</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="5">
@@ -6111,10 +6111,10 @@
         <v>307</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>304784</v>
       </c>
       <c r="F5" t="n">
-        <v>1582374</v>
+        <v>1277590</v>
       </c>
     </row>
     <row r="6">
@@ -6135,10 +6135,10 @@
         <v>170</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="F6" t="n">
-        <v>1019916</v>
+        <v>997916</v>
       </c>
     </row>
     <row r="7">
@@ -6159,10 +6159,10 @@
         <v>134</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>282784</v>
       </c>
       <c r="F7" t="n">
-        <v>532060</v>
+        <v>249276</v>
       </c>
     </row>
     <row r="8">
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>684305.78</v>
+        <v>685434.5</v>
       </c>
       <c r="D8" t="n">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>31572.13</v>
       </c>
       <c r="F8" t="n">
-        <v>684305.78</v>
+        <v>653862.37</v>
       </c>
     </row>
     <row r="9">
@@ -6201,16 +6201,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>433234.54</v>
+        <v>434073.26</v>
       </c>
       <c r="D9" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1107.89</v>
       </c>
       <c r="F9" t="n">
-        <v>433234.54</v>
+        <v>432965.37</v>
       </c>
     </row>
     <row r="10">
@@ -6225,16 +6225,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>251071.24</v>
+        <v>251361.24</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>30464.24</v>
       </c>
       <c r="F10" t="n">
-        <v>251071.24</v>
+        <v>220897</v>
       </c>
     </row>
     <row r="11">
@@ -6255,10 +6255,10 @@
         <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>99200</v>
       </c>
       <c r="F11" t="n">
-        <v>170600</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="12">
@@ -6351,10 +6351,10 @@
         <v>70</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>47776.36</v>
       </c>
       <c r="F15" t="n">
-        <v>190467.86</v>
+        <v>142691.5</v>
       </c>
     </row>
   </sheetData>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>684305.78</v>
+        <v>685434.5</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -528,25 +528,25 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>283217</v>
+        <v>302066</v>
       </c>
       <c r="E2" t="n">
-        <v>50850</v>
+        <v>61855</v>
       </c>
       <c r="F2" t="n">
-        <v>232366</v>
+        <v>240210</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,15 +554,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+19.7%</t>
+          <t>+27.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>160156</v>
+        <v>159157</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+45.1%</t>
+          <t>+50.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,41 +585,41 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>112657</v>
+        <v>123695</v>
       </c>
       <c r="E3" t="n">
-        <v>131545</v>
+        <v>139092</v>
       </c>
       <c r="F3" t="n">
-        <v>-18888</v>
+        <v>-15397</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>320820</v>
+        <v>325800</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-64.9%</t>
+          <t>-62.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>216257</v>
+        <v>204437</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-108.7%</t>
+          <t>-107.5%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -642,29 +642,29 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>309517</v>
+        <v>335421</v>
       </c>
       <c r="E4" t="n">
-        <v>46895</v>
+        <v>82496</v>
       </c>
       <c r="F4" t="n">
-        <v>262622</v>
+        <v>252925</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>327577</v>
+        <v>354943</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -672,11 +672,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>306377</v>
+        <v>333743</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -699,41 +699,41 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>358903</v>
+        <v>396147</v>
       </c>
       <c r="E5" t="n">
-        <v>152664</v>
+        <v>184917</v>
       </c>
       <c r="F5" t="n">
-        <v>206239</v>
+        <v>211230</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1109059</v>
+        <v>1129059</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-67.6%</t>
+          <t>-64.9%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>777779</v>
+        <v>748179</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -756,50 +756,50 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>596300</v>
+        <v>623808</v>
       </c>
       <c r="E6" t="n">
         <v>36800</v>
       </c>
       <c r="F6" t="n">
-        <v>559500</v>
+        <v>587008</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>788050</v>
+        <v>906020</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>788050</v>
+        <v>906020</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>208473</v>
+        <v>228667</v>
       </c>
       <c r="P6" t="n">
-        <v>351027</v>
+        <v>358341</v>
       </c>
       <c r="Q6" t="n">
-        <v>518704</v>
+        <v>546212</v>
       </c>
     </row>
     <row r="7">
@@ -817,39 +817,39 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>57135</v>
+        <v>58154</v>
       </c>
       <c r="E7" t="n">
-        <v>3419</v>
+        <v>3438</v>
       </c>
       <c r="F7" t="n">
-        <v>53716</v>
+        <v>54716</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>143212</v>
+        <v>143619</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-60.1%</t>
+          <t>-59.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>116812</v>
+        <v>117219</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-54.0%</t>
+          <t>-53.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -857,7 +857,7 @@
         <v>45903</v>
       </c>
       <c r="P7" t="n">
-        <v>7813</v>
+        <v>8813</v>
       </c>
       <c r="Q7" t="n">
         <v>18336</v>
@@ -878,50 +878,50 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>257597</v>
+        <v>268393</v>
       </c>
       <c r="E8" t="n">
         <v>1000</v>
       </c>
       <c r="F8" t="n">
-        <v>256597</v>
+        <v>267393</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>280599</v>
+        <v>281035</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>257571</v>
+        <v>257978</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>+3.6%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>29405</v>
+        <v>29803</v>
       </c>
       <c r="P8" t="n">
-        <v>227192</v>
+        <v>237590</v>
       </c>
       <c r="Q8" t="n">
-        <v>52419</v>
+        <v>52817</v>
       </c>
     </row>
     <row r="9">
@@ -939,52 +939,52 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>205081</v>
+        <v>227629</v>
       </c>
       <c r="E9" t="n">
         <v>33000</v>
       </c>
       <c r="F9" t="n">
-        <v>172081</v>
+        <v>194629</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>264021</v>
+        <v>300521</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>238113</v>
+        <v>274594</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6927</v>
+        <v>15077</v>
       </c>
       <c r="O9" t="n">
-        <v>42322</v>
+        <v>53520</v>
       </c>
       <c r="P9" t="n">
-        <v>122831</v>
+        <v>126031</v>
       </c>
       <c r="Q9" t="n">
-        <v>16199</v>
+        <v>25949</v>
       </c>
     </row>
     <row r="10">
@@ -1002,13 +1002,13 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>62025</v>
+        <v>62083</v>
       </c>
       <c r="E10" t="n">
-        <v>75789</v>
+        <v>87789</v>
       </c>
       <c r="F10" t="n">
-        <v>-13764</v>
+        <v>-25706</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1022,32 +1022,32 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>96892</v>
+        <v>117290</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>82026</v>
+        <v>102424</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-116.8%</t>
+          <t>-125.1%</t>
         </is>
       </c>
       <c r="N10" t="n">
         <v>6355</v>
       </c>
       <c r="O10" t="n">
-        <v>-35527</v>
+        <v>-47469</v>
       </c>
       <c r="P10" t="n">
         <v>15408</v>
       </c>
       <c r="Q10" t="n">
-        <v>-32148</v>
+        <v>-32090</v>
       </c>
     </row>
     <row r="11">
@@ -1065,50 +1065,50 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>18651</v>
+        <v>19068</v>
       </c>
       <c r="E11" t="n">
         <v>7121</v>
       </c>
       <c r="F11" t="n">
-        <v>11530</v>
+        <v>11947</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>79127</v>
+        <v>88081</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>63270</v>
+        <v>72224</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-81.8%</t>
+          <t>-83.5%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>-7026</v>
+        <v>-7007</v>
       </c>
       <c r="P11" t="n">
-        <v>18556</v>
+        <v>18954</v>
       </c>
       <c r="Q11" t="n">
-        <v>3417</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="12">
@@ -1126,50 +1126,50 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>220245</v>
+        <v>231060</v>
       </c>
       <c r="E12" t="n">
-        <v>9219</v>
+        <v>10419</v>
       </c>
       <c r="F12" t="n">
-        <v>211026</v>
+        <v>220641</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>120764</v>
+        <v>197885</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+82.4%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>120366</v>
+        <v>197487</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+75.3%</t>
+          <t>+11.7%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>52636</v>
+        <v>53451</v>
       </c>
       <c r="P12" t="n">
-        <v>158390</v>
+        <v>167190</v>
       </c>
       <c r="Q12" t="n">
-        <v>91448</v>
+        <v>91467</v>
       </c>
     </row>
     <row r="13">
@@ -1187,52 +1187,52 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>105001</v>
+        <v>105466</v>
       </c>
       <c r="E13" t="n">
-        <v>10796</v>
+        <v>11194</v>
       </c>
       <c r="F13" t="n">
-        <v>94205</v>
+        <v>94272</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>209357</v>
+        <v>229895</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-54.1%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>162757</v>
+        <v>183295</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-48.6%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>12318</v>
+        <v>12385</v>
       </c>
       <c r="O13" t="n">
-        <v>13603</v>
+        <v>13205</v>
       </c>
       <c r="P13" t="n">
-        <v>68284</v>
+        <v>68682</v>
       </c>
       <c r="Q13" t="n">
-        <v>24741</v>
+        <v>24410</v>
       </c>
     </row>
     <row r="14">
@@ -1250,52 +1250,52 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>529417</v>
+        <v>625444</v>
       </c>
       <c r="E14" t="n">
-        <v>60447</v>
+        <v>67947</v>
       </c>
       <c r="F14" t="n">
-        <v>468970</v>
+        <v>557497</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>473019</v>
+        <v>640689</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+11.9%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>453362</v>
+        <v>621032</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>21200</v>
       </c>
       <c r="O14" t="n">
-        <v>77728</v>
+        <v>117974</v>
       </c>
       <c r="P14" t="n">
-        <v>370042</v>
+        <v>418323</v>
       </c>
       <c r="Q14" t="n">
-        <v>166594</v>
+        <v>202025</v>
       </c>
     </row>
     <row r="15">
@@ -1313,52 +1313,52 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>174531</v>
+        <v>196473</v>
       </c>
       <c r="E15" t="n">
         <v>33609</v>
       </c>
       <c r="F15" t="n">
-        <v>140922</v>
+        <v>162864</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>145003</v>
+        <v>171792</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+20.4%</t>
+          <t>+14.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>144794</v>
+        <v>171583</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>38440</v>
+        <v>38786</v>
       </c>
       <c r="O15" t="n">
-        <v>31586</v>
+        <v>51586</v>
       </c>
       <c r="P15" t="n">
-        <v>70896</v>
+        <v>72492</v>
       </c>
       <c r="Q15" t="n">
-        <v>38440</v>
+        <v>39184</v>
       </c>
     </row>
     <row r="16">
@@ -1376,50 +1376,50 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>48671</v>
+        <v>81488</v>
       </c>
       <c r="E16" t="n">
-        <v>598</v>
+        <v>2676</v>
       </c>
       <c r="F16" t="n">
-        <v>48073</v>
+        <v>78812</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>240008</v>
+        <v>250587</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>199243</v>
+        <v>209765</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-62.4%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>19366</v>
+        <v>29385</v>
       </c>
       <c r="P16" t="n">
-        <v>28707</v>
+        <v>49427</v>
       </c>
       <c r="Q16" t="n">
-        <v>7395</v>
+        <v>7134</v>
       </c>
     </row>
     <row r="17">
@@ -1502,7 +1502,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>1404551</v>
+        <v>1498593</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>900135</v>
+        <v>975257</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1543,54 +1543,54 @@
         <v>17200000</v>
       </c>
       <c r="D19" t="n">
-        <v>3338948</v>
+        <v>3656394</v>
       </c>
       <c r="E19" t="n">
-        <v>660252</v>
+        <v>769853</v>
       </c>
       <c r="F19" t="n">
-        <v>2678696</v>
+        <v>2886541</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6238573</v>
+        <v>6872322</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4987069</v>
+        <v>5534394</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-46.3%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>85240</v>
+        <v>93803</v>
       </c>
       <c r="O19" t="n">
-        <v>1090424</v>
+        <v>1176747</v>
       </c>
       <c r="P19" t="n">
-        <v>1503030</v>
+        <v>1615990</v>
       </c>
       <c r="Q19" t="n">
-        <v>1374240</v>
+        <v>1453010</v>
       </c>
     </row>
   </sheetData>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>448637</v>
+        <v>449420</v>
       </c>
       <c r="D2" t="n">
-        <v>27463</v>
+        <v>28318</v>
       </c>
       <c r="E2" t="n">
-        <v>379432</v>
+        <v>390672</v>
       </c>
     </row>
     <row r="3">
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169819</v>
+        <v>164810</v>
       </c>
       <c r="D3" t="n">
-        <v>36420</v>
+        <v>46420</v>
       </c>
       <c r="E3" t="n">
-        <v>89263</v>
+        <v>83458</v>
       </c>
     </row>
     <row r="4">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>478468</v>
+        <v>569017</v>
       </c>
       <c r="D4" t="n">
-        <v>1439145</v>
+        <v>1541250</v>
       </c>
       <c r="E4" t="n">
-        <v>905544</v>
+        <v>978879</v>
       </c>
     </row>
     <row r="5">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>215539</v>
+        <v>222528</v>
       </c>
       <c r="D5" t="n">
-        <v>16827</v>
+        <v>17682</v>
       </c>
       <c r="E5" t="n">
-        <v>178382</v>
+        <v>185828</v>
       </c>
     </row>
     <row r="6">
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-19506</v>
+        <v>-16015</v>
       </c>
       <c r="D6" t="n">
         <v>618</v>
       </c>
       <c r="E6" t="n">
-        <v>-1782</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="7">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>252603</v>
+        <v>242906</v>
       </c>
       <c r="D7" t="n">
         <v>10019</v>
       </c>
       <c r="E7" t="n">
-        <v>202832</v>
+        <v>203135</v>
       </c>
     </row>
     <row r="8">
@@ -1870,13 +1870,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>169819</v>
+        <v>164810</v>
       </c>
       <c r="D8" t="n">
-        <v>36420</v>
+        <v>46420</v>
       </c>
       <c r="E8" t="n">
-        <v>89263</v>
+        <v>83458</v>
       </c>
     </row>
     <row r="9">
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>208473</v>
+        <v>228667</v>
       </c>
       <c r="D9" t="n">
-        <v>351027</v>
+        <v>358341</v>
       </c>
       <c r="E9" t="n">
-        <v>518704</v>
+        <v>546212</v>
       </c>
     </row>
     <row r="10">
@@ -1915,7 +1915,7 @@
         <v>45903</v>
       </c>
       <c r="D10" t="n">
-        <v>7813</v>
+        <v>8813</v>
       </c>
       <c r="E10" t="n">
         <v>18336</v>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29405</v>
+        <v>29803</v>
       </c>
       <c r="D11" t="n">
-        <v>227192</v>
+        <v>237590</v>
       </c>
       <c r="E11" t="n">
-        <v>52419</v>
+        <v>52817</v>
       </c>
     </row>
     <row r="12">
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>42322</v>
+        <v>53520</v>
       </c>
       <c r="D12" t="n">
-        <v>122831</v>
+        <v>126031</v>
       </c>
       <c r="E12" t="n">
-        <v>16199</v>
+        <v>25949</v>
       </c>
     </row>
     <row r="13">
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-35527</v>
+        <v>-47469</v>
       </c>
       <c r="D13" t="n">
         <v>15408</v>
       </c>
       <c r="E13" t="n">
-        <v>-32148</v>
+        <v>-32090</v>
       </c>
     </row>
     <row r="14">
@@ -1996,13 +1996,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-7026</v>
+        <v>-7007</v>
       </c>
       <c r="D14" t="n">
-        <v>18556</v>
+        <v>18954</v>
       </c>
       <c r="E14" t="n">
-        <v>3417</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="15">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>52636</v>
+        <v>53451</v>
       </c>
       <c r="D15" t="n">
-        <v>158390</v>
+        <v>167190</v>
       </c>
       <c r="E15" t="n">
-        <v>91448</v>
+        <v>91467</v>
       </c>
     </row>
     <row r="16">
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13603</v>
+        <v>13205</v>
       </c>
       <c r="D16" t="n">
-        <v>68284</v>
+        <v>68682</v>
       </c>
       <c r="E16" t="n">
-        <v>24741</v>
+        <v>24410</v>
       </c>
     </row>
     <row r="17">
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>77728</v>
+        <v>117974</v>
       </c>
       <c r="D17" t="n">
-        <v>370042</v>
+        <v>418323</v>
       </c>
       <c r="E17" t="n">
-        <v>166594</v>
+        <v>202025</v>
       </c>
     </row>
     <row r="18">
@@ -2080,13 +2080,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>31586</v>
+        <v>51586</v>
       </c>
       <c r="D18" t="n">
-        <v>70896</v>
+        <v>72492</v>
       </c>
       <c r="E18" t="n">
-        <v>38440</v>
+        <v>39184</v>
       </c>
     </row>
     <row r="19">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19366</v>
+        <v>29385</v>
       </c>
       <c r="D19" t="n">
-        <v>28707</v>
+        <v>49427</v>
       </c>
       <c r="E19" t="n">
-        <v>7395</v>
+        <v>7134</v>
       </c>
     </row>
     <row r="20">
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1090424</v>
+        <v>1176747</v>
       </c>
       <c r="D22" t="n">
-        <v>1503030</v>
+        <v>1615990</v>
       </c>
       <c r="E22" t="n">
-        <v>1374240</v>
+        <v>1453010</v>
       </c>
     </row>
   </sheetData>
@@ -2254,31 +2254,31 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>84954</v>
+        <v>80372</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9776.700000000001</v>
+        <v>13491.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>75177.3</v>
+        <v>66880.3</v>
       </c>
     </row>
     <row r="3">
@@ -2338,19 +2338,19 @@
         <v>269938</v>
       </c>
       <c r="D4" t="n">
-        <v>34860</v>
+        <v>44820</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2358,11 +2358,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>27357</v>
+        <v>37317</v>
       </c>
     </row>
     <row r="5">
@@ -2422,19 +2422,19 @@
         <v>161154</v>
       </c>
       <c r="D6" t="n">
-        <v>21200</v>
+        <v>24900</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2442,11 +2442,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>15520</v>
+        <v>19220</v>
       </c>
     </row>
     <row r="7">
@@ -2522,15 +2522,15 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3980</v>
+        <v>10580</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>212.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1000</v>
+        <v>-5600</v>
       </c>
     </row>
     <row r="9">
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1792</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-1792</v>
       </c>
     </row>
     <row r="11">
@@ -2648,15 +2648,15 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10000</v>
+        <v>14150</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>139.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>160</v>
+        <v>-3990</v>
       </c>
     </row>
     <row r="12">
@@ -2758,31 +2758,31 @@
         <v>207051</v>
       </c>
       <c r="D14" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>55763</v>
+        <v>57263</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>373.2%</t>
+          <t>287.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-40823</v>
+        <v>-37343</v>
       </c>
     </row>
     <row r="15">
@@ -2942,15 +2942,15 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>25696</v>
+        <v>896</v>
       </c>
     </row>
     <row r="19">
@@ -2968,19 +2968,19 @@
         <v>291091</v>
       </c>
       <c r="D19" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>300.8%</t>
+          <t>150.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-10000</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="20">
@@ -3010,19 +3010,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>19920</v>
+        <v>14940</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3030,11 +3030,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15493.33</v>
+        <v>10513.33</v>
       </c>
     </row>
     <row r="21">
@@ -3052,19 +3052,19 @@
         <v>155796</v>
       </c>
       <c r="D21" t="n">
-        <v>14940</v>
+        <v>19920</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3072,11 +3072,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="22">
@@ -3110,15 +3110,15 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>9980</v>
+        <v>19980</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>100.3%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9940</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="23">
@@ -3136,19 +3136,19 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>36178</v>
+        <v>55978</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3156,11 +3156,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>26218</v>
+        <v>46018</v>
       </c>
     </row>
     <row r="24">
@@ -3220,31 +3220,31 @@
         <v>128563</v>
       </c>
       <c r="D25" t="n">
-        <v>44600</v>
+        <v>45396</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18800</v>
+        <v>32000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>25800</v>
+        <v>13396</v>
       </c>
     </row>
     <row r="26">
@@ -3346,19 +3346,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>6600</v>
+        <v>16600</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6600</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="29">
@@ -3556,19 +3556,19 @@
         <v>102098</v>
       </c>
       <c r="D33" t="n">
-        <v>34800</v>
+        <v>41400</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>34800</v>
+        <v>41400</v>
       </c>
     </row>
     <row r="34">
@@ -3780,11 +3780,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>61370</v>
+        <v>71370</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>61370</v>
+        <v>71370</v>
       </c>
     </row>
     <row r="3">
@@ -3814,23 +3814,23 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>281908</v>
+        <v>320804</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>58800</v>
+        <v>66300</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>223108</v>
+        <v>254504</v>
       </c>
     </row>
     <row r="4">
@@ -3848,11 +3848,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>93468</v>
+        <v>113268</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>93468</v>
+        <v>113268</v>
       </c>
     </row>
     <row r="5">
@@ -3916,11 +3916,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>28392</v>
+        <v>38392</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3928,11 +3928,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>26792</v>
+        <v>36792</v>
       </c>
     </row>
     <row r="7">
@@ -3950,23 +3950,23 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>16600</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="8">
@@ -3984,23 +3984,23 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>40090</v>
+        <v>61288</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>40090</v>
+        <v>59608</v>
       </c>
     </row>
     <row r="9">
@@ -4120,23 +4120,23 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>6592</v>
+        <v>7192</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6592</v>
+        <v>6794</v>
       </c>
     </row>
     <row r="13">
@@ -4154,11 +4154,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>22279.66999999998</v>
+        <v>26022.66999999998</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>22279.66999999998</v>
+        <v>26022.66999999998</v>
       </c>
     </row>
     <row r="14">
@@ -4188,11 +4188,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>42671.55</v>
+        <v>55467.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>42671.55</v>
+        <v>55467.55</v>
       </c>
     </row>
     <row r="15">
@@ -4222,11 +4222,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>75946</v>
+        <v>77660.29000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>75946</v>
+        <v>77660.29000000001</v>
       </c>
     </row>
     <row r="16">
@@ -4256,11 +4256,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>63906.2</v>
+        <v>84906.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>63906.2</v>
+        <v>84906.2</v>
       </c>
     </row>
     <row r="17">
@@ -4290,11 +4290,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>112331.61</v>
+        <v>115986.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>112331.61</v>
+        <v>115986.61</v>
       </c>
     </row>
     <row r="18">
@@ -4426,11 +4426,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>64606</v>
+        <v>42606</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>64606</v>
+        <v>42606</v>
       </c>
     </row>
     <row r="22">
@@ -4460,11 +4460,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>74349</v>
+        <v>80949</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>74349</v>
+        <v>80949</v>
       </c>
     </row>
     <row r="23">
@@ -4502,15 +4502,15 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>40980.32</v>
+        <v>40582.32</v>
       </c>
     </row>
     <row r="24">
@@ -4528,11 +4528,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>55419.88</v>
+        <v>55885.04</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>54623.88</v>
+        <v>55089.04</v>
       </c>
     </row>
     <row r="25">
@@ -4698,11 +4698,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>75154.2</v>
+        <v>86352.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>75154.2</v>
+        <v>86352.2</v>
       </c>
     </row>
     <row r="30">
@@ -4732,11 +4732,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>7700</v>
+        <v>9300</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4744,11 +4744,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>188.3%</t>
+          <t>155.9%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-6800</v>
+        <v>-5200</v>
       </c>
     </row>
     <row r="31">
@@ -4766,11 +4766,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>49696</v>
+        <v>51296</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4778,11 +4778,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>40196</v>
+        <v>41796</v>
       </c>
     </row>
     <row r="32">
@@ -5140,11 +5140,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>1200</v>
+        <v>1598</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5152,11 +5152,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>590.3%</t>
+          <t>443.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-5883.33</v>
+        <v>-5485.33</v>
       </c>
     </row>
     <row r="43">
@@ -5276,11 +5276,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>43792</v>
+        <v>54190</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>43792</v>
+        <v>54190</v>
       </c>
     </row>
     <row r="47">
@@ -5378,23 +5378,23 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>5398</v>
+        <v>5796</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5398</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="50">
@@ -5412,11 +5412,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>23668.15</v>
+        <v>24411.55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>23668.15</v>
+        <v>24411.55</v>
       </c>
     </row>
     <row r="51">
@@ -5480,11 +5480,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>46836.3</v>
+        <v>47234.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>46836.3</v>
+        <v>47234.3</v>
       </c>
     </row>
     <row r="53">
@@ -5582,11 +5582,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>21500</v>
+        <v>22300</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>21500</v>
+        <v>22300</v>
       </c>
     </row>
     <row r="56">
@@ -5650,11 +5650,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>30994</v>
+        <v>40994</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>30994</v>
+        <v>40994</v>
       </c>
     </row>
     <row r="58">
@@ -5684,11 +5684,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>30796</v>
+        <v>31194</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>30796</v>
+        <v>31194</v>
       </c>
     </row>
     <row r="59">
@@ -5718,11 +5718,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>65998</v>
+        <v>66396</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>64998</v>
+        <v>65396</v>
       </c>
     </row>
     <row r="60">
@@ -6033,16 +6033,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>670171.5699999999</v>
+        <v>782913.5699999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2264</v>
+        <v>2558</v>
       </c>
       <c r="E2" t="n">
-        <v>580961.5699999999</v>
+        <v>660550.5699999999</v>
       </c>
       <c r="F2" t="n">
-        <v>89210</v>
+        <v>122363</v>
       </c>
     </row>
     <row r="3">
@@ -6057,16 +6057,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>595051</v>
+        <v>697991</v>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E3" t="n">
-        <v>509131</v>
+        <v>579071</v>
       </c>
       <c r="F3" t="n">
-        <v>85920</v>
+        <v>118920</v>
       </c>
     </row>
     <row r="4">
@@ -6081,16 +6081,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75120.57000000001</v>
+        <v>84922.57000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>2151</v>
+        <v>2431</v>
       </c>
       <c r="E4" t="n">
-        <v>71830.57000000001</v>
+        <v>81479.57000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>3290</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="5">
@@ -6105,16 +6105,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1582374</v>
+        <v>1750946</v>
       </c>
       <c r="D5" t="n">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="E5" t="n">
-        <v>304784</v>
+        <v>316376</v>
       </c>
       <c r="F5" t="n">
-        <v>1277590</v>
+        <v>1434570</v>
       </c>
     </row>
     <row r="6">
@@ -6129,16 +6129,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1019916</v>
+        <v>1116106</v>
       </c>
       <c r="D6" t="n">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="E6" t="n">
-        <v>22000</v>
+        <v>32000</v>
       </c>
       <c r="F6" t="n">
-        <v>997916</v>
+        <v>1084106</v>
       </c>
     </row>
     <row r="7">
@@ -6153,16 +6153,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>532060</v>
+        <v>596442</v>
       </c>
       <c r="D7" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="E7" t="n">
-        <v>282784</v>
+        <v>284376</v>
       </c>
       <c r="F7" t="n">
-        <v>249276</v>
+        <v>312066</v>
       </c>
     </row>
     <row r="8">
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>685434.5</v>
+        <v>710791.84</v>
       </c>
       <c r="D8" t="n">
-        <v>807</v>
+        <v>896</v>
       </c>
       <c r="E8" t="n">
-        <v>31572.13</v>
+        <v>32427.1</v>
       </c>
       <c r="F8" t="n">
-        <v>653862.37</v>
+        <v>678364.74</v>
       </c>
     </row>
     <row r="9">
@@ -6201,16 +6201,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>434073.26</v>
+        <v>439387.6</v>
       </c>
       <c r="D9" t="n">
-        <v>449</v>
+        <v>493</v>
       </c>
       <c r="E9" t="n">
-        <v>1107.89</v>
+        <v>1962.86</v>
       </c>
       <c r="F9" t="n">
-        <v>432965.37</v>
+        <v>437424.74</v>
       </c>
     </row>
     <row r="10">
@@ -6225,16 +6225,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>251361.24</v>
+        <v>271404.24</v>
       </c>
       <c r="D10" t="n">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="E10" t="n">
         <v>30464.24</v>
       </c>
       <c r="F10" t="n">
-        <v>220897</v>
+        <v>240940</v>
       </c>
     </row>
     <row r="11">
@@ -6249,16 +6249,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>170600</v>
+        <v>178600</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
         <v>99200</v>
       </c>
       <c r="F11" t="n">
-        <v>71400</v>
+        <v>79400</v>
       </c>
     </row>
     <row r="12">
@@ -6273,16 +6273,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30000</v>
+        <v>30800</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>30000</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="13">
@@ -6345,16 +6345,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>190467.86</v>
+        <v>192442.86</v>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="E15" t="n">
-        <v>47776.36</v>
+        <v>48775.36</v>
       </c>
       <c r="F15" t="n">
-        <v>142691.5</v>
+        <v>143667.5</v>
       </c>
     </row>
   </sheetData>
@@ -6415,22 +6415,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>670171.5699999999</v>
+        <v>782913.5699999999</v>
       </c>
       <c r="C2" t="n">
-        <v>101119.04</v>
+        <v>132973.04</v>
       </c>
       <c r="D2" t="n">
-        <v>8248</v>
+        <v>8800</v>
       </c>
       <c r="E2" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="F2" t="n">
-        <v>92871.03999999999</v>
+        <v>124173.04</v>
       </c>
       <c r="G2" t="n">
-        <v>13.86</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="3">
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1582374</v>
+        <v>1750946</v>
       </c>
       <c r="C3" t="n">
-        <v>247521.33</v>
+        <v>279017.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6452,10 +6452,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>247521.33</v>
+        <v>279017.33</v>
       </c>
       <c r="G3" t="n">
-        <v>15.64</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="4">
@@ -6465,10 +6465,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>685434.5</v>
+        <v>710791.84</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6477,10 +6477,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="5">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>170600</v>
+        <v>178600</v>
       </c>
       <c r="C5" t="n">
-        <v>92200</v>
+        <v>117000</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6502,10 +6502,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>92200</v>
+        <v>117000</v>
       </c>
       <c r="G5" t="n">
-        <v>54.04</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30000</v>
+        <v>30800</v>
       </c>
       <c r="C6" t="n">
-        <v>57080</v>
+        <v>76054.88</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -6527,10 +6527,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>57080</v>
+        <v>76054.88</v>
       </c>
       <c r="G6" t="n">
-        <v>190.27</v>
+        <v>246.93</v>
       </c>
     </row>
     <row r="7">
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>150780</v>
+        <v>152280</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>150780</v>
+        <v>152280</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190467.86</v>
+        <v>192442.86</v>
       </c>
       <c r="C9" t="n">
-        <v>5611.75</v>
+        <v>6009.75</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6602,10 +6602,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5611.75</v>
+        <v>6009.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
     </row>
   </sheetData>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C2" t="n">
-        <v>354332.7</v>
+        <v>405099.58</v>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>129557</v>
+        <v>163537</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C4" t="n">
-        <v>69558.67</v>
+        <v>82532.67</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>47646.75</v>
+        <v>47722.75</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -6731,13 +6731,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>8979</v>
+        <v>20688</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>332</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6815,7 +6815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>102106</v>
+        <v>127680.88</v>
       </c>
     </row>
     <row r="3">
@@ -6902,14 +6902,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="6">
@@ -6920,14 +6920,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>385</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="7">
@@ -6938,32 +6938,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>97380</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -6974,14 +6974,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>27115.67</v>
+        <v>97380</v>
       </c>
     </row>
     <row r="10">
@@ -6992,14 +6992,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>4368</v>
+        <v>27134.67</v>
       </c>
     </row>
     <row r="11">
@@ -7010,14 +7010,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>1660</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="12">
@@ -7028,14 +7028,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>793</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="13">
@@ -7046,14 +7046,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>114</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="14">
@@ -7064,14 +7064,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -7082,32 +7082,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>65580</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -7118,14 +7118,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7200</v>
+        <v>77580</v>
       </c>
     </row>
     <row r="18">
@@ -7136,205 +7136,205 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3009</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>58809</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1619</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>29859</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D22" t="n">
-        <v>18073.7</v>
+        <v>16013.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D23" t="n">
-        <v>11989</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>7319</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>4979</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>4837.75</v>
+        <v>58809</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3605</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7347,163 +7347,163 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D30" t="n">
-        <v>19239</v>
+        <v>19044</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D31" t="n">
-        <v>15908.67</v>
+        <v>18630.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>10000</v>
+        <v>10636</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1268</v>
+        <v>4979</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D34" t="n">
-        <v>403</v>
+        <v>4856.75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>76</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>36800</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>19000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>11009</v>
+        <v>36800</v>
       </c>
     </row>
     <row r="39">
@@ -7514,20 +7514,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>3600</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>16000</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>10000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="42">
@@ -7568,56 +7568,56 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>7000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>10398</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>398</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7626,28 +7626,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>8000</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1200</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47">
@@ -7658,38 +7658,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>19</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>7083.33</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7698,16 +7698,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7719,31 +7719,31 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>6500</v>
+        <v>7083.33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3419</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7755,25 +7755,115 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3419</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>徐汇</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>主动放弃/拍错</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C56" t="n">
         <v>1</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D56" t="n">
         <v>598</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -7814,10 +7904,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>183781.33</v>
+        <v>214077.33</v>
       </c>
     </row>
     <row r="3">
@@ -7827,10 +7917,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>91200</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="4">
@@ -7840,10 +7930,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>85437.03999999999</v>
+        <v>95196.03999999999</v>
       </c>
     </row>
     <row r="5">
@@ -7862,27 +7952,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>65200</v>
+        <v>76054.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>57080</v>
+        <v>65200</v>
       </c>
     </row>
     <row r="8">
@@ -7905,36 +7995,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23100</v>
+        <v>26300</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>工作坊</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>6736</v>
+        <v>24840</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>工作坊</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>307</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>5390</v>
+        <v>7134</v>
       </c>
     </row>
   </sheetData>
@@ -7975,10 +8065,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>151719.33</v>
+        <v>151843.33</v>
       </c>
     </row>
     <row r="3">
@@ -7988,10 +8078,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>101670</v>
+        <v>114508</v>
       </c>
     </row>
     <row r="4">
@@ -8001,36 +8091,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>96965</v>
+        <v>96984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>62577</v>
+        <v>83489.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>49992.7</v>
+        <v>80634</v>
       </c>
     </row>
     <row r="7">
@@ -8040,10 +8130,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n">
-        <v>37337.67</v>
+        <v>42443.67</v>
       </c>
     </row>
     <row r="8">
@@ -8053,75 +8143,75 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>35693</v>
+        <v>35712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>18830</v>
+        <v>33051.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>14877</v>
+        <v>26668</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>12211</v>
+        <v>20816</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>11262.67</v>
+        <v>12211</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>10861</v>
+        <v>11262.67</v>
       </c>
     </row>
     <row r="14">
@@ -8131,10 +8221,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>10294</v>
+        <v>10749</v>
       </c>
     </row>
     <row r="15">
@@ -8144,10 +8234,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>7983</v>
+        <v>8032</v>
       </c>
     </row>
     <row r="16">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -528,41 +528,41 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>302066</v>
+        <v>340226</v>
       </c>
       <c r="E2" t="n">
-        <v>61855</v>
+        <v>67842</v>
       </c>
       <c r="F2" t="n">
-        <v>240210</v>
+        <v>272384</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>236512</v>
+        <v>348152</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+27.7%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>159157</v>
+        <v>266817</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+50.9%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,41 +585,41 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>123695</v>
+        <v>138330</v>
       </c>
       <c r="E3" t="n">
-        <v>139092</v>
+        <v>162419</v>
       </c>
       <c r="F3" t="n">
-        <v>-15397</v>
+        <v>-24089</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>325800</v>
+        <v>348678</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-62.0%</t>
+          <t>-60.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>204437</v>
+        <v>217355</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-107.5%</t>
+          <t>-111.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -642,41 +642,41 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>335421</v>
+        <v>390108</v>
       </c>
       <c r="E4" t="n">
-        <v>82496</v>
+        <v>84677</v>
       </c>
       <c r="F4" t="n">
-        <v>252925</v>
+        <v>305431</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>354943</v>
+        <v>392241</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>333743</v>
+        <v>371041</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -699,41 +699,41 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>396147</v>
+        <v>484621</v>
       </c>
       <c r="E5" t="n">
-        <v>184917</v>
+        <v>204997</v>
       </c>
       <c r="F5" t="n">
-        <v>211230</v>
+        <v>279624</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1129059</v>
+        <v>1160489</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-64.9%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>748179</v>
+        <v>766409</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-63.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -756,50 +756,50 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>623808</v>
+        <v>742475</v>
       </c>
       <c r="E6" t="n">
-        <v>36800</v>
+        <v>47800</v>
       </c>
       <c r="F6" t="n">
-        <v>587008</v>
+        <v>694675</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>906020</v>
+        <v>918831</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>906020</v>
+        <v>918831</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>228667</v>
+        <v>273665</v>
       </c>
       <c r="P6" t="n">
-        <v>358341</v>
+        <v>421010</v>
       </c>
       <c r="Q6" t="n">
-        <v>546212</v>
+        <v>664879</v>
       </c>
     </row>
     <row r="7">
@@ -817,50 +817,50 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>58154</v>
+        <v>79028</v>
       </c>
       <c r="E7" t="n">
-        <v>3438</v>
+        <v>5438</v>
       </c>
       <c r="F7" t="n">
-        <v>54716</v>
+        <v>73590</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>143619</v>
+        <v>157832</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-59.5%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>117219</v>
+        <v>131432</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-44.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>45903</v>
+        <v>56388</v>
       </c>
       <c r="P7" t="n">
-        <v>8813</v>
+        <v>17202</v>
       </c>
       <c r="Q7" t="n">
-        <v>18336</v>
+        <v>18812</v>
       </c>
     </row>
     <row r="8">
@@ -878,50 +878,50 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>268393</v>
+        <v>278412</v>
       </c>
       <c r="E8" t="n">
-        <v>1000</v>
+        <v>2680</v>
       </c>
       <c r="F8" t="n">
-        <v>267393</v>
+        <v>275732</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>281035</v>
+        <v>283450</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>257978</v>
+        <v>260374</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+3.6%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>29803</v>
+        <v>28142</v>
       </c>
       <c r="P8" t="n">
-        <v>237590</v>
+        <v>247590</v>
       </c>
       <c r="Q8" t="n">
-        <v>52817</v>
+        <v>51156</v>
       </c>
     </row>
     <row r="9">
@@ -939,52 +939,52 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>227629</v>
+        <v>231627</v>
       </c>
       <c r="E9" t="n">
         <v>33000</v>
       </c>
       <c r="F9" t="n">
-        <v>194629</v>
+        <v>198627</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>300521</v>
+        <v>327727</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>274594</v>
+        <v>282799</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>15077</v>
+        <v>18658</v>
       </c>
       <c r="O9" t="n">
-        <v>53520</v>
+        <v>53937</v>
       </c>
       <c r="P9" t="n">
         <v>126031</v>
       </c>
       <c r="Q9" t="n">
-        <v>25949</v>
+        <v>29549</v>
       </c>
     </row>
     <row r="10">
@@ -1002,52 +1002,52 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>62083</v>
+        <v>62520</v>
       </c>
       <c r="E10" t="n">
-        <v>87789</v>
+        <v>97789</v>
       </c>
       <c r="F10" t="n">
-        <v>-25706</v>
+        <v>-35269</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>117290</v>
+        <v>117780</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>102424</v>
+        <v>102914</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-125.1%</t>
+          <t>-134.3%</t>
         </is>
       </c>
       <c r="N10" t="n">
         <v>6355</v>
       </c>
       <c r="O10" t="n">
-        <v>-47469</v>
+        <v>-57430</v>
       </c>
       <c r="P10" t="n">
-        <v>15408</v>
+        <v>15806</v>
       </c>
       <c r="Q10" t="n">
-        <v>-32090</v>
+        <v>-31653</v>
       </c>
     </row>
     <row r="11">
@@ -1065,47 +1065,47 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>19068</v>
+        <v>34466</v>
       </c>
       <c r="E11" t="n">
         <v>7121</v>
       </c>
       <c r="F11" t="n">
-        <v>11947</v>
+        <v>27345</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>88081</v>
+        <v>88479</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-61.0%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>72224</v>
+        <v>72622</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-83.5%</t>
+          <t>-62.3%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>-7007</v>
+        <v>-6609</v>
       </c>
       <c r="P11" t="n">
-        <v>18954</v>
+        <v>33954</v>
       </c>
       <c r="Q11" t="n">
         <v>3436</v>
@@ -1126,13 +1126,13 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>231060</v>
+        <v>231031</v>
       </c>
       <c r="E12" t="n">
         <v>10419</v>
       </c>
       <c r="F12" t="n">
-        <v>220641</v>
+        <v>220612</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -1146,30 +1146,30 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>197885</v>
+        <v>225302</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+16.8%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>197487</v>
+        <v>216104</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+11.7%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>53451</v>
+        <v>53422</v>
       </c>
       <c r="P12" t="n">
         <v>167190</v>
       </c>
       <c r="Q12" t="n">
-        <v>91467</v>
+        <v>91438</v>
       </c>
     </row>
     <row r="13">
@@ -1187,52 +1187,52 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>105466</v>
+        <v>129014</v>
       </c>
       <c r="E13" t="n">
         <v>11194</v>
       </c>
       <c r="F13" t="n">
-        <v>94272</v>
+        <v>117820</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>229895</v>
+        <v>289091</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-54.1%</t>
+          <t>-55.4%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>183295</v>
+        <v>242291</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-48.6%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>12385</v>
+        <v>22385</v>
       </c>
       <c r="O13" t="n">
         <v>13205</v>
       </c>
       <c r="P13" t="n">
-        <v>68682</v>
+        <v>82230</v>
       </c>
       <c r="Q13" t="n">
-        <v>24410</v>
+        <v>39360</v>
       </c>
     </row>
     <row r="14">
@@ -1250,52 +1250,52 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>625444</v>
+        <v>715178</v>
       </c>
       <c r="E14" t="n">
-        <v>67947</v>
+        <v>93547</v>
       </c>
       <c r="F14" t="n">
-        <v>557497</v>
+        <v>621631</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>640689</v>
+        <v>686667</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>621032</v>
+        <v>660410</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>21200</v>
       </c>
       <c r="O14" t="n">
-        <v>117974</v>
+        <v>95412</v>
       </c>
       <c r="P14" t="n">
-        <v>418323</v>
+        <v>505019</v>
       </c>
       <c r="Q14" t="n">
-        <v>202025</v>
+        <v>259159</v>
       </c>
     </row>
     <row r="15">
@@ -1313,39 +1313,39 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>196473</v>
+        <v>214769</v>
       </c>
       <c r="E15" t="n">
         <v>33609</v>
       </c>
       <c r="F15" t="n">
-        <v>162864</v>
+        <v>181160</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>171792</v>
+        <v>183273</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+14.4%</t>
+          <t>+17.2%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>171583</v>
+        <v>183064</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1355,10 +1355,10 @@
         <v>51586</v>
       </c>
       <c r="P15" t="n">
-        <v>72492</v>
+        <v>90788</v>
       </c>
       <c r="Q15" t="n">
-        <v>39184</v>
+        <v>39582</v>
       </c>
     </row>
     <row r="16">
@@ -1376,50 +1376,50 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>81488</v>
+        <v>83487</v>
       </c>
       <c r="E16" t="n">
-        <v>2676</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="n">
-        <v>78812</v>
+        <v>77211</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>250587</v>
+        <v>261127</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-68.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>209765</v>
+        <v>220286</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-62.4%</t>
+          <t>-64.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>29385</v>
+        <v>31384</v>
       </c>
       <c r="P16" t="n">
-        <v>49427</v>
+        <v>45827</v>
       </c>
       <c r="Q16" t="n">
-        <v>7134</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="17">
@@ -1502,7 +1502,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>1498593</v>
+        <v>1763897</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>975257</v>
+        <v>1182779</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-100.7%</t>
+          <t>-100.5%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1543,54 +1543,54 @@
         <v>17200000</v>
       </c>
       <c r="D19" t="n">
-        <v>3656394</v>
+        <v>4155291</v>
       </c>
       <c r="E19" t="n">
-        <v>769853</v>
+        <v>875309</v>
       </c>
       <c r="F19" t="n">
-        <v>2886541</v>
+        <v>3279982</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6872322</v>
+        <v>7553017</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-45.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5534394</v>
+        <v>6095530</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-46.2%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>93803</v>
+        <v>107384</v>
       </c>
       <c r="O19" t="n">
-        <v>1176747</v>
+        <v>1342950</v>
       </c>
       <c r="P19" t="n">
-        <v>1615990</v>
+        <v>1829649</v>
       </c>
       <c r="Q19" t="n">
-        <v>1453010</v>
+        <v>1731045</v>
       </c>
     </row>
   </sheetData>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>449420</v>
+        <v>529743</v>
       </c>
       <c r="D2" t="n">
-        <v>28318</v>
+        <v>23981</v>
       </c>
       <c r="E2" t="n">
-        <v>390672</v>
+        <v>427839</v>
       </c>
     </row>
     <row r="3">
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>164810</v>
+        <v>226604</v>
       </c>
       <c r="D3" t="n">
-        <v>46420</v>
+        <v>53020</v>
       </c>
       <c r="E3" t="n">
-        <v>83458</v>
+        <v>128954</v>
       </c>
     </row>
     <row r="4">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>569017</v>
+        <v>593101</v>
       </c>
       <c r="D4" t="n">
-        <v>1541250</v>
+        <v>1752646</v>
       </c>
       <c r="E4" t="n">
-        <v>978879</v>
+        <v>1174249</v>
       </c>
     </row>
     <row r="5">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>222528</v>
+        <v>249039</v>
       </c>
       <c r="D5" t="n">
-        <v>17682</v>
+        <v>23345</v>
       </c>
       <c r="E5" t="n">
-        <v>185828</v>
+        <v>218002</v>
       </c>
     </row>
     <row r="6">
@@ -1828,13 +1828,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-16015</v>
+        <v>-24707</v>
       </c>
       <c r="D6" t="n">
         <v>618</v>
       </c>
       <c r="E6" t="n">
-        <v>1709</v>
+        <v>-6983</v>
       </c>
     </row>
     <row r="7">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>242906</v>
+        <v>305412</v>
       </c>
       <c r="D7" t="n">
-        <v>10019</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>203135</v>
+        <v>216821</v>
       </c>
     </row>
     <row r="8">
@@ -1870,13 +1870,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>164810</v>
+        <v>226604</v>
       </c>
       <c r="D8" t="n">
-        <v>46420</v>
+        <v>53020</v>
       </c>
       <c r="E8" t="n">
-        <v>83458</v>
+        <v>128954</v>
       </c>
     </row>
     <row r="9">
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>228667</v>
+        <v>273665</v>
       </c>
       <c r="D9" t="n">
-        <v>358341</v>
+        <v>421010</v>
       </c>
       <c r="E9" t="n">
-        <v>546212</v>
+        <v>664879</v>
       </c>
     </row>
     <row r="10">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45903</v>
+        <v>56388</v>
       </c>
       <c r="D10" t="n">
-        <v>8813</v>
+        <v>17202</v>
       </c>
       <c r="E10" t="n">
-        <v>18336</v>
+        <v>18812</v>
       </c>
     </row>
     <row r="11">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29803</v>
+        <v>28142</v>
       </c>
       <c r="D11" t="n">
-        <v>237590</v>
+        <v>247590</v>
       </c>
       <c r="E11" t="n">
-        <v>52817</v>
+        <v>51156</v>
       </c>
     </row>
     <row r="12">
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>53520</v>
+        <v>53937</v>
       </c>
       <c r="D12" t="n">
         <v>126031</v>
       </c>
       <c r="E12" t="n">
-        <v>25949</v>
+        <v>29549</v>
       </c>
     </row>
     <row r="13">
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-47469</v>
+        <v>-57430</v>
       </c>
       <c r="D13" t="n">
-        <v>15408</v>
+        <v>15806</v>
       </c>
       <c r="E13" t="n">
-        <v>-32090</v>
+        <v>-31653</v>
       </c>
     </row>
     <row r="14">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-7007</v>
+        <v>-6609</v>
       </c>
       <c r="D14" t="n">
-        <v>18954</v>
+        <v>33954</v>
       </c>
       <c r="E14" t="n">
         <v>3436</v>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53451</v>
+        <v>53422</v>
       </c>
       <c r="D15" t="n">
         <v>167190</v>
       </c>
       <c r="E15" t="n">
-        <v>91467</v>
+        <v>91438</v>
       </c>
     </row>
     <row r="16">
@@ -2041,10 +2041,10 @@
         <v>13205</v>
       </c>
       <c r="D16" t="n">
-        <v>68682</v>
+        <v>82230</v>
       </c>
       <c r="E16" t="n">
-        <v>24410</v>
+        <v>39360</v>
       </c>
     </row>
     <row r="17">
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>117974</v>
+        <v>95412</v>
       </c>
       <c r="D17" t="n">
-        <v>418323</v>
+        <v>505019</v>
       </c>
       <c r="E17" t="n">
-        <v>202025</v>
+        <v>259159</v>
       </c>
     </row>
     <row r="18">
@@ -2083,10 +2083,10 @@
         <v>51586</v>
       </c>
       <c r="D18" t="n">
-        <v>72492</v>
+        <v>90788</v>
       </c>
       <c r="E18" t="n">
-        <v>39184</v>
+        <v>39582</v>
       </c>
     </row>
     <row r="19">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>29385</v>
+        <v>31384</v>
       </c>
       <c r="D19" t="n">
-        <v>49427</v>
+        <v>45827</v>
       </c>
       <c r="E19" t="n">
-        <v>7134</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="20">
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1176747</v>
+        <v>1342950</v>
       </c>
       <c r="D22" t="n">
-        <v>1615990</v>
+        <v>1829649</v>
       </c>
       <c r="E22" t="n">
-        <v>1453010</v>
+        <v>1731045</v>
       </c>
     </row>
   </sheetData>
@@ -2254,19 +2254,19 @@
         <v>312912</v>
       </c>
       <c r="D2" t="n">
-        <v>80372</v>
+        <v>93333</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2274,11 +2274,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>66880.3</v>
+        <v>79841.3</v>
       </c>
     </row>
     <row r="3">
@@ -2522,15 +2522,15 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10580</v>
+        <v>14560</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>212.4%</t>
+          <t>292.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-5600</v>
+        <v>-9580</v>
       </c>
     </row>
     <row r="9">
@@ -2548,31 +2548,31 @@
         <v>333616</v>
       </c>
       <c r="D9" t="n">
-        <v>42936</v>
+        <v>47916</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>53896.67</v>
+        <v>73696.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>153.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-10960.67</v>
+        <v>-25780.67</v>
       </c>
     </row>
     <row r="10">
@@ -2648,15 +2648,15 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14150</v>
+        <v>17466.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>139.3%</t>
+          <t>171.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-3990</v>
+        <v>-7306.700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2842,19 +2842,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>34900</v>
+        <v>73720</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>34900</v>
+        <v>73720</v>
       </c>
     </row>
     <row r="17">
@@ -2884,19 +2884,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>89054</v>
+        <v>92854</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2904,11 +2904,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>84489</v>
+        <v>88289</v>
       </c>
     </row>
     <row r="18">
@@ -2926,19 +2926,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>25696</v>
+        <v>35696</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2946,11 +2946,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>896</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="19">
@@ -3010,31 +3010,31 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>14940</v>
+        <v>21540</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4426.67</v>
+        <v>4626.67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10513.33</v>
+        <v>16913.33</v>
       </c>
     </row>
     <row r="21">
@@ -3136,31 +3136,31 @@
         <v>265322</v>
       </c>
       <c r="D23" t="n">
-        <v>55978</v>
+        <v>74158</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>46018</v>
+        <v>59218</v>
       </c>
     </row>
     <row r="24">
@@ -3304,19 +3304,19 @@
         <v>192375</v>
       </c>
       <c r="D27" t="n">
-        <v>66400</v>
+        <v>106000</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3324,11 +3324,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>57400</v>
+        <v>97000</v>
       </c>
     </row>
     <row r="28">
@@ -3346,19 +3346,19 @@
         <v>102098</v>
       </c>
       <c r="D28" t="n">
-        <v>16600</v>
+        <v>36600</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>16600</v>
+        <v>36600</v>
       </c>
     </row>
     <row r="29">
@@ -3430,31 +3430,31 @@
         <v>139041</v>
       </c>
       <c r="D30" t="n">
-        <v>25200</v>
+        <v>25598</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>25200</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="31">
@@ -3488,15 +3488,15 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4000</v>
+        <v>11500</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>20088</v>
+        <v>12588</v>
       </c>
     </row>
     <row r="32">
@@ -3514,19 +3514,19 @@
         <v>102098</v>
       </c>
       <c r="D32" t="n">
-        <v>43800</v>
+        <v>53800</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>43800</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="33">
@@ -3814,11 +3814,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>320804</v>
+        <v>400500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3826,11 +3826,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>254504</v>
+        <v>334200</v>
       </c>
     </row>
     <row r="4">
@@ -3848,23 +3848,23 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>113268</v>
+        <v>123268</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>113268</v>
+        <v>120268</v>
       </c>
     </row>
     <row r="5">
@@ -3924,15 +3924,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1600</v>
+        <v>22400</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36792</v>
+        <v>15992</v>
       </c>
     </row>
     <row r="7">
@@ -4060,15 +4060,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>251.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1194</v>
+        <v>-1806</v>
       </c>
     </row>
     <row r="11">
@@ -4120,23 +4120,23 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>7192</v>
+        <v>9172</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>398</v>
+        <v>998</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6794</v>
+        <v>8174</v>
       </c>
     </row>
     <row r="13">
@@ -4222,11 +4222,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>77660.29000000001</v>
+        <v>98086.29000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>77660.29000000001</v>
+        <v>98086.29000000001</v>
       </c>
     </row>
     <row r="16">
@@ -4256,11 +4256,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>84906.2</v>
+        <v>93996.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>84906.2</v>
+        <v>93996.2</v>
       </c>
     </row>
     <row r="17">
@@ -4290,11 +4290,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>115986.61</v>
+        <v>167786.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>115986.61</v>
+        <v>167786.61</v>
       </c>
     </row>
     <row r="18">
@@ -4392,11 +4392,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>128100.6</v>
+        <v>153676.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>128100.6</v>
+        <v>153676.6</v>
       </c>
     </row>
     <row r="21">
@@ -4426,11 +4426,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>42606</v>
+        <v>47550</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>42606</v>
+        <v>47550</v>
       </c>
     </row>
     <row r="22">
@@ -4460,11 +4460,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>80949</v>
+        <v>87761</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>80949</v>
+        <v>87761</v>
       </c>
     </row>
     <row r="23">
@@ -4528,11 +4528,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>55885.04</v>
+        <v>65885.03999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4540,11 +4540,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>55089.04</v>
+        <v>65089.03999999999</v>
       </c>
     </row>
     <row r="25">
@@ -4596,11 +4596,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>398</v>
+        <v>996</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>398</v>
+        <v>996</v>
       </c>
     </row>
     <row r="27">
@@ -4630,11 +4630,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>3796</v>
+        <v>11796</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3796</v>
+        <v>11796</v>
       </c>
     </row>
     <row r="28">
@@ -4664,11 +4664,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>598</v>
+        <v>5548</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>598</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="29">
@@ -4698,11 +4698,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>86352.2</v>
+        <v>88163.62</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>86352.2</v>
+        <v>88163.62</v>
       </c>
     </row>
     <row r="30">
@@ -4800,11 +4800,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>30896</v>
+        <v>31920.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>30896</v>
+        <v>31920.8</v>
       </c>
     </row>
     <row r="33">
@@ -4834,11 +4834,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>17796</v>
+        <v>18938.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4846,11 +4846,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9296</v>
+        <v>10438.6</v>
       </c>
     </row>
     <row r="34">
@@ -4944,15 +4944,15 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>438.8%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2278.9</v>
+        <v>-7721.1</v>
       </c>
     </row>
     <row r="37">
@@ -4970,11 +4970,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>20000</v>
+        <v>20398</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4982,11 +4982,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>16040</v>
+        <v>16438</v>
       </c>
     </row>
     <row r="38">
@@ -5174,11 +5174,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>6680</v>
+        <v>21680</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6680</v>
+        <v>21680</v>
       </c>
     </row>
     <row r="44">
@@ -5208,11 +5208,11 @@
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>8996</v>
+        <v>9394</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8996</v>
+        <v>9394</v>
       </c>
     </row>
     <row r="45">
@@ -5412,11 +5412,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>24411.55</v>
+        <v>24809.55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>24411.55</v>
+        <v>24809.55</v>
       </c>
     </row>
     <row r="51">
@@ -5446,11 +5446,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>33564.8</v>
+        <v>43962.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5458,11 +5458,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>21964.8</v>
+        <v>32362.8</v>
       </c>
     </row>
     <row r="52">
@@ -5548,11 +5548,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>10972.7</v>
+        <v>18472.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>10972.7</v>
+        <v>18472.7</v>
       </c>
     </row>
     <row r="55">
@@ -5658,15 +5658,15 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>40994</v>
+        <v>39314</v>
       </c>
     </row>
     <row r="58">
@@ -5718,11 +5718,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>66396</v>
+        <v>76396</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5730,11 +5730,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>65396</v>
+        <v>75396</v>
       </c>
     </row>
     <row r="60">
@@ -5854,23 +5854,23 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>43190</v>
+        <v>53190</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3400</v>
+        <v>5400</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>39790</v>
+        <v>47790</v>
       </c>
     </row>
     <row r="64">
@@ -5956,11 +5956,11 @@
         <v>40000</v>
       </c>
       <c r="D66" t="n">
-        <v>1594</v>
+        <v>11992</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1594</v>
+        <v>11992</v>
       </c>
     </row>
   </sheetData>
@@ -6033,16 +6033,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>782913.5699999999</v>
+        <v>922904.5699999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2558</v>
+        <v>2964</v>
       </c>
       <c r="E2" t="n">
-        <v>660550.5699999999</v>
+        <v>766447.5699999999</v>
       </c>
       <c r="F2" t="n">
-        <v>122363</v>
+        <v>156457</v>
       </c>
     </row>
     <row r="3">
@@ -6057,16 +6057,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>697991</v>
+        <v>825942</v>
       </c>
       <c r="D3" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="E3" t="n">
-        <v>579071</v>
+        <v>673032</v>
       </c>
       <c r="F3" t="n">
-        <v>118920</v>
+        <v>152910</v>
       </c>
     </row>
     <row r="4">
@@ -6081,16 +6081,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84922.57000000001</v>
+        <v>96962.57000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>2431</v>
+        <v>2817</v>
       </c>
       <c r="E4" t="n">
-        <v>81479.57000000001</v>
+        <v>93415.57000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>3443</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="5">
@@ -6105,16 +6105,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1750946</v>
+        <v>1912854</v>
       </c>
       <c r="D5" t="n">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="E5" t="n">
-        <v>316376</v>
+        <v>385594</v>
       </c>
       <c r="F5" t="n">
-        <v>1434570</v>
+        <v>1527260</v>
       </c>
     </row>
     <row r="6">
@@ -6129,16 +6129,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1116106</v>
+        <v>1177602</v>
       </c>
       <c r="D6" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E6" t="n">
-        <v>32000</v>
+        <v>22000</v>
       </c>
       <c r="F6" t="n">
-        <v>1084106</v>
+        <v>1155602</v>
       </c>
     </row>
     <row r="7">
@@ -6153,16 +6153,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>596442</v>
+        <v>686854</v>
       </c>
       <c r="D7" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E7" t="n">
-        <v>284376</v>
+        <v>363594</v>
       </c>
       <c r="F7" t="n">
-        <v>312066</v>
+        <v>323260</v>
       </c>
     </row>
     <row r="8">
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>710791.84</v>
+        <v>835657.71</v>
       </c>
       <c r="D8" t="n">
-        <v>896</v>
+        <v>1032</v>
       </c>
       <c r="E8" t="n">
-        <v>32427.1</v>
+        <v>34268.31</v>
       </c>
       <c r="F8" t="n">
-        <v>678364.74</v>
+        <v>801389.4</v>
       </c>
     </row>
     <row r="9">
@@ -6201,16 +6201,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>439387.6</v>
+        <v>517802.98</v>
       </c>
       <c r="D9" t="n">
-        <v>493</v>
+        <v>558</v>
       </c>
       <c r="E9" t="n">
-        <v>1962.86</v>
+        <v>2625.58</v>
       </c>
       <c r="F9" t="n">
-        <v>437424.74</v>
+        <v>515177.4</v>
       </c>
     </row>
     <row r="10">
@@ -6225,16 +6225,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>271404.24</v>
+        <v>317854.73</v>
       </c>
       <c r="D10" t="n">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="E10" t="n">
-        <v>30464.24</v>
+        <v>31642.73</v>
       </c>
       <c r="F10" t="n">
-        <v>240940</v>
+        <v>286212</v>
       </c>
     </row>
     <row r="11">
@@ -6249,16 +6249,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>178600</v>
+        <v>224200</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
         <v>99200</v>
       </c>
       <c r="F11" t="n">
-        <v>79400</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="12">
@@ -6273,13 +6273,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30800</v>
+        <v>34600</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F12" t="n">
         <v>30800</v>
@@ -6297,16 +6297,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>5940</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="14">
@@ -6345,16 +6345,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>192442.86</v>
+        <v>209234.86</v>
       </c>
       <c r="D15" t="n">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="E15" t="n">
-        <v>48775.36</v>
+        <v>63975.36</v>
       </c>
       <c r="F15" t="n">
-        <v>143667.5</v>
+        <v>145259.5</v>
       </c>
     </row>
   </sheetData>
@@ -6415,22 +6415,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>782913.5699999999</v>
+        <v>922904.5699999999</v>
       </c>
       <c r="C2" t="n">
-        <v>132973.04</v>
+        <v>156150.74</v>
       </c>
       <c r="D2" t="n">
-        <v>8800</v>
+        <v>9511</v>
       </c>
       <c r="E2" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="F2" t="n">
-        <v>124173.04</v>
+        <v>146639.74</v>
       </c>
       <c r="G2" t="n">
-        <v>15.86</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="3">
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1750946</v>
+        <v>1912854</v>
       </c>
       <c r="C3" t="n">
-        <v>279017.33</v>
+        <v>315517.33</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6452,10 +6452,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>279017.33</v>
+        <v>315517.33</v>
       </c>
       <c r="G3" t="n">
-        <v>15.94</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="4">
@@ -6465,22 +6465,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>710791.84</v>
+        <v>835657.71</v>
       </c>
       <c r="C4" t="n">
-        <v>578</v>
+        <v>3178</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>578</v>
+        <v>2578</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="5">
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>178600</v>
+        <v>224200</v>
       </c>
       <c r="C5" t="n">
-        <v>117000</v>
+        <v>138800</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6502,10 +6502,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>117000</v>
+        <v>138800</v>
       </c>
       <c r="G5" t="n">
-        <v>65.51000000000001</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="6">
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30800</v>
+        <v>34600</v>
       </c>
       <c r="C6" t="n">
-        <v>76054.88</v>
+        <v>77633.17999999999</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -6527,10 +6527,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>76054.88</v>
+        <v>77633.17999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>246.93</v>
+        <v>224.37</v>
       </c>
     </row>
     <row r="7">
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>5940</v>
       </c>
       <c r="C7" t="n">
-        <v>152280</v>
+        <v>172080</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6552,10 +6552,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>152280</v>
+        <v>172080</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2896.97</v>
       </c>
     </row>
     <row r="8">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192442.86</v>
+        <v>209234.86</v>
       </c>
       <c r="C9" t="n">
         <v>6009.75</v>
@@ -6605,7 +6605,7 @@
         <v>6009.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
     </row>
   </sheetData>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C2" t="n">
-        <v>405099.58</v>
+        <v>458852.58</v>
       </c>
       <c r="D2" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>163537</v>
+        <v>193937</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -6683,45 +6683,45 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C4" t="n">
-        <v>82532.67</v>
+        <v>87559.67</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>47722.75</v>
+        <v>51700</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>42200</v>
+        <v>49386.05</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -6731,13 +6731,13 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>24004.7</v>
+      </c>
+      <c r="D7" t="n">
         <v>7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>20688</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -6747,13 +6747,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>4103</v>
+        <v>5880</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6815,7 +6815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>127680.88</v>
+        <v>132660.88</v>
       </c>
     </row>
     <row r="3">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>16800</v>
+        <v>24400</v>
       </c>
     </row>
     <row r="5">
@@ -6902,14 +6902,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6600</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="6">
@@ -6920,14 +6920,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="7">
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>97380</v>
+        <v>117180</v>
       </c>
     </row>
     <row r="10">
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>27134.67</v>
+        <v>27191.67</v>
       </c>
     </row>
     <row r="11">
@@ -7010,14 +7010,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>6510</v>
+        <v>6768.7</v>
       </c>
     </row>
     <row r="12">
@@ -7028,14 +7028,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>4368</v>
+        <v>6586</v>
       </c>
     </row>
     <row r="13">
@@ -7046,14 +7046,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>3452</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="14">
@@ -7064,14 +7064,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
@@ -7082,14 +7082,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>77580</v>
+        <v>87580</v>
       </c>
     </row>
     <row r="18">
@@ -7167,73 +7167,73 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>34800</v>
+        <v>81409</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>29859</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>16013.67</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1325</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -7244,14 +7244,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>403</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="25">
@@ -7262,86 +7262,86 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D25" t="n">
-        <v>95</v>
+        <v>30196</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="D26" t="n">
-        <v>58809</v>
+        <v>16213.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>7500</v>
+        <v>2931.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>1619</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D30" t="n">
-        <v>19044</v>
+        <v>23195</v>
       </c>
     </row>
     <row r="31">
@@ -7374,10 +7374,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D31" t="n">
-        <v>18630.7</v>
+        <v>18729.7</v>
       </c>
     </row>
     <row r="32">
@@ -7406,14 +7406,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>4979</v>
+        <v>5304</v>
       </c>
     </row>
     <row r="34">
@@ -7424,14 +7424,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>4856.75</v>
+        <v>4979</v>
       </c>
     </row>
     <row r="35">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D35" t="n">
-        <v>3605</v>
+        <v>4894.75</v>
       </c>
     </row>
     <row r="36">
@@ -7509,19 +7509,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>19000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="40">
@@ -7532,14 +7532,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>11009</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="41">
@@ -7550,32 +7550,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>3600</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>16000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="43">
@@ -7586,14 +7586,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>10000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="44">
@@ -7604,32 +7604,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>7000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>10796</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="46">
@@ -7640,32 +7640,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>398</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>9200</v>
+        <v>398</v>
       </c>
     </row>
     <row r="48">
@@ -7676,14 +7676,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>1200</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="49">
@@ -7694,32 +7694,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>7083.33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
@@ -7730,38 +7730,38 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>38</v>
+        <v>7083.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>6500</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7770,28 +7770,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>3419</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>19</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="55">
@@ -7824,16 +7824,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>598</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7842,28 +7842,64 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>398</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1000</v>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2680</v>
       </c>
     </row>
   </sheetData>
@@ -7904,10 +7940,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>214077.33</v>
+        <v>250577.33</v>
       </c>
     </row>
     <row r="3">
@@ -7917,10 +7953,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>116000</v>
+        <v>137800</v>
       </c>
     </row>
     <row r="4">
@@ -7930,49 +7966,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>95196.03999999999</v>
+        <v>107472.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>83600</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>76054.88</v>
+        <v>83600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>65200</v>
+        <v>76054.88</v>
       </c>
     </row>
     <row r="8">
@@ -7991,27 +8027,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26300</v>
+        <v>33120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>24840</v>
+        <v>27100</v>
       </c>
     </row>
     <row r="11">
@@ -8065,10 +8101,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>151843.33</v>
+        <v>174409.33</v>
       </c>
     </row>
     <row r="3">
@@ -8078,10 +8114,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>114508</v>
+        <v>132165</v>
       </c>
     </row>
     <row r="4">
@@ -8091,10 +8127,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>96984</v>
+        <v>98664</v>
       </c>
     </row>
     <row r="5">
@@ -8104,10 +8140,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>83489.7</v>
+        <v>87350.7</v>
       </c>
     </row>
     <row r="6">
@@ -8117,10 +8153,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>80634</v>
+        <v>83691</v>
       </c>
     </row>
     <row r="7">
@@ -8130,10 +8166,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n">
-        <v>42443.67</v>
+        <v>42471.67</v>
       </c>
     </row>
     <row r="8">
@@ -8143,10 +8179,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>35712</v>
+        <v>39855</v>
       </c>
     </row>
     <row r="9">
@@ -8156,101 +8192,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33051.88</v>
+        <v>34089.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>26668</v>
+        <v>32011</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>20816</v>
+        <v>26782</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>12211</v>
+        <v>22664</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>11262.67</v>
+        <v>18287</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>10749</v>
+        <v>15531</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>8032</v>
+        <v>14598.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>7150</v>
+        <v>8032</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -535,10 +535,10 @@
         <v>5330</v>
       </c>
       <c r="E2" t="n">
-        <v>1313</v>
+        <v>77275</v>
       </c>
       <c r="F2" t="n">
-        <v>4017</v>
+        <v>-71945</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-98.8%</t>
+          <t>-122.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -592,10 +592,10 @@
         <v>1915</v>
       </c>
       <c r="E3" t="n">
-        <v>248</v>
+        <v>177625</v>
       </c>
       <c r="F3" t="n">
-        <v>1667</v>
+        <v>-175710</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-99.2%</t>
+          <t>-184.8%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -649,10 +649,10 @@
         <v>4837</v>
       </c>
       <c r="E4" t="n">
-        <v>524</v>
+        <v>94905</v>
       </c>
       <c r="F4" t="n">
-        <v>4313</v>
+        <v>-90068</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -680,7 +680,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-98.9%</t>
+          <t>-123.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -706,10 +706,10 @@
         <v>732</v>
       </c>
       <c r="E5" t="n">
-        <v>299</v>
+        <v>235996</v>
       </c>
       <c r="F5" t="n">
-        <v>433</v>
+        <v>-235264</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -737,7 +737,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-125.7%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -763,10 +763,10 @@
         <v>752468</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>47800</v>
       </c>
       <c r="F6" t="n">
-        <v>752468</v>
+        <v>704668</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -800,10 +800,10 @@
         <v>287059</v>
       </c>
       <c r="P6" t="n">
-        <v>465409</v>
+        <v>417609</v>
       </c>
       <c r="Q6" t="n">
-        <v>752468</v>
+        <v>715668</v>
       </c>
     </row>
     <row r="7">
@@ -824,10 +824,10 @@
         <v>38</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>5457</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>-5419</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -853,18 +853,18 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-103.7%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-5400</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="8">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2680</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-2680</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
@@ -914,18 +914,18 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-100.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="9">
@@ -946,10 +946,10 @@
         <v>22338</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="F9" t="n">
-        <v>22338</v>
+        <v>-10662</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-103.1%</t>
         </is>
       </c>
       <c r="N9" t="n">
         <v>22338</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="Q9" t="n">
         <v>22338</v>
@@ -1009,10 +1009,10 @@
         <v>6384</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>111788</v>
       </c>
       <c r="F10" t="n">
-        <v>6384</v>
+        <v>-105404</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-94.8%</t>
+          <t>-186.3%</t>
         </is>
       </c>
       <c r="N10" t="n">
         <v>6355</v>
       </c>
       <c r="O10" t="n">
-        <v>29</v>
+        <v>-58580</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-53179</v>
       </c>
       <c r="Q10" t="n">
-        <v>6384</v>
+        <v>-37204</v>
       </c>
     </row>
     <row r="11">
@@ -1072,10 +1072,10 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>7121</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>-7102</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1101,18 +1101,18 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-109.7%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>-7102</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="12">
@@ -1133,10 +1133,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>10419</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-10419</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -1162,18 +1162,18 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-105.0%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-10400</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="13">
@@ -1194,10 +1194,10 @@
         <v>22919</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>11194</v>
       </c>
       <c r="F13" t="n">
-        <v>22919</v>
+        <v>11725</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -1223,20 +1223,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-90.4%</t>
+          <t>-95.1%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>22919</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-796</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-10398</v>
       </c>
       <c r="Q13" t="n">
-        <v>22919</v>
+        <v>21725</v>
       </c>
     </row>
     <row r="14">
@@ -1257,10 +1257,10 @@
         <v>22869</v>
       </c>
       <c r="E14" t="n">
-        <v>1342</v>
+        <v>99689</v>
       </c>
       <c r="F14" t="n">
-        <v>21527</v>
+        <v>-76820</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
@@ -1286,20 +1286,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>-111.5%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>21200</v>
       </c>
       <c r="O14" t="n">
-        <v>327</v>
+        <v>-67920</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-30100</v>
       </c>
       <c r="Q14" t="n">
-        <v>21527</v>
+        <v>-46720</v>
       </c>
     </row>
     <row r="15">
@@ -1320,10 +1320,10 @@
         <v>39431</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>33609</v>
       </c>
       <c r="F15" t="n">
-        <v>39431</v>
+        <v>5822</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
@@ -1349,20 +1349,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-83.0%</t>
+          <t>-97.5%</t>
         </is>
       </c>
       <c r="N15" t="n">
         <v>39422</v>
       </c>
       <c r="O15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-33600</v>
       </c>
       <c r="Q15" t="n">
-        <v>39431</v>
+        <v>39422</v>
       </c>
     </row>
     <row r="16">
@@ -1383,10 +1383,10 @@
         <v>638</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>6314</v>
       </c>
       <c r="F16" t="n">
-        <v>600</v>
+        <v>-5676</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-99.7%</t>
+          <t>-102.4%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>600</v>
+        <v>-5676</v>
       </c>
       <c r="Q16" t="n">
-        <v>600</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="17">
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-100.5%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1550,10 +1550,10 @@
         <v>879917</v>
       </c>
       <c r="E19" t="n">
-        <v>3783</v>
+        <v>961373</v>
       </c>
       <c r="F19" t="n">
-        <v>876134</v>
+        <v>-81456</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1581,20 +1581,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>-101.2%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>112234</v>
       </c>
       <c r="O19" t="n">
-        <v>297892</v>
+        <v>-434584</v>
       </c>
       <c r="P19" t="n">
-        <v>466009</v>
+        <v>240896</v>
       </c>
       <c r="Q19" t="n">
-        <v>876135</v>
+        <v>261173</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1636,80 +1636,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="C2" t="n">
-        <v>2117.59</v>
+        <v>478737.58</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>1113</v>
+        <v>231127</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>233</v>
       </c>
       <c r="C4" t="n">
-        <v>303</v>
+        <v>95350.25999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>172</v>
+        <v>65500</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50595.05</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>24004.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>协商一致</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>77</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="B8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10975</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>价格问题</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1464</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1724,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,217 +1832,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>1341.59</v>
+        <v>138560.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1018</v>
+        <v>49200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>142</v>
+        <v>27354</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>115</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>观行组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>123</v>
+        <v>122160</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n">
-        <v>96</v>
+        <v>37207.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>6768.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>6691</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>299</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="14">
@@ -1973,14 +2053,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>86</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15">
@@ -1991,20 +2071,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2013,34 +2093,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>87580</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>16200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2052,13 +2132,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>4999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2067,28 +2147,784 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>81409</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1360.59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>初心组</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>34800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>初心组</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>90</v>
+      </c>
+      <c r="D26" t="n">
+        <v>33949</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>初心组</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>98</v>
+      </c>
+      <c r="D27" t="n">
+        <v>21469.67</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>初心组</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>35</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4064.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>初心组</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>初心组</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>72</v>
+      </c>
+      <c r="D31" t="n">
+        <v>23946</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>54</v>
+      </c>
+      <c r="D32" t="n">
+        <v>18945.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12389</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>10636</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5323</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>20</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4913.75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>36800</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11009</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>价格问题</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10796</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7083.33</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3398</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>昆明</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3419</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>服务未交付/联系不上</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C61" t="n">
         <v>1</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D61" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2680</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2125,66 +2961,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>科学营养实体商品</t>
+          <t>分享咨询</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>1341.59</v>
+        <v>270277.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>完形心理基训课</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>999</v>
+        <v>162600</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>911</v>
+        <v>131041.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>299元青春期家庭21天陪跑</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>299</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29睡眠基础营</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>83600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>心灯—长程课</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>76054.88</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>家庭守护计划</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>49050</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>少年说倾听计划</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="C6" t="n">
-        <v>232</v>
+      <c r="C9" t="n">
+        <v>33120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="n">
+        <v>27100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>完形心理基训课</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7912.75</v>
       </c>
     </row>
   </sheetData>
@@ -2221,53 +3122,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>1427.59</v>
+        <v>199396.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>999</v>
+        <v>158059</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>451</v>
+        <v>103663</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>209</v>
+        <v>93866.59</v>
       </c>
     </row>
     <row r="6">
@@ -2277,140 +3178,140 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>96</v>
+        <v>87446.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>76</v>
+        <v>42969.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>39874</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>34108.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>32049</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>西藏自治区</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>23705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>22814</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>15559</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>保留地址</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>14627.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>8032</v>
       </c>
     </row>
   </sheetData>
@@ -2564,13 +3465,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9997</v>
+        <v>-328743</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-8980</v>
       </c>
       <c r="E2" t="n">
-        <v>9997</v>
+        <v>-285415</v>
       </c>
     </row>
     <row r="3">
@@ -2585,13 +3486,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>433</v>
+        <v>-233283</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-1980</v>
       </c>
       <c r="E3" t="n">
-        <v>433</v>
+        <v>-165223</v>
       </c>
     </row>
     <row r="4">
@@ -2606,13 +3507,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>287462</v>
+        <v>133942</v>
       </c>
       <c r="D4" t="n">
-        <v>466008</v>
+        <v>251855</v>
       </c>
       <c r="E4" t="n">
-        <v>865704</v>
+        <v>711811</v>
       </c>
     </row>
     <row r="5">
@@ -2627,13 +3528,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4017</v>
+        <v>-67945</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="E5" t="n">
-        <v>4017</v>
+        <v>-60137</v>
       </c>
     </row>
     <row r="6">
@@ -2648,13 +3549,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1667</v>
+        <v>-170730</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-4980</v>
       </c>
       <c r="E6" t="n">
-        <v>1667</v>
+        <v>-157210</v>
       </c>
     </row>
     <row r="7">
@@ -2669,13 +3570,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4313</v>
+        <v>-90068</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>4313</v>
+        <v>-68068</v>
       </c>
     </row>
     <row r="8">
@@ -2690,13 +3591,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>433</v>
+        <v>-233284</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-1980</v>
       </c>
       <c r="E8" t="n">
-        <v>433</v>
+        <v>-165224</v>
       </c>
     </row>
     <row r="9">
@@ -2714,10 +3615,10 @@
         <v>287059</v>
       </c>
       <c r="D9" t="n">
-        <v>465409</v>
+        <v>417609</v>
       </c>
       <c r="E9" t="n">
-        <v>752468</v>
+        <v>715668</v>
       </c>
     </row>
     <row r="10">
@@ -2732,13 +3633,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-5400</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="11">
@@ -2753,13 +3654,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="12">
@@ -2774,10 +3675,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="E12" t="n">
         <v>22338</v>
@@ -2795,13 +3696,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>-58580</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-53179</v>
       </c>
       <c r="E13" t="n">
-        <v>6384</v>
+        <v>-37204</v>
       </c>
     </row>
     <row r="14">
@@ -2816,13 +3717,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>-7102</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="15">
@@ -2837,13 +3738,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-10400</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="16">
@@ -2858,13 +3759,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-796</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-10398</v>
       </c>
       <c r="E16" t="n">
-        <v>22919</v>
+        <v>21725</v>
       </c>
     </row>
     <row r="17">
@@ -2879,13 +3780,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>327</v>
+        <v>-67920</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-30100</v>
       </c>
       <c r="E17" t="n">
-        <v>21527</v>
+        <v>-46720</v>
       </c>
     </row>
     <row r="18">
@@ -2900,13 +3801,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-33600</v>
       </c>
       <c r="E18" t="n">
-        <v>39431</v>
+        <v>39422</v>
       </c>
     </row>
     <row r="19">
@@ -2924,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>600</v>
+        <v>-5676</v>
       </c>
       <c r="E19" t="n">
-        <v>600</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="20">
@@ -2963,7 +3864,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2984,13 +3885,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>297892</v>
+        <v>-434584</v>
       </c>
       <c r="D22" t="n">
-        <v>466009</v>
+        <v>240896</v>
       </c>
       <c r="E22" t="n">
-        <v>876135</v>
+        <v>261173</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3991,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>13491.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3098,7 +3999,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-13491.7</v>
       </c>
     </row>
     <row r="3">
@@ -3132,7 +4033,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4979</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3140,7 +4041,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-4979</v>
       </c>
     </row>
     <row r="4">
@@ -3174,7 +4075,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>7503</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3182,7 +4083,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-7503</v>
       </c>
     </row>
     <row r="5">
@@ -3216,7 +4117,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4681</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3224,7 +4125,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-4681</v>
       </c>
     </row>
     <row r="6">
@@ -3258,7 +4159,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>5680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3266,7 +4167,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-5680</v>
       </c>
     </row>
     <row r="7">
@@ -3300,7 +4201,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>7410</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3308,7 +4209,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-7410</v>
       </c>
     </row>
     <row r="8">
@@ -3342,7 +4243,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3350,7 +4251,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-14560</v>
       </c>
     </row>
     <row r="9">
@@ -3384,7 +4285,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>73696.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -3392,7 +4293,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-73696.67</v>
       </c>
     </row>
     <row r="10">
@@ -3426,7 +4327,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>11752</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3434,7 +4335,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-11752</v>
       </c>
     </row>
     <row r="11">
@@ -3468,7 +4369,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>17466.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3476,7 +4377,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-17466.7</v>
       </c>
     </row>
     <row r="12">
@@ -3594,7 +4495,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>57263</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3602,7 +4503,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-57263</v>
       </c>
     </row>
     <row r="15">
@@ -3720,7 +4621,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>9545</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3728,7 +4629,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-9545</v>
       </c>
     </row>
     <row r="18">
@@ -3762,7 +4663,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3770,7 +4671,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-24800</v>
       </c>
     </row>
     <row r="19">
@@ -3804,7 +4705,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3812,7 +4713,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-14980</v>
       </c>
     </row>
     <row r="20">
@@ -3846,7 +4747,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4626.67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3854,7 +4755,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-4626.67</v>
       </c>
     </row>
     <row r="21">
@@ -3888,7 +4789,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3896,7 +4797,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-4980</v>
       </c>
     </row>
     <row r="22">
@@ -3930,7 +4831,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>23629</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3938,7 +4839,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-23629</v>
       </c>
     </row>
     <row r="23">
@@ -3972,7 +4873,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>14940</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3980,7 +4881,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-14940</v>
       </c>
     </row>
     <row r="24">
@@ -4014,7 +4915,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>26820</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -4022,7 +4923,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-26820</v>
       </c>
     </row>
     <row r="25">
@@ -4056,7 +4957,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4064,7 +4965,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-32000</v>
       </c>
     </row>
     <row r="26">
@@ -4140,7 +5041,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4148,7 +5049,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
     </row>
     <row r="28">
@@ -4182,7 +5083,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4190,7 +5091,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-5500</v>
       </c>
     </row>
     <row r="29">
@@ -4224,7 +5125,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4232,7 +5133,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="30">
@@ -4266,7 +5167,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4274,7 +5175,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="31">
@@ -4308,7 +5209,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4316,7 +5217,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-11500</v>
       </c>
     </row>
     <row r="32">
@@ -4476,7 +5377,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -4484,7 +5385,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-24800</v>
       </c>
     </row>
     <row r="36">
@@ -4642,7 +5543,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>66300</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4650,7 +5551,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-66300</v>
       </c>
     </row>
     <row r="4">
@@ -4676,15 +5577,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21200</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="5">
@@ -4744,7 +5645,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>22400</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4752,7 +5653,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-22400</v>
       </c>
     </row>
     <row r="7">
@@ -4812,7 +5713,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4820,7 +5721,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="9">
@@ -4846,7 +5747,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4854,7 +5755,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-598</v>
       </c>
     </row>
     <row r="10">
@@ -4880,7 +5781,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4888,7 +5789,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="11">
@@ -4948,15 +5849,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>998</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>166.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>600</v>
+        <v>-398</v>
       </c>
     </row>
     <row r="13">
@@ -5322,15 +6223,15 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>425.76</v>
+        <v>27.75999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -5356,15 +6257,15 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22493.04</v>
+        <v>21697.04</v>
       </c>
     </row>
     <row r="25">
@@ -5390,7 +6291,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -5398,7 +6299,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="26">
@@ -5560,7 +6461,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5568,7 +6469,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-14500</v>
       </c>
     </row>
     <row r="31">
@@ -5594,15 +6495,15 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4750.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>200</v>
+        <v>-9300</v>
       </c>
     </row>
     <row r="32">
@@ -5662,15 +6563,15 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>270.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3142.6</v>
+        <v>-5357.4</v>
       </c>
     </row>
     <row r="34">
@@ -5730,15 +6631,15 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>689.7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4872</v>
+        <v>-28728</v>
       </c>
     </row>
     <row r="36">
@@ -5764,15 +6665,15 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>674.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1482.9</v>
+        <v>-8517.1</v>
       </c>
     </row>
     <row r="37">
@@ -5798,7 +6699,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3960</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -5806,7 +6707,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-3960</v>
       </c>
     </row>
     <row r="38">
@@ -5968,7 +6869,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7083.33</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5976,7 +6877,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-7083.33</v>
       </c>
     </row>
     <row r="43">
@@ -6138,7 +7039,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6146,7 +7047,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-9200</v>
       </c>
     </row>
     <row r="48">
@@ -6206,7 +7107,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6214,7 +7115,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>-1200</v>
       </c>
     </row>
     <row r="50">
@@ -6274,15 +7175,15 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12494.32</v>
+        <v>894.3199999999997</v>
       </c>
     </row>
     <row r="52">
@@ -6478,7 +7379,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6486,7 +7387,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="58">
@@ -6546,7 +7447,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6554,7 +7455,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="60">
@@ -6682,7 +7583,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -6690,7 +7591,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>-5400</v>
       </c>
     </row>
     <row r="64">
@@ -8824,23 +9725,23 @@
         <v>11815</v>
       </c>
       <c r="D2" t="n">
-        <v>1385</v>
+        <v>14207</v>
       </c>
       <c r="E2" t="n">
-        <v>1385</v>
+        <v>11596</v>
       </c>
       <c r="F2" t="n">
-        <v>11.72</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2611</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 299.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 266.0；1号课：睡前静心基础营-心理学网课+陪伴能量提升 203.0</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 2392.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 1280.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 1083.0</t>
         </is>
       </c>
     </row>
@@ -8859,7 +9760,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>131041.74</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -8868,12 +9769,16 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>131041.74</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>青少年同行者计划领航营 69328.7；青少年同行者计划-护航营 16598.0；青少年同行者计划向阳营 14593.37</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8890,7 +9795,7 @@
         <v>48398</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>293577.33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -8899,12 +9804,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>293577.33</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>606.59</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>儿童青少年 195981.33；精神心理 37196.0；电商咨询 31500.0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8921,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>85530</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -8930,12 +9839,16 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>85530</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>家庭守护计划2.0（二阶） 26820.0；少年说陪伴计划 26400.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8952,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>163600</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -8961,12 +9874,16 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>163600</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>肠道菌群移植（双疗程） 91200.0；肠道菌群移植 49600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8983,23 +9900,23 @@
         <v>787371.21</v>
       </c>
       <c r="D7" t="n">
-        <v>1341.59</v>
+        <v>4519.59</v>
       </c>
       <c r="E7" t="n">
-        <v>1341.59</v>
+        <v>1941.59</v>
       </c>
       <c r="F7" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2578</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59</t>
+          <t>线上/线下门诊 1800.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 800.0</t>
         </is>
       </c>
     </row>
@@ -9018,23 +9935,23 @@
         <v>32332.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1056</v>
+        <v>268896.93</v>
       </c>
       <c r="E8" t="n">
-        <v>1056</v>
+        <v>1160</v>
       </c>
       <c r="F8" t="n">
-        <v>3.27</v>
+        <v>3.59</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>267736.93</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>828.0700000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 38.0；（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题 19.0</t>
+          <t>青少年成长基地3月营（金盏基地） 83600.0；心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 75254.88；蛋壳跳动身心复能营21天（一阶） 34600.0</t>
         </is>
       </c>
     </row>
@@ -9053,23 +9970,23 @@
         <v>11815</v>
       </c>
       <c r="D9" t="n">
-        <v>1385</v>
+        <v>14207</v>
       </c>
       <c r="E9" t="n">
-        <v>1385</v>
+        <v>11596</v>
       </c>
       <c r="F9" t="n">
-        <v>11.72</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2611</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 299.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 266.0；1号课：睡前静心基础营-心理学网课+陪伴能量提升 203.0</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 2392.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 1280.0；青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题 1083.0</t>
         </is>
       </c>
     </row>
@@ -9088,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>131041.74</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -9097,12 +10014,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>131041.74</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>青少年同行者计划领航营 69328.7；青少年同行者计划-护航营 16598.0；青少年同行者计划向阳营 14593.37</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9119,7 +10040,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>73298</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -9128,12 +10049,16 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>73298</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>儿童青少年 50900.0；精神心理 22398.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9150,7 +10075,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>82170</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -9159,12 +10084,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>82170</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>家庭守护计划2.0（二阶） 26820.0；少年说陪伴计划 26400.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9181,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>96200</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -9190,12 +10119,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>96200</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>肠道菌群移植 49600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9212,7 +10145,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -9221,12 +10154,16 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9243,7 +10180,7 @@
         <v>999</v>
       </c>
       <c r="D15" t="n">
-        <v>999</v>
+        <v>188106.93</v>
       </c>
       <c r="E15" t="n">
         <v>999</v>
@@ -9252,14 +10189,14 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>187107.93</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>18729.52</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[自我成长/疗愈] 完形心理认知课，增加智慧。 999.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 75254.88；青少年成长基地3月营（金盏基地） 46800.0；蛋壳跳动身心复能营21天（一阶） 34600.0</t>
         </is>
       </c>
     </row>
@@ -9278,7 +10215,7 @@
         <v>48398</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>220279.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -9287,12 +10224,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>220279.33</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>455.14</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>儿童青少年 145081.33；电商咨询 31500.0；精神心理 14798.0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9309,7 +10250,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -9318,12 +10259,16 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>少年说倾听计划 3360.0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9340,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>67400</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -9349,12 +10294,16 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>67400</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0；肠道菌群检测（医生专用） 1000.0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9371,23 +10320,23 @@
         <v>787371.21</v>
       </c>
       <c r="D19" t="n">
-        <v>1341.59</v>
+        <v>3741.59</v>
       </c>
       <c r="E19" t="n">
-        <v>1341.59</v>
+        <v>1941.59</v>
       </c>
       <c r="F19" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59</t>
+          <t>线上/线下门诊 1800.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
         </is>
       </c>
     </row>
@@ -9406,23 +10355,23 @@
         <v>31333.5</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>80790</v>
       </c>
       <c r="E20" t="n">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="F20" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>80629</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>257.33</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 38.0；（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题 19.0</t>
+          <t>青少年成长基地3月营（金盏基地） 36800.0；青少年【未来之翼】身心节律复能7日营 33600.0；完形心理成长计划 4999.0</t>
         </is>
       </c>
     </row>

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -4513,31 +4513,31 @@
         <v>302618</v>
       </c>
       <c r="D3" t="n">
-        <v>77878</v>
+        <v>174130</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14939</v>
+        <v>24899</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>62939</v>
+        <v>149231</v>
       </c>
     </row>
     <row r="4">
@@ -4723,19 +4723,19 @@
         <v>189136</v>
       </c>
       <c r="D8" t="n">
-        <v>4980</v>
+        <v>45856</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -4743,11 +4743,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>292.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-9580</v>
+        <v>31296</v>
       </c>
     </row>
     <row r="9">
@@ -5017,19 +5017,19 @@
         <v>147291</v>
       </c>
       <c r="D15" t="n">
-        <v>27830</v>
+        <v>32810</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>27830</v>
+        <v>32810</v>
       </c>
     </row>
     <row r="16">
@@ -5059,19 +5059,19 @@
         <v>279050</v>
       </c>
       <c r="D16" t="n">
-        <v>149298</v>
+        <v>159656</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>108538</v>
+        <v>118896</v>
       </c>
     </row>
     <row r="17">
@@ -5101,19 +5101,19 @@
         <v>285517</v>
       </c>
       <c r="D17" t="n">
-        <v>123984</v>
+        <v>148884</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -5121,11 +5121,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>114041</v>
+        <v>138941</v>
       </c>
     </row>
     <row r="18">
@@ -5143,19 +5143,19 @@
         <v>290643</v>
       </c>
       <c r="D18" t="n">
-        <v>57236</v>
+        <v>118616</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>27456</v>
+        <v>88836</v>
       </c>
     </row>
     <row r="19">
@@ -5227,19 +5227,19 @@
         <v>176745</v>
       </c>
       <c r="D20" t="n">
-        <v>53179</v>
+        <v>107660</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -5247,11 +5247,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>44572.33</v>
+        <v>99053.33</v>
       </c>
     </row>
     <row r="21">
@@ -10916,11 +10916,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>司法虚拟</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>84660</v>
+        <v>134460</v>
       </c>
     </row>
     <row r="8">
@@ -10939,11 +10939,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>62180</v>
+        <v>93340</v>
       </c>
     </row>
     <row r="9">
@@ -10962,11 +10962,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>59461</v>
+        <v>84062</v>
       </c>
     </row>
     <row r="10">
@@ -10985,11 +10985,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>严闽龙虚拟</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54780</v>
+        <v>75910</v>
       </c>
     </row>
     <row r="11">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>刘俊彤虚拟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>54481</v>
+        <v>62180</v>
       </c>
     </row>
     <row r="12">
@@ -11721,11 +11721,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>司法虚拟</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>84660</v>
+        <v>134460</v>
       </c>
     </row>
     <row r="43">
@@ -11744,11 +11744,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>62180</v>
+        <v>93340</v>
       </c>
     </row>
     <row r="44">
@@ -11767,11 +11767,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>59461</v>
+        <v>84062</v>
       </c>
     </row>
     <row r="45">
@@ -11790,11 +11790,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>严闽龙虚拟</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>54780</v>
+        <v>75910</v>
       </c>
     </row>
     <row r="46">
@@ -11813,11 +11813,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘俊彤虚拟</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>54481</v>
+        <v>62180</v>
       </c>
     </row>
     <row r="47">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -9253,7 +9253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9658,27 +9658,27 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2563515.54</v>
+        <v>195865</v>
       </c>
       <c r="E14" t="n">
-        <v>3313</v>
+        <v>135</v>
       </c>
       <c r="F14" t="n">
-        <v>643574.36</v>
+        <v>90390</v>
       </c>
       <c r="G14" t="n">
-        <v>1919941.18</v>
+        <v>105475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9687,16 +9687,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>181525.57</v>
+        <v>2367650.54</v>
       </c>
       <c r="E15" t="n">
-        <v>5893</v>
+        <v>3178</v>
       </c>
       <c r="F15" t="n">
-        <v>181525.57</v>
+        <v>553184.36</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1814466.18</v>
       </c>
     </row>
     <row r="16">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9716,13 +9716,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="E16" t="n">
-        <v>234</v>
+        <v>5893</v>
       </c>
       <c r="F16" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9745,13 +9745,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="F17" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -9770,17 +9770,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>345326</v>
+        <v>355326</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>345326</v>
+        <v>355326</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -9799,17 +9799,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>老客</t>
+          <t>新客</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10000</v>
+        <v>345326</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="F19" t="n">
-        <v>10000</v>
+        <v>345326</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -9823,22 +9823,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>老客</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1497534</v>
+        <v>10000</v>
       </c>
       <c r="E20" t="n">
-        <v>270</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>1497534</v>
+        <v>10000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9857,17 +9857,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>少年说</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1116610</v>
+        <v>1497534</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="F21" t="n">
-        <v>1116610</v>
+        <v>1497534</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9886,17 +9886,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>家守</t>
+          <t>少年说</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>380924</v>
+        <v>1116610</v>
       </c>
       <c r="E22" t="n">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="F22" t="n">
-        <v>380924</v>
+        <v>1116610</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -9910,22 +9910,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>家守</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>99200</v>
+        <v>380924</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="F23" t="n">
-        <v>99200</v>
+        <v>380924</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9948,13 +9948,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9973,17 +9973,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>37785.67</v>
+        <v>49696.78</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F25" t="n">
-        <v>37785.67</v>
+        <v>49696.78</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -10002,17 +10002,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11911.11</v>
+        <v>37785.67</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="F26" t="n">
-        <v>11911.11</v>
+        <v>37785.67</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -10026,22 +10026,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>643574.36</v>
+        <v>11911.11</v>
       </c>
       <c r="E27" t="n">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="F27" t="n">
-        <v>643574.36</v>
+        <v>11911.11</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -10050,12 +10050,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10064,45 +10064,45 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2386608.01</v>
+        <v>90390</v>
       </c>
       <c r="E28" t="n">
-        <v>582</v>
+        <v>58</v>
       </c>
       <c r="F28" t="n">
+        <v>90390</v>
+      </c>
+      <c r="G28" t="n">
         <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2386608.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>老客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1910462.01</v>
+        <v>553184.36</v>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>315</v>
       </c>
       <c r="F29" t="n">
+        <v>553184.36</v>
+      </c>
+      <c r="G29" t="n">
         <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1910462.01</v>
       </c>
     </row>
     <row r="30">
@@ -10118,20 +10118,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>新客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>418748</v>
+        <v>2386608.01</v>
       </c>
       <c r="E30" t="n">
-        <v>183</v>
+        <v>582</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>418748</v>
+        <v>2386608.01</v>
       </c>
     </row>
     <row r="31">
@@ -10142,25 +10142,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>老客</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>571481</v>
+        <v>1910462.01</v>
       </c>
       <c r="E31" t="n">
-        <v>74</v>
+        <v>392</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>571481</v>
+        <v>1910462.01</v>
       </c>
     </row>
     <row r="32">
@@ -10171,25 +10171,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>少年说</t>
+          <t>新客</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>330240</v>
+        <v>418748</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>330240</v>
+        <v>418748</v>
       </c>
     </row>
     <row r="33">
@@ -10205,20 +10205,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>家守</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>241241</v>
+        <v>571481</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>241241</v>
+        <v>571481</v>
       </c>
     </row>
     <row r="34">
@@ -10229,25 +10229,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>少年说</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>150800</v>
+        <v>330240</v>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>150800</v>
+        <v>330240</v>
       </c>
     </row>
     <row r="35">
@@ -10258,25 +10258,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>家守</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1279518.2</v>
+        <v>241241</v>
       </c>
       <c r="E35" t="n">
-        <v>2105</v>
+        <v>32</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1279518.2</v>
+        <v>241241</v>
       </c>
     </row>
     <row r="36">
@@ -10287,25 +10287,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>824010.16</v>
+        <v>150800</v>
       </c>
       <c r="E36" t="n">
-        <v>916</v>
+        <v>21</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>824010.16</v>
+        <v>150800</v>
       </c>
     </row>
     <row r="37">
@@ -10321,20 +10321,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>455508.04</v>
+        <v>1279518.2</v>
       </c>
       <c r="E37" t="n">
-        <v>1189</v>
+        <v>2105</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>455508.04</v>
+        <v>1279518.2</v>
       </c>
     </row>
     <row r="38">
@@ -10345,25 +10345,112 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1919941.18</v>
+        <v>824010.16</v>
       </c>
       <c r="E38" t="n">
-        <v>2940</v>
+        <v>916</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1919941.18</v>
+        <v>824010.16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>初诊</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>455508.04</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>455508.04</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>105475</v>
+      </c>
+      <c r="E40" t="n">
+        <v>77</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>105475</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1814466.18</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2863</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1814466.18</v>
       </c>
     </row>
   </sheetData>
@@ -10464,7 +10551,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>咨询 139650.0；家守/千金方/少年说 21480.0；医疗 17469.0；其他 4674.0</t>
+          <t>咨询 139650.0；家守/千金方/少年说 21480.0；医疗 17469.0；其他 2694.0；进化论 1980.0</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10607,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>咨询 483720.0；家守/千金方/少年说 246780.0；其他 103694.0；医疗 78122.14；菌群 54600.0</t>
+          <t>咨询 483720.0；家守/千金方/少年说 246780.0；其他 99734.0；医疗 78122.14；菌群 54600.0；进化论 3960.0</t>
         </is>
       </c>
     </row>
@@ -10600,11 +10687,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>87.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>其他 1282342.0；咨询 146542.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
+          <t>其他 1210627.0；咨询 146542.0；进化论 71715.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -10656,11 +10743,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>61.2</v>
+        <v>57.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>其他 418892.5；咨询 141738.01；家守/千金方/少年说 109800.0；医疗 14327.36</t>
+          <t>其他 391072.5；咨询 141738.01；家守/千金方/少年说 109800.0；进化论 27820.0；医疗 14327.36</t>
         </is>
       </c>
     </row>
@@ -10800,7 +10887,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>咨询 139650.0；家守/千金方/少年说 21480.0；医疗 17469.0；其他 4674.0</t>
+          <t>咨询 139650.0；家守/千金方/少年说 21480.0；医疗 17469.0；其他 2694.0；进化论 1980.0</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10943,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>咨询 483720.0；家守/千金方/少年说 246780.0；其他 103694.0；医疗 78122.14；菌群 54600.0</t>
+          <t>咨询 483720.0；家守/千金方/少年说 246780.0；其他 99734.0；医疗 78122.14；菌群 54600.0；进化论 3960.0</t>
         </is>
       </c>
     </row>
@@ -10936,11 +11023,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>87.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>其他 1282342.0；咨询 146542.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
+          <t>其他 1210627.0；咨询 146542.0；进化论 71715.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -10992,11 +11079,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>61.2</v>
+        <v>57.1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>其他 418892.5；咨询 141738.01；家守/千金方/少年说 109800.0；医疗 14327.36</t>
+          <t>其他 391072.5；咨询 141738.01；家守/千金方/少年说 109800.0；进化论 27820.0；医疗 14327.36</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11823,7 +11910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -11831,11 +11918,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>胡炫明</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>398820</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="33">
@@ -11846,7 +11933,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -11854,11 +11941,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>陈鑫</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>292350</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="34">
@@ -11869,7 +11956,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -11877,11 +11964,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>徐艳霞</t>
+          <t>高丹</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>277500</v>
+        <v>16520</v>
       </c>
     </row>
     <row r="35">
@@ -11892,7 +11979,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -11900,11 +11987,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>梁志前</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220060</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="36">
@@ -11915,7 +12002,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -11923,22 +12010,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>陈磊</t>
+          <t>徐艳霞</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>171510</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -11946,22 +12033,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>胡炫明</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1280</v>
+        <v>391000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -11969,22 +12056,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>徐艳霞</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1280</v>
+        <v>267600</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -11992,22 +12079,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1280</v>
+        <v>267600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -12015,22 +12102,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>梁志前</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1280</v>
+        <v>217900</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -12038,11 +12125,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>陈磊</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1280</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="42">
@@ -12053,7 +12140,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -12061,11 +12148,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>169320</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="43">
@@ -12076,7 +12163,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -12084,11 +12171,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103300</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="44">
@@ -12099,7 +12186,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -12107,11 +12194,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>89042</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="45">
@@ -12122,7 +12209,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -12130,11 +12217,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>79381</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="46">
@@ -12145,7 +12232,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -12153,11 +12240,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>75910</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="47">
@@ -12168,7 +12255,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -12176,11 +12263,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53194</v>
+        <v>169320</v>
       </c>
     </row>
     <row r="48">
@@ -12191,7 +12278,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -12199,11 +12286,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>30796</v>
+        <v>103300</v>
       </c>
     </row>
     <row r="49">
@@ -12214,7 +12301,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -12222,11 +12309,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>30398</v>
+        <v>89042</v>
       </c>
     </row>
     <row r="50">
@@ -12237,7 +12324,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -12245,11 +12332,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>24598</v>
+        <v>79381</v>
       </c>
     </row>
     <row r="51">
@@ -12260,7 +12347,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -12268,11 +12355,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>20000</v>
+        <v>75910</v>
       </c>
     </row>
     <row r="52">
@@ -12283,7 +12370,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -12291,11 +12378,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>165000</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="53">
@@ -12306,7 +12393,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -12314,11 +12401,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>132000</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="54">
@@ -12329,7 +12416,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -12337,11 +12424,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>109640</v>
+        <v>30398</v>
       </c>
     </row>
     <row r="55">
@@ -12352,7 +12439,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -12360,11 +12447,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>109020</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="56">
@@ -12375,7 +12462,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -12383,11 +12470,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103200</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="57">
@@ -12398,7 +12485,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -12406,11 +12493,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>49600</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="58">
@@ -12421,7 +12508,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -12429,11 +12516,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>24800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="59">
@@ -12444,7 +12531,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -12452,11 +12539,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>24800</v>
+        <v>109640</v>
       </c>
     </row>
     <row r="60">
@@ -12467,7 +12554,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -12475,11 +12562,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>109020</v>
       </c>
     </row>
     <row r="61">
@@ -12490,7 +12577,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -12498,11 +12585,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>103200</v>
       </c>
     </row>
     <row r="62">
@@ -12513,7 +12600,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -12525,7 +12612,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>16800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="63">
@@ -12536,7 +12623,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -12544,11 +12631,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1200</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="64">
@@ -12559,7 +12646,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -12571,7 +12658,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>500</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="65">
@@ -12582,7 +12669,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -12590,11 +12677,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -12605,7 +12692,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -12613,11 +12700,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -12628,7 +12715,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -12636,11 +12723,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>陈鑫</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>292350</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="68">
@@ -12651,7 +12738,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -12659,11 +12746,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>吴云龙</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>57280</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="69">
@@ -12674,7 +12761,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -12682,11 +12769,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>姚闯</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>55740</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70">
@@ -12697,7 +12784,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -12705,11 +12792,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>杨旺忠</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>54040</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71">
@@ -12720,7 +12807,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -12728,22 +12815,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>40000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -12751,22 +12838,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>233168</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -12774,22 +12861,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>158786</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -12797,22 +12884,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>91194</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -12820,22 +12907,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>吴云龙</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>85698</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -12843,22 +12930,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>魏恺志</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>81982</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -12866,22 +12953,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>164220</v>
+        <v>267600</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -12889,22 +12976,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>黄慧作</t>
+          <t>姚闯</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>90000</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -12912,22 +12999,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>杨旺忠</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>46200</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -12935,22 +13022,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>吴云龙</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>26820</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -12958,11 +13045,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>26200</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="82">
@@ -12973,7 +13060,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -12985,7 +13072,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>54600</v>
+        <v>233168</v>
       </c>
     </row>
     <row r="83">
@@ -12996,7 +13083,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -13004,11 +13091,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>45600</v>
+        <v>158786</v>
       </c>
     </row>
     <row r="84">
@@ -13019,7 +13106,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -13027,11 +13114,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>24800</v>
+        <v>91194</v>
       </c>
     </row>
     <row r="85">
@@ -13042,7 +13129,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -13050,11 +13137,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>24800</v>
+        <v>85698</v>
       </c>
     </row>
     <row r="86">
@@ -13065,7 +13152,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -13073,11 +13160,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>王秀丽</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1000</v>
+        <v>81982</v>
       </c>
     </row>
     <row r="87">
@@ -13088,7 +13175,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -13096,11 +13183,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>245315.88</v>
+        <v>164220</v>
       </c>
     </row>
     <row r="88">
@@ -13111,7 +13198,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -13119,11 +13206,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>黄慧作</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>196025.61</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="89">
@@ -13134,7 +13221,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -13142,11 +13229,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>190639.29</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="90">
@@ -13157,7 +13244,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -13165,11 +13252,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>157856.3</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="91">
@@ -13180,7 +13267,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -13188,11 +13275,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>105286</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="92">
@@ -13203,7 +13290,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -13211,11 +13298,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>胡炫明</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>398820</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="93">
@@ -13226,7 +13313,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -13234,11 +13321,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>徐艳霞</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>277500</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="94">
@@ -13249,7 +13336,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -13257,11 +13344,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>梁志前</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220060</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="95">
@@ -13272,7 +13359,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -13280,11 +13367,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>陈磊</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>171510</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="96">
@@ -13295,7 +13382,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -13303,11 +13390,356 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>王秀丽</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>王倩雅</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>245315.88</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>李怡慧</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>196025.61</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>李菲菲</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>190639.29</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>李浩然</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>157856.3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>韦微</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>105286</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>高丹</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>16520</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>徐艳霞</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>郭海明</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>8560</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>章浩进</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>韦新妮</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>胡炫明</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>391000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>徐艳霞</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>267600</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>梁志前</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>217900</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>陈磊</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>168000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>5</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
           <t>胡威特</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v>105540</v>
+      <c r="E111" t="n">
+        <v>99600</v>
       </c>
     </row>
   </sheetData>
@@ -13321,7 +13753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13589,65 +14021,65 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2563515.54</v>
+        <v>195865</v>
       </c>
       <c r="D8" t="n">
-        <v>670158.59</v>
+        <v>57250</v>
       </c>
       <c r="E8" t="n">
-        <v>31112</v>
+        <v>4060</v>
       </c>
       <c r="F8" t="n">
-        <v>1.21</v>
+        <v>2.07</v>
       </c>
       <c r="G8" t="n">
-        <v>639046.59</v>
+        <v>53190</v>
       </c>
       <c r="H8" t="n">
-        <v>24.93</v>
+        <v>27.16</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0</t>
+          <t>【青春进化论】亲子成长2日营 53010.0；青春进化论（两日制亲子营） 3960.0；【青春进化论】亲子成长2日营补差链接 280.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>181525.57</v>
+        <v>2367650.54</v>
       </c>
       <c r="D9" t="n">
-        <v>22555</v>
+        <v>612908.59</v>
       </c>
       <c r="E9" t="n">
-        <v>18920</v>
+        <v>27052</v>
       </c>
       <c r="F9" t="n">
-        <v>10.42</v>
+        <v>1.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3635</v>
+        <v>585856.59</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>24.74</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 3588.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 2560.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1688.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0</t>
         </is>
       </c>
     </row>
@@ -13659,30 +14091,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="D10" t="n">
-        <v>193920.44</v>
+        <v>22555</v>
       </c>
       <c r="E10" t="n">
-        <v>4980</v>
+        <v>18920</v>
       </c>
       <c r="F10" t="n">
-        <v>0.44</v>
+        <v>10.42</v>
       </c>
       <c r="G10" t="n">
-        <v>188940.44</v>
+        <v>3635</v>
       </c>
       <c r="H10" t="n">
-        <v>16.54</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 118165.4；青少年同行者计划-护航营 21578.0；青少年同行者计划向阳营 14593.37</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 3588.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 2560.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1688.0</t>
         </is>
       </c>
     </row>
@@ -13694,30 +14126,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="D11" t="n">
-        <v>143025.9</v>
+        <v>193920.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G11" t="n">
-        <v>143025.9</v>
+        <v>188940.44</v>
       </c>
       <c r="H11" t="n">
-        <v>40.25</v>
+        <v>16.54</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>儿童青少年 63298.0；精神心理 61198.0；青少年-资深咨询 18500.0</t>
+          <t>青少年同行者计划领航营 118165.4；青少年同行者计划-护航营 21578.0；青少年同行者计划向阳营 14593.37</t>
         </is>
       </c>
     </row>
@@ -13729,30 +14161,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1497534</v>
+        <v>355326</v>
       </c>
       <c r="D12" t="n">
-        <v>145410</v>
+        <v>143025.9</v>
       </c>
       <c r="E12" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>143730</v>
+        <v>143025.9</v>
       </c>
       <c r="H12" t="n">
-        <v>9.6</v>
+        <v>40.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+          <t>儿童青少年 63298.0；精神心理 61198.0；青少年-资深咨询 18500.0</t>
         </is>
       </c>
     </row>
@@ -13764,30 +14196,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>99200</v>
+        <v>1497534</v>
       </c>
       <c r="D13" t="n">
-        <v>121000</v>
+        <v>145410</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G13" t="n">
-        <v>121000</v>
+        <v>143730</v>
       </c>
       <c r="H13" t="n">
-        <v>121.98</v>
+        <v>9.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>肠道菌群移植 74400.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
+          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
         </is>
       </c>
     </row>
@@ -13799,14 +14231,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="D14" t="n">
-        <v>778</v>
+        <v>121000</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13815,14 +14247,14 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>778</v>
+        <v>121000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.57</v>
+        <v>121.98</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+          <t>肠道菌群移植 74400.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
         </is>
       </c>
     </row>
@@ -13834,100 +14266,100 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>643574.36</v>
+        <v>49696.78</v>
       </c>
       <c r="D15" t="n">
-        <v>290090.59</v>
+        <v>778</v>
       </c>
       <c r="E15" t="n">
-        <v>3079</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>287011.59</v>
+        <v>778</v>
       </c>
       <c r="H15" t="n">
-        <v>44.6</v>
+        <v>1.57</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；蛋壳跳动身心复能营21天（一阶） 74200.0；青少年成长基地3月营（金盏基地） 46800.0</t>
+          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2386608.01</v>
+        <v>90390</v>
       </c>
       <c r="D16" t="n">
-        <v>409927.33</v>
+        <v>15940</v>
       </c>
       <c r="E16" t="n">
-        <v>10398</v>
+        <v>2080</v>
       </c>
       <c r="F16" t="n">
-        <v>0.44</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>399529.33</v>
+        <v>13860</v>
       </c>
       <c r="H16" t="n">
-        <v>16.74</v>
+        <v>15.33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>儿童青少年 286931.33；电商咨询 37500.0；精神心理 32798.0</t>
+          <t>【青春进化论】亲子成长2日营 13860.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 100.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>571481</v>
+        <v>553184.36</v>
       </c>
       <c r="D17" t="n">
-        <v>68520</v>
+        <v>274150.59</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G17" t="n">
-        <v>68520</v>
+        <v>273151.59</v>
       </c>
       <c r="H17" t="n">
-        <v>11.99</v>
+        <v>49.38</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；蛋壳跳动身心复能营21天（一阶） 74200.0；青少年成长基地3月营（金盏基地） 46800.0</t>
         </is>
       </c>
     </row>
@@ -13939,30 +14371,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>150800</v>
+        <v>2386608.01</v>
       </c>
       <c r="D18" t="n">
-        <v>115000</v>
+        <v>409927.33</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G18" t="n">
-        <v>115000</v>
+        <v>399529.33</v>
       </c>
       <c r="H18" t="n">
-        <v>76.26000000000001</v>
+        <v>16.74</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>肠道菌群移植 47600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+          <t>儿童青少年 286931.33；电商咨询 37500.0；精神心理 32798.0</t>
         </is>
       </c>
     </row>
@@ -13974,30 +14406,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1279518.2</v>
+        <v>571481</v>
       </c>
       <c r="D19" t="n">
-        <v>5541.59</v>
+        <v>68520</v>
       </c>
       <c r="E19" t="n">
-        <v>1941.59</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3600</v>
+        <v>68520</v>
       </c>
       <c r="H19" t="n">
-        <v>0.28</v>
+        <v>11.99</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>线上/线下门诊 3200.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
+          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
         </is>
       </c>
     </row>
@@ -14009,28 +14441,133 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>150800</v>
+      </c>
+      <c r="D20" t="n">
+        <v>115000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>肠道菌群移植 47600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1279518.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5541.59</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1941.59</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>线上/线下门诊 3200.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>105475</v>
+      </c>
+      <c r="D22" t="n">
+        <v>41310</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G22" t="n">
+        <v>39330</v>
+      </c>
+      <c r="H22" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>【青春进化论】亲子成长2日营 39150.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 180.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1919941.18</v>
-      </c>
-      <c r="D20" t="n">
-        <v>380068</v>
-      </c>
-      <c r="E20" t="n">
-        <v>28033</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="G20" t="n">
-        <v>352035</v>
-      </c>
-      <c r="H20" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1814466.18</v>
+      </c>
+      <c r="D23" t="n">
+        <v>338758</v>
+      </c>
+      <c r="E23" t="n">
+        <v>26053</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G23" t="n">
+        <v>312705</v>
+      </c>
+      <c r="H23" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>青少年营地动力唤醒方案 85000.0；青少年营地家族赋能方案 80000.0；青少年身心复能成长方案 80000.0</t>
         </is>
@@ -14047,7 +14584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14251,17 +14788,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78189</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>783326.16</v>
       </c>
       <c r="F8" t="n">
-        <v>9.9817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -14272,22 +14809,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37895</v>
+        <v>78189</v>
       </c>
       <c r="E9" t="n">
-        <v>325870.41</v>
+        <v>783326.16</v>
       </c>
       <c r="F9" t="n">
-        <v>11.6289</v>
+        <v>9.9817</v>
       </c>
     </row>
     <row r="10">
@@ -14303,17 +14840,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>216560</v>
+        <v>37895</v>
       </c>
       <c r="E10" t="n">
         <v>325870.41</v>
       </c>
       <c r="F10" t="n">
-        <v>66.4559</v>
+        <v>11.6289</v>
       </c>
     </row>
     <row r="11">
@@ -14329,17 +14866,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11394</v>
+        <v>216560</v>
       </c>
       <c r="E11" t="n">
         <v>325870.41</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4965</v>
+        <v>66.4559</v>
       </c>
     </row>
     <row r="12">
@@ -14355,17 +14892,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49531</v>
+        <v>11394</v>
       </c>
       <c r="E12" t="n">
         <v>325870.41</v>
       </c>
       <c r="F12" t="n">
-        <v>15.1996</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="13">
@@ -14381,17 +14918,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>49531</v>
       </c>
       <c r="E13" t="n">
         <v>325870.41</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>15.1996</v>
       </c>
     </row>
     <row r="14">
@@ -14407,17 +14944,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10290.41</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>325870.41</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14433,17 +14970,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>200</v>
+        <v>10290.41</v>
       </c>
       <c r="E15" t="n">
         <v>325870.41</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0614</v>
+        <v>3.1578</v>
       </c>
     </row>
     <row r="16">
@@ -14454,22 +14991,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>67050</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>824725.78</v>
+        <v>325870.41</v>
       </c>
       <c r="F16" t="n">
-        <v>8.130000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14480,22 +15017,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>466672</v>
+        <v>200</v>
       </c>
       <c r="E17" t="n">
-        <v>824725.78</v>
+        <v>325870.41</v>
       </c>
       <c r="F17" t="n">
-        <v>56.5851</v>
+        <v>0.0614</v>
       </c>
     </row>
     <row r="18">
@@ -14511,17 +15048,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>116578</v>
+        <v>67050</v>
       </c>
       <c r="E18" t="n">
         <v>824725.78</v>
       </c>
       <c r="F18" t="n">
-        <v>14.1354</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -14537,17 +15074,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>163500</v>
+        <v>466672</v>
       </c>
       <c r="E19" t="n">
         <v>824725.78</v>
       </c>
       <c r="F19" t="n">
-        <v>19.8248</v>
+        <v>56.5851</v>
       </c>
     </row>
     <row r="20">
@@ -14563,17 +15100,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>116578</v>
       </c>
       <c r="E20" t="n">
         <v>824725.78</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>14.1354</v>
       </c>
     </row>
     <row r="21">
@@ -14589,17 +15126,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1107.78</v>
+        <v>163500</v>
       </c>
       <c r="E21" t="n">
         <v>824725.78</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1343</v>
+        <v>19.8248</v>
       </c>
     </row>
     <row r="22">
@@ -14615,17 +15152,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9818</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>824725.78</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -14636,22 +15173,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6574</v>
+        <v>1107.78</v>
       </c>
       <c r="E23" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4545</v>
+        <v>0.1343</v>
       </c>
     </row>
     <row r="24">
@@ -14662,22 +15199,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22410</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -14688,22 +15225,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>152588</v>
+        <v>9818</v>
       </c>
       <c r="E25" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F25" t="n">
-        <v>10.5504</v>
+        <v>1.1905</v>
       </c>
     </row>
     <row r="26">
@@ -14719,17 +15256,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1077980</v>
+        <v>6574</v>
       </c>
       <c r="E26" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F26" t="n">
-        <v>74.535</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="27">
@@ -14745,17 +15282,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>99200</v>
+        <v>22410</v>
       </c>
       <c r="E27" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F27" t="n">
-        <v>6.859</v>
+        <v>1.5495</v>
       </c>
     </row>
     <row r="28">
@@ -14771,17 +15308,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19545</v>
+        <v>152588</v>
       </c>
       <c r="E28" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3514</v>
+        <v>10.5504</v>
       </c>
     </row>
     <row r="29">
@@ -14797,17 +15334,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67977.36</v>
+        <v>1077980</v>
       </c>
       <c r="E29" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F29" t="n">
-        <v>4.7002</v>
+        <v>74.535</v>
       </c>
     </row>
     <row r="30">
@@ -14818,22 +15355,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>99200</v>
       </c>
       <c r="E30" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>6.859</v>
       </c>
     </row>
     <row r="31">
@@ -14844,22 +15381,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>19545</v>
       </c>
       <c r="E31" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.3514</v>
       </c>
     </row>
     <row r="32">
@@ -14870,22 +15407,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16194</v>
+        <v>25200</v>
       </c>
       <c r="E32" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F32" t="n">
-        <v>2.751</v>
+        <v>1.7424</v>
       </c>
     </row>
     <row r="33">
@@ -14896,22 +15433,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>85080</v>
+        <v>42777.36</v>
       </c>
       <c r="E33" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F33" t="n">
-        <v>14.4531</v>
+        <v>2.9578</v>
       </c>
     </row>
     <row r="34">
@@ -14927,7 +15464,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -14953,7 +15490,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -14979,17 +15516,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>487390</v>
+        <v>16194</v>
       </c>
       <c r="E36" t="n">
         <v>588664</v>
       </c>
       <c r="F36" t="n">
-        <v>82.79600000000001</v>
+        <v>2.751</v>
       </c>
     </row>
     <row r="37">
@@ -15000,22 +15537,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>181525.57</v>
+        <v>85080</v>
       </c>
       <c r="E37" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F37" t="n">
-        <v>4.5737</v>
+        <v>14.4531</v>
       </c>
     </row>
     <row r="38">
@@ -15026,22 +15563,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1142004</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F38" t="n">
-        <v>28.7741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -15052,22 +15589,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>355326</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F39" t="n">
-        <v>8.9528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -15078,22 +15615,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1497534</v>
+        <v>65190</v>
       </c>
       <c r="E40" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F40" t="n">
-        <v>37.7321</v>
+        <v>11.0742</v>
       </c>
     </row>
     <row r="41">
@@ -15104,22 +15641,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>99200</v>
+        <v>422200</v>
       </c>
       <c r="E41" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F41" t="n">
-        <v>2.4995</v>
+        <v>71.7217</v>
       </c>
     </row>
     <row r="42">
@@ -15135,17 +15672,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>49696.78</v>
+        <v>181525.57</v>
       </c>
       <c r="E42" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2522</v>
+        <v>4.5737</v>
       </c>
     </row>
     <row r="43">
@@ -15161,28 +15698,28 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>643574.36</v>
+        <v>1142004</v>
       </c>
       <c r="E43" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F43" t="n">
-        <v>16.2156</v>
+        <v>28.7741</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -15191,24 +15728,24 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>61592</v>
+        <v>355326</v>
       </c>
       <c r="E44" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F44" t="n">
-        <v>5.1982</v>
+        <v>8.9528</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -15217,24 +15754,24 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8280</v>
+        <v>1497534</v>
       </c>
       <c r="E45" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6988</v>
+        <v>37.7321</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -15243,24 +15780,24 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>99200</v>
       </c>
       <c r="E46" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>2.4995</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -15269,65 +15806,65 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1112992</v>
+        <v>49696.78</v>
       </c>
       <c r="E47" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F47" t="n">
-        <v>93.9336</v>
+        <v>1.2522</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2007</v>
+        <v>90390</v>
       </c>
       <c r="E48" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1694</v>
+        <v>2.2775</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>139650</v>
+        <v>553184.36</v>
       </c>
       <c r="E49" t="n">
-        <v>183273</v>
+        <v>3968860.71</v>
       </c>
       <c r="F49" t="n">
-        <v>76.1978</v>
+        <v>13.9381</v>
       </c>
     </row>
     <row r="50">
@@ -15338,22 +15875,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>21480</v>
+        <v>61592</v>
       </c>
       <c r="E50" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F50" t="n">
-        <v>11.7202</v>
+        <v>5.1982</v>
       </c>
     </row>
     <row r="51">
@@ -15364,22 +15901,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>8280</v>
       </c>
       <c r="E51" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.6988</v>
       </c>
     </row>
     <row r="52">
@@ -15390,22 +15927,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17469</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F52" t="n">
-        <v>9.531700000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -15416,22 +15953,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4674</v>
+        <v>1112992</v>
       </c>
       <c r="E53" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F53" t="n">
-        <v>2.5503</v>
+        <v>93.9336</v>
       </c>
     </row>
     <row r="54">
@@ -15442,22 +15979,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>119960</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>153032.84</v>
+        <v>1184871</v>
       </c>
       <c r="F54" t="n">
-        <v>78.3884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -15468,22 +16005,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13200</v>
+        <v>2007</v>
       </c>
       <c r="E55" t="n">
-        <v>153032.84</v>
+        <v>1184871</v>
       </c>
       <c r="F55" t="n">
-        <v>8.6256</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="56">
@@ -15494,22 +16031,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>139650</v>
       </c>
       <c r="E56" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>76.1978</v>
       </c>
     </row>
     <row r="57">
@@ -15520,22 +16057,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>18256.84</v>
+        <v>21480</v>
       </c>
       <c r="E57" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F57" t="n">
-        <v>11.93</v>
+        <v>11.7202</v>
       </c>
     </row>
     <row r="58">
@@ -15546,22 +16083,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F58" t="n">
-        <v>1.056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -15572,22 +16109,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>483720</v>
+        <v>17469</v>
       </c>
       <c r="E59" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F59" t="n">
-        <v>50.0271</v>
+        <v>9.531700000000001</v>
       </c>
     </row>
     <row r="60">
@@ -15598,22 +16135,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>246780</v>
+        <v>1980</v>
       </c>
       <c r="E60" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F60" t="n">
-        <v>25.5224</v>
+        <v>1.0804</v>
       </c>
     </row>
     <row r="61">
@@ -15624,22 +16161,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>54600</v>
+        <v>2694</v>
       </c>
       <c r="E61" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F61" t="n">
-        <v>5.6468</v>
+        <v>1.4699</v>
       </c>
     </row>
     <row r="62">
@@ -15650,22 +16187,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>78122.14</v>
+        <v>119960</v>
       </c>
       <c r="E62" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F62" t="n">
-        <v>8.079499999999999</v>
+        <v>78.3884</v>
       </c>
     </row>
     <row r="63">
@@ -15676,22 +16213,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>103694</v>
+        <v>13200</v>
       </c>
       <c r="E63" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F63" t="n">
-        <v>10.7242</v>
+        <v>8.6256</v>
       </c>
     </row>
     <row r="64">
@@ -15702,22 +16239,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>421948</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F64" t="n">
-        <v>89.5044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -15728,22 +16265,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>26400</v>
+        <v>18256.84</v>
       </c>
       <c r="E65" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F65" t="n">
-        <v>5.6</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="66">
@@ -15754,19 +16291,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -15780,22 +16317,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>21080.65</v>
+        <v>1616</v>
       </c>
       <c r="E67" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F67" t="n">
-        <v>4.4717</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="68">
@@ -15806,22 +16343,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1998.68</v>
+        <v>483720</v>
       </c>
       <c r="E68" t="n">
-        <v>471427.33</v>
+        <v>966916.14</v>
       </c>
       <c r="F68" t="n">
-        <v>0.424</v>
+        <v>50.0271</v>
       </c>
     </row>
     <row r="69">
@@ -15832,22 +16369,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>280956</v>
+        <v>246780</v>
       </c>
       <c r="E69" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F69" t="n">
-        <v>68.01130000000001</v>
+        <v>25.5224</v>
       </c>
     </row>
     <row r="70">
@@ -15858,22 +16395,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>59200</v>
+        <v>54600</v>
       </c>
       <c r="E70" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F70" t="n">
-        <v>14.3306</v>
+        <v>5.6468</v>
       </c>
     </row>
     <row r="71">
@@ -15884,22 +16421,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>70400</v>
+        <v>78122.14</v>
       </c>
       <c r="E71" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F71" t="n">
-        <v>17.0418</v>
+        <v>8.079499999999999</v>
       </c>
     </row>
     <row r="72">
@@ -15910,22 +16447,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>200</v>
+        <v>3960</v>
       </c>
       <c r="E72" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0484</v>
+        <v>0.4095</v>
       </c>
     </row>
     <row r="73">
@@ -15936,7 +16473,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15945,13 +16482,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2346</v>
+        <v>99734</v>
       </c>
       <c r="E73" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F73" t="n">
-        <v>0.5679</v>
+        <v>10.3146</v>
       </c>
     </row>
     <row r="74">
@@ -15962,7 +16499,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -15971,13 +16508,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>146542</v>
+        <v>421948</v>
       </c>
       <c r="E74" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F74" t="n">
-        <v>9.9986</v>
+        <v>89.5044</v>
       </c>
     </row>
     <row r="75">
@@ -15988,7 +16525,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -15997,13 +16534,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>33000</v>
+        <v>26400</v>
       </c>
       <c r="E75" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F75" t="n">
-        <v>2.2516</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="76">
@@ -16014,7 +16551,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -16026,7 +16563,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -16040,7 +16577,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -16049,13 +16586,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3736.4</v>
+        <v>21080.65</v>
       </c>
       <c r="E77" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2549</v>
+        <v>4.4717</v>
       </c>
     </row>
     <row r="78">
@@ -16066,22 +16603,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1282342</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F78" t="n">
-        <v>87.4948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -16092,22 +16629,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>330466</v>
+        <v>1998.68</v>
       </c>
       <c r="E79" t="n">
-        <v>408765.21</v>
+        <v>471427.33</v>
       </c>
       <c r="F79" t="n">
-        <v>80.8449</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="80">
@@ -16118,22 +16655,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>33420</v>
+        <v>280956</v>
       </c>
       <c r="E80" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F80" t="n">
-        <v>8.175800000000001</v>
+        <v>68.01130000000001</v>
       </c>
     </row>
     <row r="81">
@@ -16144,22 +16681,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>59200</v>
       </c>
       <c r="E81" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>14.3306</v>
       </c>
     </row>
     <row r="82">
@@ -16170,22 +16707,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12301.21</v>
+        <v>70400</v>
       </c>
       <c r="E82" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F82" t="n">
-        <v>3.0094</v>
+        <v>17.0418</v>
       </c>
     </row>
     <row r="83">
@@ -16196,22 +16733,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>32578</v>
+        <v>200</v>
       </c>
       <c r="E83" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F83" t="n">
-        <v>7.9699</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="84">
@@ -16222,22 +16759,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>141738.01</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>684757.87</v>
+        <v>413102</v>
       </c>
       <c r="F84" t="n">
-        <v>20.699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -16248,22 +16785,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>109800</v>
+        <v>2346</v>
       </c>
       <c r="E85" t="n">
-        <v>684757.87</v>
+        <v>413102</v>
       </c>
       <c r="F85" t="n">
-        <v>16.0349</v>
+        <v>0.5679</v>
       </c>
     </row>
     <row r="86">
@@ -16274,22 +16811,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>146542</v>
       </c>
       <c r="E86" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>9.9986</v>
       </c>
     </row>
     <row r="87">
@@ -16300,22 +16837,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14327.36</v>
+        <v>33000</v>
       </c>
       <c r="E87" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F87" t="n">
-        <v>2.0923</v>
+        <v>2.2516</v>
       </c>
     </row>
     <row r="88">
@@ -16326,22 +16863,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>418892.5</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F88" t="n">
-        <v>61.1738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -16352,22 +16889,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>68574</v>
+        <v>3736.4</v>
       </c>
       <c r="E89" t="n">
-        <v>80605.8</v>
+        <v>1465620.4</v>
       </c>
       <c r="F89" t="n">
-        <v>85.0733</v>
+        <v>0.2549</v>
       </c>
     </row>
     <row r="90">
@@ -16378,22 +16915,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11640</v>
+        <v>71715</v>
       </c>
       <c r="E90" t="n">
-        <v>80605.8</v>
+        <v>1465620.4</v>
       </c>
       <c r="F90" t="n">
-        <v>14.4406</v>
+        <v>4.8931</v>
       </c>
     </row>
     <row r="91">
@@ -16404,22 +16941,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1210627</v>
       </c>
       <c r="E91" t="n">
-        <v>80605.8</v>
+        <v>1465620.4</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>82.60169999999999</v>
       </c>
     </row>
     <row r="92">
@@ -16430,22 +16967,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>124.8</v>
+        <v>330466</v>
       </c>
       <c r="E92" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1548</v>
+        <v>80.8449</v>
       </c>
     </row>
     <row r="93">
@@ -16456,22 +16993,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>267</v>
+        <v>33420</v>
       </c>
       <c r="E93" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3312</v>
+        <v>8.175800000000001</v>
       </c>
     </row>
     <row r="94">
@@ -16482,22 +17019,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>171462</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F94" t="n">
-        <v>65.20529999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -16508,22 +17045,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6600</v>
+        <v>12301.21</v>
       </c>
       <c r="E95" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F95" t="n">
-        <v>2.5099</v>
+        <v>3.0094</v>
       </c>
     </row>
     <row r="96">
@@ -16534,22 +17071,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F96" t="n">
-        <v>9.4312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -16560,22 +17097,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>32578</v>
       </c>
       <c r="E97" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>7.9699</v>
       </c>
     </row>
     <row r="98">
@@ -16586,22 +17123,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>60095</v>
+        <v>141738.01</v>
       </c>
       <c r="E98" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F98" t="n">
-        <v>22.8535</v>
+        <v>20.699</v>
       </c>
     </row>
     <row r="99">
@@ -16612,22 +17149,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>20000</v>
+        <v>109800</v>
       </c>
       <c r="E99" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F99" t="n">
-        <v>60.5697</v>
+        <v>16.0349</v>
       </c>
     </row>
     <row r="100">
@@ -16638,22 +17175,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1681</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F100" t="n">
-        <v>5.0909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -16664,22 +17201,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1000</v>
+        <v>14327.36</v>
       </c>
       <c r="E101" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F101" t="n">
-        <v>3.0285</v>
+        <v>2.0923</v>
       </c>
     </row>
     <row r="102">
@@ -16690,22 +17227,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>907.8</v>
+        <v>27820</v>
       </c>
       <c r="E102" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F102" t="n">
-        <v>2.7493</v>
+        <v>4.0627</v>
       </c>
     </row>
     <row r="103">
@@ -16716,7 +17253,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -16725,13 +17262,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>9431</v>
+        <v>391072.5</v>
       </c>
       <c r="E103" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F103" t="n">
-        <v>28.5617</v>
+        <v>57.1111</v>
       </c>
     </row>
     <row r="104">
@@ -16742,7 +17279,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -16751,13 +17288,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2386608.01</v>
+        <v>68574</v>
       </c>
       <c r="E104" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F104" t="n">
-        <v>37.8325</v>
+        <v>85.0733</v>
       </c>
     </row>
     <row r="105">
@@ -16768,7 +17305,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -16777,13 +17314,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>571481</v>
+        <v>11640</v>
       </c>
       <c r="E105" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F105" t="n">
-        <v>9.059100000000001</v>
+        <v>14.4406</v>
       </c>
     </row>
     <row r="106">
@@ -16794,7 +17331,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -16803,13 +17340,13 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>150800</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F106" t="n">
-        <v>2.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -16820,7 +17357,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -16829,13 +17366,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1279518.2</v>
+        <v>124.8</v>
       </c>
       <c r="E107" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F107" t="n">
-        <v>20.2829</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="108">
@@ -16846,22 +17383,516 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>80605.8</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>267</v>
+      </c>
+      <c r="E109" t="n">
+        <v>80605.8</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>171462</v>
+      </c>
+      <c r="E110" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F110" t="n">
+        <v>65.20529999999999</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E111" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.5099</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>24800</v>
+      </c>
+      <c r="E112" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9.4312</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>60095</v>
+      </c>
+      <c r="E115" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F115" t="n">
+        <v>22.8535</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E116" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F116" t="n">
+        <v>60.5697</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1681</v>
+      </c>
+      <c r="E117" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F117" t="n">
+        <v>5.0909</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E118" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3.0285</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>907.8</v>
+      </c>
+      <c r="E119" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.7493</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>9431</v>
+      </c>
+      <c r="E121" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F121" t="n">
+        <v>28.5617</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2386608.01</v>
+      </c>
+      <c r="E122" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F122" t="n">
+        <v>37.8325</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>571481</v>
+      </c>
+      <c r="E123" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9.059100000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>150800</v>
+      </c>
+      <c r="E124" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.3905</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1279518.2</v>
+      </c>
+      <c r="E125" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F125" t="n">
+        <v>20.2829</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>105475</v>
+      </c>
+      <c r="E126" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.672</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>1919941.18</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="D127" t="n">
+        <v>1814466.18</v>
+      </c>
+      <c r="E127" t="n">
         <v>6308348.39</v>
       </c>
-      <c r="F108" t="n">
-        <v>30.4349</v>
+      <c r="F127" t="n">
+        <v>28.7629</v>
       </c>
     </row>
   </sheetData>
@@ -25043,16 +26074,16 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>韩冰老师一百天疗愈计划</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>40000</v>
+        <v>23760</v>
       </c>
     </row>
     <row r="328">
@@ -25068,16 +26099,16 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>23760</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="329">
@@ -25098,11 +26129,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>源生衡十五株益生菌 （买五赠一）</t>
+          <t>韩冰老师一百天疗愈计划</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>1490</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="330">
@@ -25123,11 +26154,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>源生衡十五株益生菌 （买五赠一）</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>1440</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="331">
@@ -25393,16 +26424,16 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>青少年营地动力唤醒方案</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>199200</v>
+        <v>57420</v>
       </c>
     </row>
     <row r="342">
@@ -25418,16 +26449,16 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>青少年营地家族赋能方案</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>168000</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="343">
@@ -25448,11 +26479,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>青少年营地动力唤醒方案</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>57420</v>
+        <v>199200</v>
       </c>
     </row>
     <row r="344">
@@ -25473,11 +26504,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>青少年营地家族赋能方案</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>49800</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="345">
@@ -25498,11 +26529,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>7770</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="346">
@@ -29993,7 +31024,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -31993,16 +33024,16 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>韩冰老师一百天疗愈计划</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>80000</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="606">
@@ -32023,11 +33054,11 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>压力创伤释放工作坊</t>
+          <t>韩冰老师一百天疗愈计划</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>13860</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="607">
@@ -32048,11 +33079,11 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>压力创伤释放工作坊</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>3960</v>
+        <v>13860</v>
       </c>
     </row>
     <row r="608">
@@ -35993,16 +37024,16 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>青少年营地家族赋能方案</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E765" t="n">
-        <v>672000</v>
+        <v>62685</v>
       </c>
     </row>
     <row r="766">
@@ -36018,16 +37049,16 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>青少年营地动力唤醒方案</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E766" t="n">
-        <v>448200</v>
+        <v>9030</v>
       </c>
     </row>
     <row r="767">
@@ -36048,11 +37079,11 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>青少年营地家族赋能方案</t>
         </is>
       </c>
       <c r="E767" t="n">
-        <v>62685</v>
+        <v>672000</v>
       </c>
     </row>
     <row r="768">
@@ -36073,11 +37104,11 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>青少年营地动力唤醒方案</t>
         </is>
       </c>
       <c r="E768" t="n">
-        <v>49800</v>
+        <v>448200</v>
       </c>
     </row>
     <row r="769">
@@ -36098,11 +37129,11 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>未来之翼7日身心复能营</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E769" t="n">
-        <v>19800</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="770">
@@ -36123,11 +37154,11 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>未来之翼7日身心复能营</t>
         </is>
       </c>
       <c r="E770" t="n">
-        <v>9030</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="771">
@@ -36423,7 +37454,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>青少年19元巨量</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E782" t="n">
@@ -36448,7 +37479,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>青少年19元巨量</t>
         </is>
       </c>
       <c r="E783" t="n">
@@ -36523,7 +37554,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>青少年同行者一周家长短训营亲子教育网课</t>
         </is>
       </c>
       <c r="E786" t="n">
@@ -36548,7 +37579,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>青少年adq新链接XY</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E787" t="n">
@@ -36623,7 +37654,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>青少年同行者一周家长短训营亲子教育网课</t>
+          <t>青少年adq新链接XY</t>
         </is>
       </c>
       <c r="E790" t="n">
@@ -36723,7 +37754,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>0元青少年-LH</t>
         </is>
       </c>
       <c r="E794" t="n">
@@ -36748,7 +37779,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>0元青少年-LH</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E795" t="n">
@@ -36823,7 +37854,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>义诊-线上</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E798" t="n">
@@ -36848,7 +37879,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>义诊-线上</t>
         </is>
       </c>
       <c r="E799" t="n">
@@ -39218,16 +40249,16 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>青少年营地家族赋能方案</t>
+          <t>【青春进化论】亲子成长2日营</t>
         </is>
       </c>
       <c r="E894" t="n">
-        <v>168000</v>
+        <v>23760</v>
       </c>
     </row>
     <row r="895">
@@ -39243,16 +40274,16 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>青少年营地动力唤醒方案</t>
+          <t>【青春进化论】亲子成长2日营补差链接</t>
         </is>
       </c>
       <c r="E895" t="n">
-        <v>149400</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="896">
@@ -39273,11 +40304,11 @@
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>青少年营地家族赋能方案</t>
         </is>
       </c>
       <c r="E896" t="n">
-        <v>49800</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="897">
@@ -39298,11 +40329,11 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营</t>
+          <t>青少年营地动力唤醒方案</t>
         </is>
       </c>
       <c r="E897" t="n">
-        <v>23760</v>
+        <v>149400</v>
       </c>
     </row>
     <row r="898">
@@ -39323,11 +40354,11 @@
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>未来之翼7日心理能量唤醒营</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E898" t="n">
-        <v>19800</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="899">
@@ -39348,11 +40379,11 @@
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营补差链接</t>
+          <t>未来之翼7日心理能量唤醒营</t>
         </is>
       </c>
       <c r="E899" t="n">
-        <v>4060</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="900">
@@ -39898,7 +40929,7 @@
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E921" t="n">
@@ -39923,7 +40954,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E922" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -9253,7 +9253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9687,27 +9687,27 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2367650.54</v>
+        <v>1854900</v>
       </c>
       <c r="E15" t="n">
-        <v>3178</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>553184.36</v>
+        <v>372400</v>
       </c>
       <c r="G15" t="n">
-        <v>1814466.18</v>
+        <v>1482500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9716,16 +9716,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>181525.57</v>
+        <v>512750.54</v>
       </c>
       <c r="E16" t="n">
-        <v>5893</v>
+        <v>3149</v>
       </c>
       <c r="F16" t="n">
-        <v>181525.57</v>
+        <v>180784.36</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>331966.18</v>
       </c>
     </row>
     <row r="17">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9745,13 +9745,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="E17" t="n">
-        <v>234</v>
+        <v>5893</v>
       </c>
       <c r="F17" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="F18" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -9799,17 +9799,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>新客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>345326</v>
+        <v>355326</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
-        <v>345326</v>
+        <v>355326</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -9828,17 +9828,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>老客</t>
+          <t>新客</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10000</v>
+        <v>345326</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="F20" t="n">
-        <v>10000</v>
+        <v>345326</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9852,22 +9852,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>老客</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1497534</v>
+        <v>10000</v>
       </c>
       <c r="E21" t="n">
-        <v>270</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>1497534</v>
+        <v>10000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9886,17 +9886,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>少年说</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1116610</v>
+        <v>1497534</v>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="F22" t="n">
-        <v>1116610</v>
+        <v>1497534</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -9915,17 +9915,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>家守</t>
+          <t>少年说</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>380924</v>
+        <v>1116610</v>
       </c>
       <c r="E23" t="n">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
-        <v>380924</v>
+        <v>1116610</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9939,22 +9939,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>家守</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>99200</v>
+        <v>380924</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="F24" t="n">
-        <v>99200</v>
+        <v>380924</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9977,13 +9977,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="E25" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -10002,17 +10002,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37785.67</v>
+        <v>49696.78</v>
       </c>
       <c r="E26" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F26" t="n">
-        <v>37785.67</v>
+        <v>49696.78</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -10031,17 +10031,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11911.11</v>
+        <v>37785.67</v>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="F27" t="n">
-        <v>11911.11</v>
+        <v>37785.67</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -10055,22 +10055,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>90390</v>
+        <v>11911.11</v>
       </c>
       <c r="E28" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
-        <v>90390</v>
+        <v>11911.11</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -10093,13 +10093,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>553184.36</v>
+        <v>90390</v>
       </c>
       <c r="E29" t="n">
-        <v>315</v>
+        <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>553184.36</v>
+        <v>90390</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -10108,12 +10108,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -10122,45 +10122,45 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2386608.01</v>
+        <v>372400</v>
       </c>
       <c r="E30" t="n">
-        <v>582</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
+        <v>372400</v>
+      </c>
+      <c r="G30" t="n">
         <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2386608.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>老客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1910462.01</v>
+        <v>180784.36</v>
       </c>
       <c r="E31" t="n">
-        <v>392</v>
+        <v>309</v>
       </c>
       <c r="F31" t="n">
+        <v>180784.36</v>
+      </c>
+      <c r="G31" t="n">
         <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1910462.01</v>
       </c>
     </row>
     <row r="32">
@@ -10176,20 +10176,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>新客</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>418748</v>
+        <v>2386608.01</v>
       </c>
       <c r="E32" t="n">
-        <v>183</v>
+        <v>582</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>418748</v>
+        <v>2386608.01</v>
       </c>
     </row>
     <row r="33">
@@ -10200,25 +10200,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>老客</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>571481</v>
+        <v>1910462.01</v>
       </c>
       <c r="E33" t="n">
-        <v>74</v>
+        <v>392</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>571481</v>
+        <v>1910462.01</v>
       </c>
     </row>
     <row r="34">
@@ -10229,25 +10229,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>少年说</t>
+          <t>新客</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>330240</v>
+        <v>418748</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>330240</v>
+        <v>418748</v>
       </c>
     </row>
     <row r="35">
@@ -10263,20 +10263,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>家守</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>241241</v>
+        <v>571481</v>
       </c>
       <c r="E35" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>241241</v>
+        <v>571481</v>
       </c>
     </row>
     <row r="36">
@@ -10287,25 +10287,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>少年说</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>150800</v>
+        <v>330240</v>
       </c>
       <c r="E36" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>150800</v>
+        <v>330240</v>
       </c>
     </row>
     <row r="37">
@@ -10316,25 +10316,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>家守</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1279518.2</v>
+        <v>241241</v>
       </c>
       <c r="E37" t="n">
-        <v>2105</v>
+        <v>32</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1279518.2</v>
+        <v>241241</v>
       </c>
     </row>
     <row r="38">
@@ -10345,25 +10345,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>复诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>824010.16</v>
+        <v>150800</v>
       </c>
       <c r="E38" t="n">
-        <v>916</v>
+        <v>21</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>824010.16</v>
+        <v>150800</v>
       </c>
     </row>
     <row r="39">
@@ -10379,20 +10379,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>初诊</t>
+          <t>（合计）</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>455508.04</v>
+        <v>1279518.2</v>
       </c>
       <c r="E39" t="n">
-        <v>1189</v>
+        <v>2105</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>455508.04</v>
+        <v>1279518.2</v>
       </c>
     </row>
     <row r="40">
@@ -10403,25 +10403,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>复诊</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>105475</v>
+        <v>824010.16</v>
       </c>
       <c r="E40" t="n">
-        <v>77</v>
+        <v>916</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>105475</v>
+        <v>824010.16</v>
       </c>
     </row>
     <row r="41">
@@ -10432,25 +10432,112 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>（合计）</t>
+          <t>初诊</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1814466.18</v>
+        <v>455508.04</v>
       </c>
       <c r="E41" t="n">
-        <v>2863</v>
+        <v>1189</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1814466.18</v>
+        <v>455508.04</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>105475</v>
+      </c>
+      <c r="E42" t="n">
+        <v>77</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>105475</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1482500</v>
+      </c>
+      <c r="E43" t="n">
+        <v>23</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1482500</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>331966.18</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2840</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>331966.18</v>
       </c>
     </row>
   </sheetData>
@@ -10683,15 +10770,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>82.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>其他 1210627.0；咨询 146542.0；进化论 71715.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
+          <t>营地 1145200.0；咨询 146542.0；进化论 71715.0；其他 65427.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -10739,15 +10826,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57.1</v>
+        <v>49.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>其他 391072.5；咨询 141738.01；家守/千金方/少年说 109800.0；进化论 27820.0；医疗 14327.36</t>
+          <t>营地 337300.0；咨询 141738.01；家守/千金方/少年说 109800.0；其他 53772.5；进化论 27820.0；医疗 14327.36</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10918,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>咨询 20000.0；其他 9431.0；家守/千金方/少年说 1681.0；菌群 1000.0；医疗 907.8</t>
+          <t>咨询 20000.0；其他 9431.0；家守/千金方/少年说 1681.0；菌群 1000.0；医疗 907.8；营地 0.0</t>
         </is>
       </c>
     </row>
@@ -11019,15 +11106,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>82.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>其他 1210627.0；咨询 146542.0；进化论 71715.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
+          <t>营地 1145200.0；咨询 146542.0；进化论 71715.0；其他 65427.0；家守/千金方/少年说 33000.0；医疗 3736.4；菌群 0.0</t>
         </is>
       </c>
     </row>
@@ -11075,15 +11162,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>57.1</v>
+        <v>49.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>其他 391072.5；咨询 141738.01；家守/千金方/少年说 109800.0；进化论 27820.0；医疗 14327.36</t>
+          <t>营地 337300.0；咨询 141738.01；家守/千金方/少年说 109800.0；其他 53772.5；进化论 27820.0；医疗 14327.36</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11254,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>咨询 20000.0；其他 9431.0；家守/千金方/少年说 1681.0；菌群 1000.0；医疗 907.8</t>
+          <t>咨询 20000.0；其他 9431.0；家守/千金方/少年说 1681.0；菌群 1000.0；医疗 907.8；营地 0.0</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12025,7 +12112,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -12048,7 +12135,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -12071,7 +12158,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -12083,7 +12170,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>267600</v>
+        <v>217800</v>
       </c>
     </row>
     <row r="40">
@@ -12094,7 +12181,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -12106,7 +12193,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>217900</v>
+        <v>168100</v>
       </c>
     </row>
     <row r="41">
@@ -12117,7 +12204,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -12135,12 +12222,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -12148,22 +12235,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1280</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -12171,22 +12258,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1280</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -12194,22 +12281,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>章浩进</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1280</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -12217,22 +12304,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>梁志前</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1280</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -12240,11 +12327,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1280</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="47">
@@ -12255,7 +12342,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -12263,11 +12350,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>169320</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="48">
@@ -12278,7 +12365,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -12286,11 +12373,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103300</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="49">
@@ -12301,7 +12388,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -12309,11 +12396,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>89042</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="50">
@@ -12324,7 +12411,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -12332,11 +12419,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>79381</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="51">
@@ -12347,7 +12434,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -12355,11 +12442,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>75910</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="52">
@@ -12370,7 +12457,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -12378,11 +12465,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53194</v>
+        <v>169320</v>
       </c>
     </row>
     <row r="53">
@@ -12393,7 +12480,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -12401,11 +12488,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>30796</v>
+        <v>103300</v>
       </c>
     </row>
     <row r="54">
@@ -12416,7 +12503,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -12424,11 +12511,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>30398</v>
+        <v>89042</v>
       </c>
     </row>
     <row r="55">
@@ -12439,7 +12526,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -12447,11 +12534,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>24598</v>
+        <v>79381</v>
       </c>
     </row>
     <row r="56">
@@ -12462,7 +12549,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -12470,11 +12557,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20000</v>
+        <v>75910</v>
       </c>
     </row>
     <row r="57">
@@ -12485,7 +12572,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -12493,11 +12580,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>165000</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="58">
@@ -12508,7 +12595,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -12516,11 +12603,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>132000</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="59">
@@ -12531,7 +12618,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -12539,11 +12626,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>109640</v>
+        <v>30398</v>
       </c>
     </row>
     <row r="60">
@@ -12554,7 +12641,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -12562,11 +12649,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>109020</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="61">
@@ -12577,7 +12664,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -12585,11 +12672,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103200</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="62">
@@ -12600,7 +12687,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -12608,11 +12695,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>49600</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="63">
@@ -12623,7 +12710,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -12631,11 +12718,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>24800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="64">
@@ -12646,7 +12733,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -12654,11 +12741,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>24800</v>
+        <v>109640</v>
       </c>
     </row>
     <row r="65">
@@ -12669,7 +12756,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -12677,11 +12764,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>109020</v>
       </c>
     </row>
     <row r="66">
@@ -12692,7 +12779,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -12700,11 +12787,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>103200</v>
       </c>
     </row>
     <row r="67">
@@ -12715,7 +12802,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -12727,7 +12814,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>16800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="68">
@@ -12738,7 +12825,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -12746,11 +12833,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1200</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="69">
@@ -12761,7 +12848,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -12773,7 +12860,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>500</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="70">
@@ -12784,7 +12871,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -12792,11 +12879,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -12807,7 +12894,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -12815,11 +12902,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -12830,7 +12917,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -12838,11 +12925,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>陈鑫</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>24750</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="73">
@@ -12853,7 +12940,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -12861,11 +12948,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21780</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="74">
@@ -12876,7 +12963,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -12884,11 +12971,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>余文静</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>14400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75">
@@ -12899,7 +12986,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -12907,11 +12994,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>吴云龙</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>7480</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76">
@@ -12922,7 +13009,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -12930,11 +13017,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>魏恺志</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77">
@@ -12945,7 +13032,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -12957,7 +13044,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>267600</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="78">
@@ -12968,7 +13055,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -12976,11 +13063,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>姚闯</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>49800</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="79">
@@ -12991,7 +13078,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -12999,11 +13086,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>杨旺忠</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>49800</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="80">
@@ -13014,7 +13101,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -13026,7 +13113,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>49800</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="81">
@@ -13037,7 +13124,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -13045,22 +13132,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>魏恺志</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>40000</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -13068,22 +13155,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>233168</v>
+        <v>217800</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -13091,22 +13178,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>姚闯</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>158786</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -13114,22 +13201,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>吴云龙</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>91194</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -13137,22 +13224,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>杨旺忠</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>85698</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -13160,22 +13247,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>81982</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -13183,22 +13270,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>164220</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -13206,22 +13293,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄慧作</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>90000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -13229,22 +13316,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>46200</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -13252,22 +13339,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>26820</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -13275,11 +13362,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>26200</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="92">
@@ -13290,7 +13377,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -13302,7 +13389,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>54600</v>
+        <v>233168</v>
       </c>
     </row>
     <row r="93">
@@ -13313,7 +13400,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -13321,11 +13408,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>45600</v>
+        <v>158786</v>
       </c>
     </row>
     <row r="94">
@@ -13336,7 +13423,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -13344,11 +13431,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>24800</v>
+        <v>91194</v>
       </c>
     </row>
     <row r="95">
@@ -13359,7 +13446,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -13367,11 +13454,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>24800</v>
+        <v>85698</v>
       </c>
     </row>
     <row r="96">
@@ -13382,7 +13469,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -13390,11 +13477,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>王秀丽</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1000</v>
+        <v>81982</v>
       </c>
     </row>
     <row r="97">
@@ -13405,7 +13492,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -13413,11 +13500,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>245315.88</v>
+        <v>164220</v>
       </c>
     </row>
     <row r="98">
@@ -13428,7 +13515,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -13436,11 +13523,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>黄慧作</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>196025.61</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="99">
@@ -13451,7 +13538,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -13459,11 +13546,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>190639.29</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="100">
@@ -13474,7 +13561,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -13482,11 +13569,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>157856.3</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="101">
@@ -13497,7 +13584,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -13505,11 +13592,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105286</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="102">
@@ -13520,7 +13607,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -13528,11 +13615,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>高丹</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>16520</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="103">
@@ -13543,7 +13630,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -13551,11 +13638,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>徐艳霞</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>9900</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="104">
@@ -13566,7 +13653,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -13574,11 +13661,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>郭海明</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>8560</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="105">
@@ -13589,7 +13676,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -13597,11 +13684,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>章浩进</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>8100</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="106">
@@ -13612,7 +13699,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -13620,11 +13707,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>韦新妮</t>
+          <t>王秀丽</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>7920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="107">
@@ -13635,7 +13722,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -13643,11 +13730,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>胡炫明</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>391000</v>
+        <v>245315.88</v>
       </c>
     </row>
     <row r="108">
@@ -13658,7 +13745,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -13666,11 +13753,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>徐艳霞</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>267600</v>
+        <v>196025.61</v>
       </c>
     </row>
     <row r="109">
@@ -13681,7 +13768,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -13689,11 +13776,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>梁志前</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>217900</v>
+        <v>190639.29</v>
       </c>
     </row>
     <row r="110">
@@ -13704,7 +13791,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -13712,11 +13799,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>陈磊</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>168000</v>
+        <v>157856.3</v>
       </c>
     </row>
     <row r="111">
@@ -13727,7 +13814,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -13735,11 +13822,356 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>胡威特</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="E111" t="n">
+        <v>105286</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>高丹</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>16520</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>徐艳霞</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>郭海明</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>8560</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>章浩进</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>5</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>韦新妮</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>胡炫明</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>391000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>徐艳霞</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>267600</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>梁志前</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>168100</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>陈磊</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>168000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>5</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>张佳慧</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
         <v>99600</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>张虹</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>梁志前</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>49800</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>章浩进</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>49800</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>4</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>陈翔宇</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>5</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>岳伟伟</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>33956</v>
       </c>
     </row>
   </sheetData>
@@ -13753,7 +14185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14056,65 +14488,65 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2367650.54</v>
+        <v>1854900</v>
       </c>
       <c r="D9" t="n">
-        <v>612908.59</v>
+        <v>391600</v>
       </c>
       <c r="E9" t="n">
-        <v>27052</v>
+        <v>20100</v>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="G9" t="n">
-        <v>585856.59</v>
+        <v>371500</v>
       </c>
       <c r="H9" t="n">
-        <v>24.74</v>
+        <v>20.03</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0</t>
+          <t>青少年营地动力唤醒方案 85000.0；青少年成长基地3月营（金盏基地） 83600.0；青少年营地家族赋能方案 80000.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>全部</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>181525.57</v>
+        <v>512750.54</v>
       </c>
       <c r="D10" t="n">
-        <v>22555</v>
+        <v>221308.59</v>
       </c>
       <c r="E10" t="n">
-        <v>18920</v>
+        <v>6952</v>
       </c>
       <c r="F10" t="n">
-        <v>10.42</v>
+        <v>1.36</v>
       </c>
       <c r="G10" t="n">
-        <v>3635</v>
+        <v>214356.59</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>41.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 3588.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 2560.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1688.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；青少年身心复能成长方案 80000.0；【廖文婷】萨提亚家庭系统工作坊 5940.0</t>
         </is>
       </c>
     </row>
@@ -14126,30 +14558,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1142004</v>
+        <v>181525.57</v>
       </c>
       <c r="D11" t="n">
-        <v>193920.44</v>
+        <v>22555</v>
       </c>
       <c r="E11" t="n">
-        <v>4980</v>
+        <v>18920</v>
       </c>
       <c r="F11" t="n">
-        <v>0.44</v>
+        <v>10.42</v>
       </c>
       <c r="G11" t="n">
-        <v>188940.44</v>
+        <v>3635</v>
       </c>
       <c r="H11" t="n">
-        <v>16.54</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>青少年同行者计划领航营 118165.4；青少年同行者计划-护航营 21578.0；青少年同行者计划向阳营 14593.37</t>
+          <t>青春期家庭困扰21天陪跑指导训练亲子教育网课（已购1280、4980家长勿买） 3588.0；（家长学）韩冰老师智慧父母成长营网课-帮助家长应对孩子厌学休学叛逆情绪等问题 2560.0；青少年家庭成长同行者计划一周家长网课-帮家长应对孩子厌学休学叛逆情绪低落等 1688.0</t>
         </is>
       </c>
     </row>
@@ -14161,30 +14593,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>355326</v>
+        <v>1142004</v>
       </c>
       <c r="D12" t="n">
-        <v>143025.9</v>
+        <v>193920.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G12" t="n">
-        <v>143025.9</v>
+        <v>188940.44</v>
       </c>
       <c r="H12" t="n">
-        <v>40.25</v>
+        <v>16.54</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>儿童青少年 63298.0；精神心理 61198.0；青少年-资深咨询 18500.0</t>
+          <t>青少年同行者计划领航营 118165.4；青少年同行者计划-护航营 21578.0；青少年同行者计划向阳营 14593.37</t>
         </is>
       </c>
     </row>
@@ -14196,30 +14628,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1497534</v>
+        <v>355326</v>
       </c>
       <c r="D13" t="n">
-        <v>145410</v>
+        <v>143025.9</v>
       </c>
       <c r="E13" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>143730</v>
+        <v>143025.9</v>
       </c>
       <c r="H13" t="n">
-        <v>9.6</v>
+        <v>40.25</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
+          <t>儿童青少年 63298.0；精神心理 61198.0；青少年-资深咨询 18500.0</t>
         </is>
       </c>
     </row>
@@ -14231,30 +14663,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>99200</v>
+        <v>1497534</v>
       </c>
       <c r="D14" t="n">
-        <v>121000</v>
+        <v>145410</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G14" t="n">
-        <v>121000</v>
+        <v>143730</v>
       </c>
       <c r="H14" t="n">
-        <v>121.98</v>
+        <v>9.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>肠道菌群移植 74400.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
+          <t>家庭守护计划2.0（二阶） 58620.0；少年说陪伴计划 52800.0；家庭守护计划2.0一阶（4980补差价产品） 14820.0</t>
         </is>
       </c>
     </row>
@@ -14266,14 +14698,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>49696.78</v>
+        <v>99200</v>
       </c>
       <c r="D15" t="n">
-        <v>778</v>
+        <v>121000</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14282,14 +14714,14 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>778</v>
+        <v>121000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.57</v>
+        <v>121.98</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
+          <t>肠道菌群移植 74400.0；肠道菌群移植（双疗程） 45600.0；肠道菌群检测 1000.0</t>
         </is>
       </c>
     </row>
@@ -14301,30 +14733,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90390</v>
+        <v>49696.78</v>
       </c>
       <c r="D16" t="n">
-        <v>15940</v>
+        <v>778</v>
       </c>
       <c r="E16" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>13860</v>
+        <v>778</v>
       </c>
       <c r="H16" t="n">
-        <v>15.33</v>
+        <v>1.57</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营 13860.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 100.0</t>
+          <t>20分钟问诊（专家医师） -线上 500.0；20分钟问诊（医师） -线上 200.0；AI测评V9.0-多维父母教养行为测评 49.0</t>
         </is>
       </c>
     </row>
@@ -14336,100 +14768,100 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>553184.36</v>
+        <v>90390</v>
       </c>
       <c r="D17" t="n">
-        <v>274150.59</v>
+        <v>15940</v>
       </c>
       <c r="E17" t="n">
-        <v>999</v>
+        <v>2080</v>
       </c>
       <c r="F17" t="n">
-        <v>0.18</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>273151.59</v>
+        <v>13860</v>
       </c>
       <c r="H17" t="n">
-        <v>49.38</v>
+        <v>15.33</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；蛋壳跳动身心复能营21天（一阶） 74200.0；青少年成长基地3月营（金盏基地） 46800.0</t>
+          <t>【青春进化论】亲子成长2日营 13860.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 100.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2386608.01</v>
+        <v>372400</v>
       </c>
       <c r="D18" t="n">
-        <v>409927.33</v>
+        <v>156100</v>
       </c>
       <c r="E18" t="n">
-        <v>10398</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>399529.33</v>
+        <v>156100</v>
       </c>
       <c r="H18" t="n">
-        <v>16.74</v>
+        <v>41.92</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>儿童青少年 286931.33；电商咨询 37500.0；精神心理 32798.0</t>
+          <t>蛋壳跳动身心复能营21天（一阶） 74200.0；青少年成长基地3月营（金盏基地） 46800.0；未来王者（AI探索&amp;学习力营） 16800.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>571481</v>
+        <v>180784.36</v>
       </c>
       <c r="D19" t="n">
-        <v>68520</v>
+        <v>118050.59</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="G19" t="n">
-        <v>68520</v>
+        <v>117051.59</v>
       </c>
       <c r="H19" t="n">
-        <v>11.99</v>
+        <v>64.75</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
+          <t>心灯计划-实战派心理咨询师执业培训项目（初阶+中阶） 100835.88；8周系统性心身综合干预+深度服务包（全国统一价） 3900.0；心理咨询师职业能力水平评价考试培训 3800.0</t>
         </is>
       </c>
     </row>
@@ -14441,30 +14873,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>150800</v>
+        <v>2386608.01</v>
       </c>
       <c r="D20" t="n">
-        <v>115000</v>
+        <v>409927.33</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G20" t="n">
-        <v>115000</v>
+        <v>399529.33</v>
       </c>
       <c r="H20" t="n">
-        <v>76.26000000000001</v>
+        <v>16.74</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>肠道菌群移植 47600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
+          <t>儿童青少年 286931.33；电商咨询 37500.0；精神心理 32798.0</t>
         </is>
       </c>
     </row>
@@ -14476,30 +14908,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1279518.2</v>
+        <v>571481</v>
       </c>
       <c r="D21" t="n">
-        <v>5541.59</v>
+        <v>68520</v>
       </c>
       <c r="E21" t="n">
-        <v>1941.59</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>3600</v>
+        <v>68520</v>
       </c>
       <c r="H21" t="n">
-        <v>0.28</v>
+        <v>11.99</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>线上/线下门诊 3200.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
+          <t>家庭守护计划2.0（三阶） 26310.0；家庭守护计划2.0（一阶） 23970.0；少年说陪伴计划 13200.0</t>
         </is>
       </c>
     </row>
@@ -14511,30 +14943,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>105475</v>
+        <v>150800</v>
       </c>
       <c r="D22" t="n">
-        <v>41310</v>
+        <v>115000</v>
       </c>
       <c r="E22" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>39330</v>
+        <v>115000</v>
       </c>
       <c r="H22" t="n">
-        <v>37.29</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>【青春进化论】亲子成长2日营 39150.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 180.0</t>
+          <t>肠道菌群移植 47600.0；肠道菌群移植（双疗程） 45600.0；肠道菌群移植（双疗程优惠） 20800.0</t>
         </is>
       </c>
     </row>
@@ -14546,30 +14978,135 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1279518.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5541.59</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1941.59</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>线上/线下门诊 3200.0；【组合装】维研素 PS 磷脂酰丝氨酸+神经酸-甘磷酸胆碱--- 1341.59；20分钟问诊（医师） -线上 600.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>105475</v>
+      </c>
+      <c r="D24" t="n">
+        <v>41310</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G24" t="n">
+        <v>39330</v>
+      </c>
+      <c r="H24" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>【青春进化论】亲子成长2日营 39150.0；青春进化论（两日制亲子营） 1980.0；【青春进化论】亲子成长2日营补差链接 180.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1482500</v>
+      </c>
+      <c r="D25" t="n">
+        <v>235500</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20100</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G25" t="n">
+        <v>215400</v>
+      </c>
+      <c r="H25" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>青少年营地动力唤醒方案 85000.0；青少年营地家族赋能方案 80000.0；青少年成长基地3月营（金盏基地） 36800.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1814466.18</v>
-      </c>
-      <c r="D23" t="n">
-        <v>338758</v>
-      </c>
-      <c r="E23" t="n">
-        <v>26053</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G23" t="n">
-        <v>312705</v>
-      </c>
-      <c r="H23" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>青少年营地动力唤醒方案 85000.0；青少年营地家族赋能方案 80000.0；青少年身心复能成长方案 80000.0</t>
+      <c r="C26" t="n">
+        <v>331966.18</v>
+      </c>
+      <c r="D26" t="n">
+        <v>103258</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5953</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G26" t="n">
+        <v>97305</v>
+      </c>
+      <c r="H26" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>青少年身心复能成长方案 80000.0；完形心理成长计划 4999.0；青少年同行者计划之领航营亲子教育网课 4980.0</t>
         </is>
       </c>
     </row>
@@ -14584,7 +15121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14814,17 +15351,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78189</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>783326.16</v>
       </c>
       <c r="F9" t="n">
-        <v>9.9817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -14835,22 +15372,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>观懋组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37895</v>
+        <v>78189</v>
       </c>
       <c r="E10" t="n">
-        <v>325870.41</v>
+        <v>783326.16</v>
       </c>
       <c r="F10" t="n">
-        <v>11.6289</v>
+        <v>9.9817</v>
       </c>
     </row>
     <row r="11">
@@ -14866,17 +15403,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>216560</v>
+        <v>37895</v>
       </c>
       <c r="E11" t="n">
         <v>325870.41</v>
       </c>
       <c r="F11" t="n">
-        <v>66.4559</v>
+        <v>11.6289</v>
       </c>
     </row>
     <row r="12">
@@ -14892,17 +15429,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11394</v>
+        <v>216560</v>
       </c>
       <c r="E12" t="n">
         <v>325870.41</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4965</v>
+        <v>66.4559</v>
       </c>
     </row>
     <row r="13">
@@ -14918,17 +15455,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>49531</v>
+        <v>11394</v>
       </c>
       <c r="E13" t="n">
         <v>325870.41</v>
       </c>
       <c r="F13" t="n">
-        <v>15.1996</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="14">
@@ -14944,17 +15481,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>49531</v>
       </c>
       <c r="E14" t="n">
         <v>325870.41</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>15.1996</v>
       </c>
     </row>
     <row r="15">
@@ -14970,17 +15507,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10290.41</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>325870.41</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14996,17 +15533,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>10290.41</v>
       </c>
       <c r="E16" t="n">
         <v>325870.41</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3.1578</v>
       </c>
     </row>
     <row r="17">
@@ -15022,17 +15559,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>325870.41</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15043,22 +15580,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67050</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>824725.78</v>
+        <v>325870.41</v>
       </c>
       <c r="F18" t="n">
-        <v>8.130000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15069,22 +15606,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>初心组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>466672</v>
+        <v>200</v>
       </c>
       <c r="E19" t="n">
-        <v>824725.78</v>
+        <v>325870.41</v>
       </c>
       <c r="F19" t="n">
-        <v>56.5851</v>
+        <v>0.0614</v>
       </c>
     </row>
     <row r="20">
@@ -15100,17 +15637,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>116578</v>
+        <v>67050</v>
       </c>
       <c r="E20" t="n">
         <v>824725.78</v>
       </c>
       <c r="F20" t="n">
-        <v>14.1354</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -15126,17 +15663,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>163500</v>
+        <v>466672</v>
       </c>
       <c r="E21" t="n">
         <v>824725.78</v>
       </c>
       <c r="F21" t="n">
-        <v>19.8248</v>
+        <v>56.5851</v>
       </c>
     </row>
     <row r="22">
@@ -15152,17 +15689,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>116578</v>
       </c>
       <c r="E22" t="n">
         <v>824725.78</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>14.1354</v>
       </c>
     </row>
     <row r="23">
@@ -15178,17 +15715,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1107.78</v>
+        <v>163500</v>
       </c>
       <c r="E23" t="n">
         <v>824725.78</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1343</v>
+        <v>19.8248</v>
       </c>
     </row>
     <row r="24">
@@ -15204,7 +15741,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -15230,17 +15767,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9818</v>
+        <v>1107.78</v>
       </c>
       <c r="E25" t="n">
         <v>824725.78</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1905</v>
+        <v>0.1343</v>
       </c>
     </row>
     <row r="26">
@@ -15251,22 +15788,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6574</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -15277,22 +15814,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22410</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -15303,22 +15840,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>观鼎组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>152588</v>
+        <v>9818</v>
       </c>
       <c r="E28" t="n">
-        <v>1446274.36</v>
+        <v>824725.78</v>
       </c>
       <c r="F28" t="n">
-        <v>10.5504</v>
+        <v>1.1905</v>
       </c>
     </row>
     <row r="29">
@@ -15334,17 +15871,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1077980</v>
+        <v>6574</v>
       </c>
       <c r="E29" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F29" t="n">
-        <v>74.535</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="30">
@@ -15360,17 +15897,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>99200</v>
+        <v>22410</v>
       </c>
       <c r="E30" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F30" t="n">
-        <v>6.859</v>
+        <v>1.5495</v>
       </c>
     </row>
     <row r="31">
@@ -15386,17 +15923,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19545</v>
+        <v>152588</v>
       </c>
       <c r="E31" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3514</v>
+        <v>10.5504</v>
       </c>
     </row>
     <row r="32">
@@ -15412,17 +15949,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>25200</v>
+        <v>1077980</v>
       </c>
       <c r="E32" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7424</v>
+        <v>74.535</v>
       </c>
     </row>
     <row r="33">
@@ -15438,17 +15975,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>42777.36</v>
+        <v>99200</v>
       </c>
       <c r="E33" t="n">
         <v>1446274.36</v>
       </c>
       <c r="F33" t="n">
-        <v>2.9578</v>
+        <v>6.859</v>
       </c>
     </row>
     <row r="34">
@@ -15459,22 +15996,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>19545</v>
       </c>
       <c r="E34" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.3514</v>
       </c>
     </row>
     <row r="35">
@@ -15485,22 +16022,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="E35" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.7424</v>
       </c>
     </row>
     <row r="36">
@@ -15511,22 +16048,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16194</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F36" t="n">
-        <v>2.751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -15537,22 +16074,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>85080</v>
+        <v>42777.36</v>
       </c>
       <c r="E37" t="n">
-        <v>588664</v>
+        <v>1446274.36</v>
       </c>
       <c r="F37" t="n">
-        <v>14.4531</v>
+        <v>2.9578</v>
       </c>
     </row>
     <row r="38">
@@ -15568,7 +16105,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -15594,7 +16131,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -15620,17 +16157,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>65190</v>
+        <v>16194</v>
       </c>
       <c r="E40" t="n">
         <v>588664</v>
       </c>
       <c r="F40" t="n">
-        <v>11.0742</v>
+        <v>2.751</v>
       </c>
     </row>
     <row r="41">
@@ -15646,17 +16183,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>422200</v>
+        <v>85080</v>
       </c>
       <c r="E41" t="n">
         <v>588664</v>
       </c>
       <c r="F41" t="n">
-        <v>71.7217</v>
+        <v>14.4531</v>
       </c>
     </row>
     <row r="42">
@@ -15667,22 +16204,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>体验课</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>181525.57</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F42" t="n">
-        <v>4.5737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -15693,22 +16230,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>正价课4980/3980</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1142004</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F43" t="n">
-        <v>28.7741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -15719,22 +16256,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>355326</v>
+        <v>65190</v>
       </c>
       <c r="E44" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F44" t="n">
-        <v>8.9528</v>
+        <v>11.0742</v>
       </c>
     </row>
     <row r="45">
@@ -15745,22 +16282,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1497534</v>
+        <v>372400</v>
       </c>
       <c r="E45" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F45" t="n">
-        <v>37.7321</v>
+        <v>63.2619</v>
       </c>
     </row>
     <row r="46">
@@ -15771,22 +16308,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>99200</v>
+        <v>49800</v>
       </c>
       <c r="E46" t="n">
-        <v>3968860.71</v>
+        <v>588664</v>
       </c>
       <c r="F46" t="n">
-        <v>2.4995</v>
+        <v>8.4598</v>
       </c>
     </row>
     <row r="47">
@@ -15802,17 +16339,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>体验课</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>49696.78</v>
+        <v>181525.57</v>
       </c>
       <c r="E47" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F47" t="n">
-        <v>1.2522</v>
+        <v>4.5737</v>
       </c>
     </row>
     <row r="48">
@@ -15828,17 +16365,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>正价课4980/3980</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>90390</v>
+        <v>1142004</v>
       </c>
       <c r="E48" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F48" t="n">
-        <v>2.2775</v>
+        <v>28.7741</v>
       </c>
     </row>
     <row r="49">
@@ -15854,158 +16391,158 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>553184.36</v>
+        <v>355326</v>
       </c>
       <c r="E49" t="n">
         <v>3968860.71</v>
       </c>
       <c r="F49" t="n">
-        <v>13.9381</v>
+        <v>8.9528</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>61592</v>
+        <v>1497534</v>
       </c>
       <c r="E50" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F50" t="n">
-        <v>5.1982</v>
+        <v>37.7321</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8280</v>
+        <v>99200</v>
       </c>
       <c r="E51" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6988</v>
+        <v>2.4995</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>49696.78</v>
       </c>
       <c r="E52" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1.2522</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1112992</v>
+        <v>90390</v>
       </c>
       <c r="E53" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F53" t="n">
-        <v>93.9336</v>
+        <v>2.2775</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>372400</v>
       </c>
       <c r="E54" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>9.382999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16014,13 +16551,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2007</v>
+        <v>180784.36</v>
       </c>
       <c r="E55" t="n">
-        <v>1184871</v>
+        <v>3968860.71</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1694</v>
+        <v>4.5551</v>
       </c>
     </row>
     <row r="56">
@@ -16031,7 +16568,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16040,13 +16577,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>139650</v>
+        <v>61592</v>
       </c>
       <c r="E56" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F56" t="n">
-        <v>76.1978</v>
+        <v>5.1982</v>
       </c>
     </row>
     <row r="57">
@@ -16057,7 +16594,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16066,13 +16603,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>21480</v>
+        <v>8280</v>
       </c>
       <c r="E57" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F57" t="n">
-        <v>11.7202</v>
+        <v>0.6988</v>
       </c>
     </row>
     <row r="58">
@@ -16083,7 +16620,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16095,7 +16632,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -16109,7 +16646,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16118,13 +16655,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17469</v>
+        <v>1112992</v>
       </c>
       <c r="E59" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F59" t="n">
-        <v>9.531700000000001</v>
+        <v>93.9336</v>
       </c>
     </row>
     <row r="60">
@@ -16135,7 +16672,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16144,13 +16681,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F60" t="n">
-        <v>1.0804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -16161,22 +16698,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2694</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>183273</v>
+        <v>1184871</v>
       </c>
       <c r="F61" t="n">
-        <v>1.4699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -16187,22 +16724,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>119960</v>
+        <v>2007</v>
       </c>
       <c r="E62" t="n">
-        <v>153032.84</v>
+        <v>1184871</v>
       </c>
       <c r="F62" t="n">
-        <v>78.3884</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="63">
@@ -16213,22 +16750,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13200</v>
+        <v>139650</v>
       </c>
       <c r="E63" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F63" t="n">
-        <v>8.6256</v>
+        <v>76.1978</v>
       </c>
     </row>
     <row r="64">
@@ -16239,22 +16776,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>21480</v>
       </c>
       <c r="E64" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>11.7202</v>
       </c>
     </row>
     <row r="65">
@@ -16265,22 +16802,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18256.84</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F65" t="n">
-        <v>11.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -16291,22 +16828,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>17469</v>
       </c>
       <c r="E66" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>9.531700000000001</v>
       </c>
     </row>
     <row r="67">
@@ -16317,22 +16854,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1616</v>
+        <v>1980</v>
       </c>
       <c r="E67" t="n">
-        <v>153032.84</v>
+        <v>183273</v>
       </c>
       <c r="F67" t="n">
-        <v>1.056</v>
+        <v>1.0804</v>
       </c>
     </row>
     <row r="68">
@@ -16343,22 +16880,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>483720</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F68" t="n">
-        <v>50.0271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -16369,22 +16906,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>246780</v>
+        <v>2694</v>
       </c>
       <c r="E69" t="n">
-        <v>966916.14</v>
+        <v>183273</v>
       </c>
       <c r="F69" t="n">
-        <v>25.5224</v>
+        <v>1.4699</v>
       </c>
     </row>
     <row r="70">
@@ -16395,22 +16932,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>54600</v>
+        <v>119960</v>
       </c>
       <c r="E70" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F70" t="n">
-        <v>5.6468</v>
+        <v>78.3884</v>
       </c>
     </row>
     <row r="71">
@@ -16421,22 +16958,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>78122.14</v>
+        <v>13200</v>
       </c>
       <c r="E71" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F71" t="n">
-        <v>8.079499999999999</v>
+        <v>8.6256</v>
       </c>
     </row>
     <row r="72">
@@ -16447,22 +16984,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -16473,22 +17010,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>99734</v>
+        <v>18256.84</v>
       </c>
       <c r="E73" t="n">
-        <v>966916.14</v>
+        <v>153032.84</v>
       </c>
       <c r="F73" t="n">
-        <v>10.3146</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="74">
@@ -16499,22 +17036,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>421948</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F74" t="n">
-        <v>89.5044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -16525,22 +17062,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>26400</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F75" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -16551,22 +17088,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="E76" t="n">
-        <v>471427.33</v>
+        <v>153032.84</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="77">
@@ -16577,22 +17114,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>21080.65</v>
+        <v>483720</v>
       </c>
       <c r="E77" t="n">
-        <v>471427.33</v>
+        <v>966916.14</v>
       </c>
       <c r="F77" t="n">
-        <v>4.4717</v>
+        <v>50.0271</v>
       </c>
     </row>
     <row r="78">
@@ -16603,22 +17140,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>246780</v>
       </c>
       <c r="E78" t="n">
-        <v>471427.33</v>
+        <v>966916.14</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>25.5224</v>
       </c>
     </row>
     <row r="79">
@@ -16629,22 +17166,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1998.68</v>
+        <v>54600</v>
       </c>
       <c r="E79" t="n">
-        <v>471427.33</v>
+        <v>966916.14</v>
       </c>
       <c r="F79" t="n">
-        <v>0.424</v>
+        <v>5.6468</v>
       </c>
     </row>
     <row r="80">
@@ -16655,22 +17192,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>280956</v>
+        <v>78122.14</v>
       </c>
       <c r="E80" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F80" t="n">
-        <v>68.01130000000001</v>
+        <v>8.079499999999999</v>
       </c>
     </row>
     <row r="81">
@@ -16681,22 +17218,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>59200</v>
+        <v>3960</v>
       </c>
       <c r="E81" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F81" t="n">
-        <v>14.3306</v>
+        <v>0.4095</v>
       </c>
     </row>
     <row r="82">
@@ -16707,22 +17244,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>70400</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F82" t="n">
-        <v>17.0418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -16733,22 +17270,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>200</v>
+        <v>99734</v>
       </c>
       <c r="E83" t="n">
-        <v>413102</v>
+        <v>966916.14</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0484</v>
+        <v>10.3146</v>
       </c>
     </row>
     <row r="84">
@@ -16759,22 +17296,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>421948</v>
       </c>
       <c r="E84" t="n">
-        <v>413102</v>
+        <v>471427.33</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>89.5044</v>
       </c>
     </row>
     <row r="85">
@@ -16785,22 +17322,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2346</v>
+        <v>26400</v>
       </c>
       <c r="E85" t="n">
-        <v>413102</v>
+        <v>471427.33</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5679</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="86">
@@ -16811,22 +17348,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>146542</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F86" t="n">
-        <v>9.9986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -16837,22 +17374,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>33000</v>
+        <v>21080.65</v>
       </c>
       <c r="E87" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F87" t="n">
-        <v>2.2516</v>
+        <v>4.4717</v>
       </c>
     </row>
     <row r="88">
@@ -16863,19 +17400,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -16889,22 +17426,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3736.4</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -16915,22 +17452,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>71715</v>
+        <v>1998.68</v>
       </c>
       <c r="E90" t="n">
-        <v>1465620.4</v>
+        <v>471427.33</v>
       </c>
       <c r="F90" t="n">
-        <v>4.8931</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="91">
@@ -16941,22 +17478,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1210627</v>
+        <v>280956</v>
       </c>
       <c r="E91" t="n">
-        <v>1465620.4</v>
+        <v>413102</v>
       </c>
       <c r="F91" t="n">
-        <v>82.60169999999999</v>
+        <v>68.01130000000001</v>
       </c>
     </row>
     <row r="92">
@@ -16967,22 +17504,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>330466</v>
+        <v>59200</v>
       </c>
       <c r="E92" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F92" t="n">
-        <v>80.8449</v>
+        <v>14.3306</v>
       </c>
     </row>
     <row r="93">
@@ -16993,22 +17530,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>33420</v>
+        <v>70400</v>
       </c>
       <c r="E93" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F93" t="n">
-        <v>8.175800000000001</v>
+        <v>17.0418</v>
       </c>
     </row>
     <row r="94">
@@ -17019,22 +17556,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E94" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="95">
@@ -17045,22 +17582,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12301.21</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F95" t="n">
-        <v>3.0094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -17071,19 +17608,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -17097,7 +17634,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17106,13 +17643,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>32578</v>
+        <v>2346</v>
       </c>
       <c r="E97" t="n">
-        <v>408765.21</v>
+        <v>413102</v>
       </c>
       <c r="F97" t="n">
-        <v>7.9699</v>
+        <v>0.5679</v>
       </c>
     </row>
     <row r="98">
@@ -17123,7 +17660,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17132,13 +17669,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>141738.01</v>
+        <v>146542</v>
       </c>
       <c r="E98" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F98" t="n">
-        <v>20.699</v>
+        <v>9.9986</v>
       </c>
     </row>
     <row r="99">
@@ -17149,7 +17686,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -17158,13 +17695,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>109800</v>
+        <v>33000</v>
       </c>
       <c r="E99" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F99" t="n">
-        <v>16.0349</v>
+        <v>2.2516</v>
       </c>
     </row>
     <row r="100">
@@ -17175,7 +17712,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -17187,7 +17724,7 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -17201,7 +17738,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -17210,13 +17747,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>14327.36</v>
+        <v>3736.4</v>
       </c>
       <c r="E101" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F101" t="n">
-        <v>2.0923</v>
+        <v>0.2549</v>
       </c>
     </row>
     <row r="102">
@@ -17227,7 +17764,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -17236,13 +17773,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>27820</v>
+        <v>71715</v>
       </c>
       <c r="E102" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0627</v>
+        <v>4.8931</v>
       </c>
     </row>
     <row r="103">
@@ -17253,22 +17790,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>391072.5</v>
+        <v>1145200</v>
       </c>
       <c r="E103" t="n">
-        <v>684757.87</v>
+        <v>1465620.4</v>
       </c>
       <c r="F103" t="n">
-        <v>57.1111</v>
+        <v>78.13760000000001</v>
       </c>
     </row>
     <row r="104">
@@ -17279,22 +17816,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>68574</v>
+        <v>65427</v>
       </c>
       <c r="E104" t="n">
-        <v>80605.8</v>
+        <v>1465620.4</v>
       </c>
       <c r="F104" t="n">
-        <v>85.0733</v>
+        <v>4.4641</v>
       </c>
     </row>
     <row r="105">
@@ -17305,22 +17842,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11640</v>
+        <v>330466</v>
       </c>
       <c r="E105" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F105" t="n">
-        <v>14.4406</v>
+        <v>80.8449</v>
       </c>
     </row>
     <row r="106">
@@ -17331,22 +17868,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>33420</v>
       </c>
       <c r="E106" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>8.175800000000001</v>
       </c>
     </row>
     <row r="107">
@@ -17357,22 +17894,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>124.8</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -17383,22 +17920,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>12301.21</v>
       </c>
       <c r="E108" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>3.0094</v>
       </c>
     </row>
     <row r="109">
@@ -17409,22 +17946,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>80605.8</v>
+        <v>408765.21</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -17435,22 +17972,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>171462</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F110" t="n">
-        <v>65.20529999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -17461,22 +17998,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6600</v>
+        <v>32578</v>
       </c>
       <c r="E111" t="n">
-        <v>262957</v>
+        <v>408765.21</v>
       </c>
       <c r="F111" t="n">
-        <v>2.5099</v>
+        <v>7.9699</v>
       </c>
     </row>
     <row r="112">
@@ -17487,22 +18024,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>24800</v>
+        <v>141738.01</v>
       </c>
       <c r="E112" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F112" t="n">
-        <v>9.4312</v>
+        <v>20.699</v>
       </c>
     </row>
     <row r="113">
@@ -17513,22 +18050,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>109800</v>
       </c>
       <c r="E113" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>16.0349</v>
       </c>
     </row>
     <row r="114">
@@ -17539,19 +18076,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -17565,22 +18102,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>60095</v>
+        <v>14327.36</v>
       </c>
       <c r="E115" t="n">
-        <v>262957</v>
+        <v>684757.87</v>
       </c>
       <c r="F115" t="n">
-        <v>22.8535</v>
+        <v>2.0923</v>
       </c>
     </row>
     <row r="116">
@@ -17591,22 +18128,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>20000</v>
+        <v>27820</v>
       </c>
       <c r="E116" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F116" t="n">
-        <v>60.5697</v>
+        <v>4.0627</v>
       </c>
     </row>
     <row r="117">
@@ -17617,22 +18154,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1681</v>
+        <v>337300</v>
       </c>
       <c r="E117" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F117" t="n">
-        <v>5.0909</v>
+        <v>49.2583</v>
       </c>
     </row>
     <row r="118">
@@ -17643,22 +18180,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1000</v>
+        <v>53772.5</v>
       </c>
       <c r="E118" t="n">
-        <v>33019.8</v>
+        <v>684757.87</v>
       </c>
       <c r="F118" t="n">
-        <v>3.0285</v>
+        <v>7.8528</v>
       </c>
     </row>
     <row r="119">
@@ -17669,22 +18206,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>907.8</v>
+        <v>68574</v>
       </c>
       <c r="E119" t="n">
-        <v>33019.8</v>
+        <v>80605.8</v>
       </c>
       <c r="F119" t="n">
-        <v>2.7493</v>
+        <v>85.0733</v>
       </c>
     </row>
     <row r="120">
@@ -17695,22 +18232,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>家守/千金方/少年说</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>11640</v>
       </c>
       <c r="E120" t="n">
-        <v>33019.8</v>
+        <v>80605.8</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>14.4406</v>
       </c>
     </row>
     <row r="121">
@@ -17721,22 +18258,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>菌群</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9431</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>33019.8</v>
+        <v>80605.8</v>
       </c>
       <c r="F121" t="n">
-        <v>28.5617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -17747,22 +18284,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2386608.01</v>
+        <v>124.8</v>
       </c>
       <c r="E122" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F122" t="n">
-        <v>37.8325</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="123">
@@ -17773,22 +18310,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>家守/千金方/少年说</t>
+          <t>进化论</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>571481</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F123" t="n">
-        <v>9.059100000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -17799,22 +18336,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>菌群</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>150800</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F124" t="n">
-        <v>2.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -17825,22 +18362,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1279518.2</v>
+        <v>267</v>
       </c>
       <c r="E125" t="n">
-        <v>6308348.39</v>
+        <v>80605.8</v>
       </c>
       <c r="F125" t="n">
-        <v>20.2829</v>
+        <v>0.3312</v>
       </c>
     </row>
     <row r="126">
@@ -17851,22 +18388,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>进化论</t>
+          <t>咨询</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>105475</v>
+        <v>171462</v>
       </c>
       <c r="E126" t="n">
-        <v>6308348.39</v>
+        <v>262957</v>
       </c>
       <c r="F126" t="n">
-        <v>1.672</v>
+        <v>65.20529999999999</v>
       </c>
     </row>
     <row r="127">
@@ -17877,22 +18414,516 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E127" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2.5099</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>24800</v>
+      </c>
+      <c r="E128" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F128" t="n">
+        <v>9.4312</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>60095</v>
+      </c>
+      <c r="E132" t="n">
+        <v>262957</v>
+      </c>
+      <c r="F132" t="n">
+        <v>22.8535</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E133" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F133" t="n">
+        <v>60.5697</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1681</v>
+      </c>
+      <c r="E134" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F134" t="n">
+        <v>5.0909</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E135" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3.0285</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>907.8</v>
+      </c>
+      <c r="E136" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.7493</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>9431</v>
+      </c>
+      <c r="E139" t="n">
+        <v>33019.8</v>
+      </c>
+      <c r="F139" t="n">
+        <v>28.5617</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>咨询</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2386608.01</v>
+      </c>
+      <c r="E140" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F140" t="n">
+        <v>37.8325</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>家守/千金方/少年说</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>571481</v>
+      </c>
+      <c r="E141" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F141" t="n">
+        <v>9.059100000000001</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>菌群</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>150800</v>
+      </c>
+      <c r="E142" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2.3905</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1279518.2</v>
+      </c>
+      <c r="E143" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F143" t="n">
+        <v>20.2829</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>进化论</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>105475</v>
+      </c>
+      <c r="E144" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.672</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1482500</v>
+      </c>
+      <c r="E145" t="n">
+        <v>6308348.39</v>
+      </c>
+      <c r="F145" t="n">
+        <v>23.5006</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>线下</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D127" t="n">
-        <v>1814466.18</v>
-      </c>
-      <c r="E127" t="n">
+      <c r="D146" t="n">
+        <v>331966.18</v>
+      </c>
+      <c r="E146" t="n">
         <v>6308348.39</v>
       </c>
-      <c r="F127" t="n">
-        <v>28.7629</v>
+      <c r="F146" t="n">
+        <v>5.2623</v>
       </c>
     </row>
   </sheetData>
@@ -26474,7 +27505,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -26499,7 +27530,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -26524,16 +27555,16 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>青少年营地食宿费补差价</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>49800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="346">
@@ -26554,11 +27585,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>青少年营地食宿费补差价</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>5200</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="347">
@@ -37074,7 +38105,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -37099,7 +38130,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -37124,16 +38155,16 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>未来之翼7日身心复能营</t>
         </is>
       </c>
       <c r="E769" t="n">
-        <v>49800</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="770">
@@ -37149,16 +38180,16 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>未来之翼7日身心复能营</t>
+          <t>青少年营地食宿费补差价</t>
         </is>
       </c>
       <c r="E770" t="n">
-        <v>19800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="771">
@@ -37179,11 +38210,11 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>心理咨询 - 青英咨询 - 10次</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E771" t="n">
-        <v>8000</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="772">
@@ -37204,11 +38235,11 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>青少年营地食宿费补差价</t>
+          <t>心理咨询 - 青英咨询 - 10次</t>
         </is>
       </c>
       <c r="E772" t="n">
-        <v>5200</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="773">
@@ -37404,7 +38435,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>yl5（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E780" t="n">
@@ -37429,7 +38460,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
+          <t>青少年19元巨量</t>
         </is>
       </c>
       <c r="E781" t="n">
@@ -37454,7 +38485,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>yl5（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E782" t="n">
@@ -37479,7 +38510,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>青少年19元巨量</t>
+          <t>qy（网课、家长学）青少年家庭同行者计划一周短训营</t>
         </is>
       </c>
       <c r="E783" t="n">
@@ -37554,7 +38585,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>青少年同行者一周家长短训营亲子教育网课</t>
+          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
         </is>
       </c>
       <c r="E786" t="n">
@@ -37579,7 +38610,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>青少年adq新链接XY</t>
         </is>
       </c>
       <c r="E787" t="n">
@@ -37604,7 +38635,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
+          <t>青少年同行者一周家长短训营亲子教育网课</t>
         </is>
       </c>
       <c r="E788" t="n">
@@ -37654,7 +38685,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>青少年adq新链接XY</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E790" t="n">
@@ -37729,7 +38760,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E793" t="n">
@@ -37754,7 +38785,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>0元青少年-LH</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E794" t="n">
@@ -37779,7 +38810,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E795" t="n">
@@ -37804,7 +38835,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>杭州一日一生体验课</t>
         </is>
       </c>
       <c r="E796" t="n">
@@ -37829,7 +38860,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>义诊-线上</t>
         </is>
       </c>
       <c r="E797" t="n">
@@ -37854,7 +38885,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>0元青少年-LH</t>
         </is>
       </c>
       <c r="E798" t="n">
@@ -37879,7 +38910,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>义诊-线上</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E799" t="n">
@@ -37904,7 +38935,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>青少年同行者智慧父母启航营</t>
         </is>
       </c>
       <c r="E800" t="n">
@@ -37929,7 +38960,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>青少年同行者智慧父母启航营</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E801" t="n">
@@ -40299,7 +41330,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -40324,7 +41355,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -40349,16 +41380,16 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>动力唤醒方案</t>
+          <t>未来之翼7日心理能量唤醒营</t>
         </is>
       </c>
       <c r="E898" t="n">
-        <v>49800</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="899">
@@ -40374,16 +41405,16 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>未来之翼7日心理能量唤醒营</t>
+          <t>青少年营地食宿费补差价</t>
         </is>
       </c>
       <c r="E899" t="n">
-        <v>19800</v>
+        <v>100</v>
       </c>
     </row>
     <row r="900">
@@ -40404,11 +41435,11 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>门店《一日一生》</t>
+          <t>动力唤醒方案</t>
         </is>
       </c>
       <c r="E900" t="n">
-        <v>1592</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="901">
@@ -40429,11 +41460,11 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>ACT个案概念化工作坊</t>
+          <t>门店《一日一生》</t>
         </is>
       </c>
       <c r="E901" t="n">
-        <v>1500</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="902">
@@ -40454,11 +41485,11 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>解郁丸[4g*9袋]</t>
+          <t>ACT个案概念化工作坊</t>
         </is>
       </c>
       <c r="E902" t="n">
-        <v>333.5</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="903">
@@ -40479,11 +41510,11 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
+          <t>解郁丸[4g*9袋]</t>
         </is>
       </c>
       <c r="E903" t="n">
-        <v>114</v>
+        <v>333.5</v>
       </c>
     </row>
     <row r="904">
@@ -40504,11 +41535,11 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>青少年营地食宿费补差价</t>
+          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
         </is>
       </c>
       <c r="E904" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="905">
@@ -40679,7 +41710,7 @@
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）WY</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E911" t="n">
@@ -40704,7 +41735,7 @@
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>青少年同行者计划周训营（网课）WY</t>
         </is>
       </c>
       <c r="E912" t="n">
@@ -40729,7 +41760,7 @@
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题yh</t>
+          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
         </is>
       </c>
       <c r="E913" t="n">
@@ -40754,7 +41785,7 @@
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>青少年同行者计划：试听课</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题yh</t>
         </is>
       </c>
       <c r="E914" t="n">
@@ -40779,7 +41810,7 @@
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>lc（网课、家长学）青少年家庭同行者计划一周短训营lc</t>
+          <t>青少年同行者计划：试听课</t>
         </is>
       </c>
       <c r="E915" t="n">
@@ -40854,7 +41885,7 @@
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>杭州一日一生体验课</t>
         </is>
       </c>
       <c r="E918" t="n">
@@ -40879,7 +41910,7 @@
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>21天蛋壳跳动休学复能营</t>
         </is>
       </c>
       <c r="E919" t="n">
@@ -40904,7 +41935,7 @@
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E920" t="n">
@@ -40929,7 +41960,7 @@
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E921" t="n">
@@ -40954,7 +41985,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>21天蛋壳跳动休学复能营</t>
+          <t>青少年同行者计划</t>
         </is>
       </c>
       <c r="E922" t="n">
@@ -40979,7 +42010,7 @@
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E923" t="n">
@@ -41004,7 +42035,7 @@
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>青少年同行者计划</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E924" t="n">
@@ -42324,16 +43355,16 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>青少年同行者计划之领航营亲子教育网课</t>
+          <t>未来之翼7日身心复能营</t>
         </is>
       </c>
       <c r="E977" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
     </row>
     <row r="978">
@@ -42349,16 +43380,16 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>营地</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>心理咨询师职业能力水平评价考试培训</t>
+          <t>青少年【未来之翼】身心节律复能7日营</t>
         </is>
       </c>
       <c r="E978" t="n">
-        <v>3800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="979">
@@ -42379,11 +43410,11 @@
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>考务服务费（心理咨询专业技能培训）</t>
+          <t>青少年同行者计划之领航营亲子教育网课</t>
         </is>
       </c>
       <c r="E979" t="n">
-        <v>540</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="980">
@@ -42404,11 +43435,11 @@
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
+          <t>心理咨询师职业能力水平评价考试培训</t>
         </is>
       </c>
       <c r="E980" t="n">
-        <v>35</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="981">
@@ -42429,11 +43460,11 @@
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>青少年同行者计划周训营（网课）WY</t>
+          <t>考务服务费（心理咨询专业技能培训）</t>
         </is>
       </c>
       <c r="E981" t="n">
-        <v>19</v>
+        <v>540</v>
       </c>
     </row>
     <row r="982">
@@ -42454,11 +43485,11 @@
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
+          <t>（网课、家长学）青少年家庭同行者计划一周短训营LH</t>
         </is>
       </c>
       <c r="E982" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="983">
@@ -42504,7 +43535,7 @@
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
+          <t>青少年同行者短训营-帮助家长解决孩子厌学休学叛逆顶嘴无法沟通问题</t>
         </is>
       </c>
       <c r="E984" t="n">
@@ -42529,11 +43560,11 @@
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>观心少年-腾讯-lmt</t>
+          <t>（家长学）青少年同行者网课一周短训营-帮助家长应对孩子厌学休学叛逆情绪低落等问题</t>
         </is>
       </c>
       <c r="E985" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="986">
@@ -42554,11 +43585,11 @@
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>杭州一日一生体验课</t>
+          <t>青少年同行者计划周训营（网课）WY</t>
         </is>
       </c>
       <c r="E986" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="987">
@@ -42579,7 +43610,7 @@
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>未来之翼7日身心复能营</t>
+          <t>0元青少年--LH</t>
         </is>
       </c>
       <c r="E987" t="n">
@@ -42629,7 +43660,7 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>0元青少年--LH</t>
+          <t>杭州一日一生体验课</t>
         </is>
       </c>
       <c r="E989" t="n">
@@ -42654,7 +43685,7 @@
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>青少年【未来之翼】身心节律复能7日营</t>
+          <t>观心少年2天1夜心理赋能营-ys-北京</t>
         </is>
       </c>
       <c r="E990" t="n">
@@ -42679,7 +43710,7 @@
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
+          <t>观心少年-腾讯-lmt</t>
         </is>
       </c>
       <c r="E991" t="n">
@@ -42704,7 +43735,7 @@
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>观心少年2天1夜心理赋能营-ys-北京</t>
+          <t>观心少年2天1夜厌学复能营-ys-杭州</t>
         </is>
       </c>
       <c r="E992" t="n">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -4121,7 +4121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4132,22 +4132,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>呼出</t>
+          <t>通话数/日</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>90s以上</t>
+          <t>≥90S通话数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>时长(分)</t>
+          <t>≥20分钟通话数</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>加微信</t>
+          <t>云客通话数</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>企业微信通话数</t>
         </is>
       </c>
     </row>
@@ -4158,16 +4163,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>216</v>
+        <v>306</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>567.2</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>2835</v>
+        <v>269</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -4177,16 +4185,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>340.6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>37</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -4196,16 +4207,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>660</v>
+        <v>446</v>
       </c>
       <c r="C4" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D4" t="n">
-        <v>1388.4</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>3311</v>
+        <v>406</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -4215,16 +4229,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>131</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6972,7 +6989,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>芊雅</t>
+          <t>王芊雅</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -8264,30 +8281,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>黄惠作</t>
+          <t>黄慧作</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>200000</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>197010</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>54910</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>142100</v>
       </c>
     </row>
     <row r="50">

--- a/导出_总表_10月.xlsx
+++ b/导出_总表_10月.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1133732</v>
+        <v>1491270</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+67.0%</t>
+          <t>+27.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>613316</v>
+        <v>959874</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+135.4%</t>
+          <t>+50.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1571,19 +1571,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10846084</v>
+        <v>11203622</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+43.6%</t>
+          <t>+39.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9109939</v>
+        <v>9456497</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+40.3%</t>
+          <t>+35.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4932,7 +4932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6460,43 +6460,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>观澜组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>姚闯</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>102694</v>
+        <v>215700</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>33460</v>
+        <v>16400</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>69234</v>
+        <v>199300</v>
       </c>
     </row>
     <row r="38">
@@ -6507,38 +6507,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>魏恺志</t>
+          <t>姚闯</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="D38" t="n">
-        <v>8280</v>
+        <v>102694</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2160</v>
+        <v>33460</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6120</v>
+        <v>69234</v>
       </c>
     </row>
     <row r="39">
@@ -6549,38 +6549,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>杨旺忠</t>
+          <t>魏恺志</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="D39" t="n">
-        <v>93640</v>
+        <v>8280</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4060</v>
+        <v>2160</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>89580</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="40">
@@ -6591,38 +6591,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>闫浩</t>
+          <t>杨旺忠</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>93640</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>4060</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>89580</v>
       </c>
     </row>
     <row r="41">
@@ -6633,38 +6633,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>余文静</t>
+          <t>闫浩</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>126380</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4240</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>122140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -6675,38 +6675,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>陈鑫</t>
+          <t>余文静</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="D42" t="n">
-        <v>436890</v>
+        <v>126380</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1980</v>
+        <v>4240</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>434910</v>
+        <v>122140</v>
       </c>
     </row>
     <row r="43">
@@ -6717,38 +6717,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>吴云龙</t>
+          <t>陈鑫</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="D43" t="n">
-        <v>57280</v>
+        <v>436890</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>57280</v>
+        <v>434910</v>
       </c>
     </row>
     <row r="44">
@@ -6759,37 +6759,79 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>龙刚</t>
+          <t>吴云龙</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="D44" t="n">
-        <v>2190</v>
+        <v>57280</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>57280</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>龙刚</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2190</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>2.2%</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>2.2%</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="H45" t="n">
         <v>2980</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>136.1%</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J45" t="n">
         <v>-790</v>
       </c>
     </row>
